--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="H1012" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1072"/>
+  <dimension ref="A1:K1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.1247</v>
+        <v>5.085</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.1253</v>
+        <v>5.0856</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
     </row>
     <row r="774">
       <c r="A774" s="1" t="n">
-        <v>44469</v>
+        <v>46265</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -39859,34 +39859,34 @@
         </is>
       </c>
       <c r="C774" t="n">
-        <v>20541</v>
+        <v>3546</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>R$ milhões</t>
+          <t>US$ milhões</t>
         </is>
       </c>
       <c r="G774" t="n">
-        <v>2546936</v>
+        <v>372616</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas físicas.</t>
+          <t>Reservas internacionais.</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -39896,13 +39896,13 @@
       </c>
       <c r="K774" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         </is>
       </c>
       <c r="G775" t="n">
-        <v>2601017</v>
+        <v>2546936</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
     </row>
     <row r="776">
       <c r="A776" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="G776" t="n">
-        <v>2664395</v>
+        <v>2601017</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
     </row>
     <row r="777">
       <c r="A777" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         </is>
       </c>
       <c r="G777" t="n">
-        <v>2708461</v>
+        <v>2664395</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
     </row>
     <row r="778">
       <c r="A778" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         </is>
       </c>
       <c r="G778" t="n">
-        <v>2735096</v>
+        <v>2708461</v>
       </c>
       <c r="H778" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
     </row>
     <row r="779">
       <c r="A779" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         </is>
       </c>
       <c r="G779" t="n">
-        <v>2756295</v>
+        <v>2735096</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
     </row>
     <row r="780">
       <c r="A780" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         </is>
       </c>
       <c r="G780" t="n">
-        <v>2800464</v>
+        <v>2756295</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
     </row>
     <row r="781">
       <c r="A781" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         </is>
       </c>
       <c r="G781" t="n">
-        <v>2830420</v>
+        <v>2800464</v>
       </c>
       <c r="H781" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
     </row>
     <row r="782">
       <c r="A782" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         </is>
       </c>
       <c r="G782" t="n">
-        <v>2875671</v>
+        <v>2830420</v>
       </c>
       <c r="H782" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         </is>
       </c>
       <c r="G783" t="n">
-        <v>2913035</v>
+        <v>2875671</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         </is>
       </c>
       <c r="G784" t="n">
-        <v>2952207</v>
+        <v>2913035</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         </is>
       </c>
       <c r="G785" t="n">
-        <v>3008528</v>
+        <v>2952207</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         </is>
       </c>
       <c r="G786" t="n">
-        <v>3054969</v>
+        <v>3008528</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         </is>
       </c>
       <c r="G787" t="n">
-        <v>3110134</v>
+        <v>3054969</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         </is>
       </c>
       <c r="G788" t="n">
-        <v>3155345</v>
+        <v>3110134</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>3187833</v>
+        <v>3155345</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         </is>
       </c>
       <c r="G790" t="n">
-        <v>3221831</v>
+        <v>3187833</v>
       </c>
       <c r="H790" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         </is>
       </c>
       <c r="G791" t="n">
-        <v>3234845</v>
+        <v>3221831</v>
       </c>
       <c r="H791" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         </is>
       </c>
       <c r="G792" t="n">
-        <v>3269910</v>
+        <v>3234845</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         </is>
       </c>
       <c r="G793" t="n">
-        <v>3281308</v>
+        <v>3269910</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="G794" t="n">
-        <v>3308178</v>
+        <v>3281308</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
     </row>
     <row r="795">
       <c r="A795" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         </is>
       </c>
       <c r="G795" t="n">
-        <v>3309846</v>
+        <v>3308178</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
     </row>
     <row r="796">
       <c r="A796" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         </is>
       </c>
       <c r="G796" t="n">
-        <v>3331330</v>
+        <v>3309846</v>
       </c>
       <c r="H796" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
     </row>
     <row r="797">
       <c r="A797" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         </is>
       </c>
       <c r="G797" t="n">
-        <v>3386405</v>
+        <v>3331330</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
     </row>
     <row r="798">
       <c r="A798" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         </is>
       </c>
       <c r="G798" t="n">
-        <v>3410769</v>
+        <v>3386405</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
     </row>
     <row r="799">
       <c r="A799" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         </is>
       </c>
       <c r="G799" t="n">
-        <v>3449000</v>
+        <v>3410769</v>
       </c>
       <c r="H799" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
     </row>
     <row r="800">
       <c r="A800" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="G800" t="n">
-        <v>3490337</v>
+        <v>3449000</v>
       </c>
       <c r="H800" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>3521672</v>
+        <v>3490337</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3560345</v>
+        <v>3521672</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3580652</v>
+        <v>3560345</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3613967</v>
+        <v>3580652</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         </is>
       </c>
       <c r="G805" t="n">
-        <v>3646659</v>
+        <v>3613967</v>
       </c>
       <c r="H805" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         </is>
       </c>
       <c r="G806" t="n">
-        <v>3675652</v>
+        <v>3646659</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         </is>
       </c>
       <c r="G807" t="n">
-        <v>3705041</v>
+        <v>3675652</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         </is>
       </c>
       <c r="G808" t="n">
-        <v>3745844</v>
+        <v>3705041</v>
       </c>
       <c r="H808" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         </is>
       </c>
       <c r="G809" t="n">
-        <v>3790900</v>
+        <v>3745844</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         </is>
       </c>
       <c r="G810" t="n">
-        <v>3831700</v>
+        <v>3790900</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="G811" t="n">
-        <v>3877584</v>
+        <v>3831700</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         </is>
       </c>
       <c r="G812" t="n">
-        <v>3929668</v>
+        <v>3877584</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="G813" t="n">
-        <v>3965425</v>
+        <v>3929668</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         </is>
       </c>
       <c r="G814" t="n">
-        <v>4013059</v>
+        <v>3965425</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         </is>
       </c>
       <c r="G815" t="n">
-        <v>4034293</v>
+        <v>4013059</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         </is>
       </c>
       <c r="G816" t="n">
-        <v>4078202</v>
+        <v>4034293</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         </is>
       </c>
       <c r="G817" t="n">
-        <v>4111522</v>
+        <v>4078202</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         </is>
       </c>
       <c r="G818" t="n">
-        <v>4133579</v>
+        <v>4111522</v>
       </c>
       <c r="H818" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
     </row>
     <row r="819">
       <c r="A819" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         </is>
       </c>
       <c r="G819" t="n">
-        <v>4155970</v>
+        <v>4133579</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
     </row>
     <row r="820">
       <c r="A820" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         </is>
       </c>
       <c r="G820" t="n">
-        <v>4188808</v>
+        <v>4155970</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
     </row>
     <row r="821">
       <c r="A821" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         </is>
       </c>
       <c r="G821" t="n">
-        <v>4228171</v>
+        <v>4188808</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
     </row>
     <row r="822">
       <c r="A822" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         </is>
       </c>
       <c r="G822" t="n">
-        <v>4262888</v>
+        <v>4228171</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
     </row>
     <row r="823">
       <c r="A823" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         </is>
       </c>
       <c r="G823" t="n">
-        <v>4326256</v>
+        <v>4262888</v>
       </c>
       <c r="H823" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
     </row>
     <row r="824">
       <c r="A824" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         </is>
       </c>
       <c r="G824" t="n">
-        <v>4387321</v>
+        <v>4326256</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
     </row>
     <row r="825">
       <c r="A825" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         </is>
       </c>
       <c r="G825" t="n">
-        <v>4435517</v>
+        <v>4387321</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
     </row>
     <row r="826">
       <c r="A826" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="G826" t="n">
-        <v>4476542</v>
+        <v>4435517</v>
       </c>
       <c r="H826" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
     </row>
     <row r="827">
       <c r="A827" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         </is>
       </c>
       <c r="G827" t="n">
-        <v>4501299</v>
+        <v>4476542</v>
       </c>
       <c r="H827" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
     </row>
     <row r="828">
       <c r="A828" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         </is>
       </c>
       <c r="G828" t="n">
-        <v>4553022</v>
+        <v>4501299</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>4574368</v>
+        <v>4553022</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
     </row>
     <row r="830">
       <c r="A830" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>4597152</v>
+        <v>4574368</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
     </row>
     <row r="831">
       <c r="A831" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>4602668</v>
+        <v>4597152</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
     </row>
     <row r="832">
       <c r="A832" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>4640730</v>
+        <v>4602668</v>
       </c>
       <c r="H832" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
     </row>
     <row r="833">
       <c r="A833" s="1" t="n">
-        <v>44469</v>
+        <v>46234</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -42868,11 +42868,11 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>20540</v>
+        <v>20541</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -42886,11 +42886,11 @@
         </is>
       </c>
       <c r="G833" t="n">
-        <v>1894119</v>
+        <v>4640730</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
+          <t>Saldo da carteira de crédito - pessoas físicas.</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -42911,7 +42911,7 @@
     </row>
     <row r="834">
       <c r="A834" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>1910940</v>
+        <v>1894119</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
     </row>
     <row r="835">
       <c r="A835" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1933111</v>
+        <v>1910940</v>
       </c>
       <c r="H835" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
     </row>
     <row r="836">
       <c r="A836" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>1974391</v>
+        <v>1933111</v>
       </c>
       <c r="H836" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
     </row>
     <row r="837">
       <c r="A837" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="G837" t="n">
-        <v>1947035</v>
+        <v>1974391</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
     </row>
     <row r="838">
       <c r="A838" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         </is>
       </c>
       <c r="G838" t="n">
-        <v>1971524</v>
+        <v>1947035</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>1994119</v>
+        <v>1971524</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         </is>
       </c>
       <c r="G840" t="n">
-        <v>2003312</v>
+        <v>1994119</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
     </row>
     <row r="841">
       <c r="A841" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>2013726</v>
+        <v>2003312</v>
       </c>
       <c r="H841" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     </row>
     <row r="842">
       <c r="A842" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>2052569</v>
+        <v>2013726</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
     </row>
     <row r="843">
       <c r="A843" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>2047038</v>
+        <v>2052569</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
     </row>
     <row r="844">
       <c r="A844" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         </is>
       </c>
       <c r="G844" t="n">
-        <v>2064183</v>
+        <v>2047038</v>
       </c>
       <c r="H844" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
     </row>
     <row r="845">
       <c r="A845" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         </is>
       </c>
       <c r="G845" t="n">
-        <v>2109806</v>
+        <v>2064183</v>
       </c>
       <c r="H845" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
     </row>
     <row r="846">
       <c r="A846" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         </is>
       </c>
       <c r="G846" t="n">
-        <v>2105856</v>
+        <v>2109806</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
     </row>
     <row r="847">
       <c r="A847" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>2130312</v>
+        <v>2105856</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
     </row>
     <row r="848">
       <c r="A848" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>2178236</v>
+        <v>2130312</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
     </row>
     <row r="849">
       <c r="A849" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>2151399</v>
+        <v>2178236</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
     </row>
     <row r="850">
       <c r="A850" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>2136105</v>
+        <v>2151399</v>
       </c>
       <c r="H850" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
     </row>
     <row r="851">
       <c r="A851" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>2154900</v>
+        <v>2136105</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
     </row>
     <row r="852">
       <c r="A852" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>2145000</v>
+        <v>2154900</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         </is>
       </c>
       <c r="G853" t="n">
-        <v>2145530</v>
+        <v>2145000</v>
       </c>
       <c r="H853" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
     </row>
     <row r="854">
       <c r="A854" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>2169613</v>
+        <v>2145530</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>2153541</v>
+        <v>2169613</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>2172658</v>
+        <v>2153541</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
     </row>
     <row r="857">
       <c r="A857" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>2215175</v>
+        <v>2172658</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
     </row>
     <row r="858">
       <c r="A858" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>2204808</v>
+        <v>2215175</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
     </row>
     <row r="859">
       <c r="A859" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>2220766</v>
+        <v>2204808</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
     </row>
     <row r="860">
       <c r="A860" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>2283485</v>
+        <v>2220766</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
     </row>
     <row r="861">
       <c r="A861" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="G861" t="n">
-        <v>2234362</v>
+        <v>2283485</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
     </row>
     <row r="862">
       <c r="A862" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2235302</v>
+        <v>2234362</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
     </row>
     <row r="863">
       <c r="A863" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>2285775</v>
+        <v>2235302</v>
       </c>
       <c r="H863" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
     </row>
     <row r="864">
       <c r="A864" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>2268879</v>
+        <v>2285775</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
     </row>
     <row r="865">
       <c r="A865" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>2278309</v>
+        <v>2268879</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
     </row>
     <row r="866">
       <c r="A866" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>2336858</v>
+        <v>2278309</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
     </row>
     <row r="867">
       <c r="A867" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>2323362</v>
+        <v>2336858</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
     </row>
     <row r="868">
       <c r="A868" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2344397</v>
+        <v>2323362</v>
       </c>
       <c r="H868" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
     </row>
     <row r="869">
       <c r="A869" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2384828</v>
+        <v>2344397</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
     </row>
     <row r="870">
       <c r="A870" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2397533</v>
+        <v>2384828</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
     </row>
     <row r="871">
       <c r="A871" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2436022</v>
+        <v>2397533</v>
       </c>
       <c r="H871" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
     </row>
     <row r="872">
       <c r="A872" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2499177</v>
+        <v>2436022</v>
       </c>
       <c r="H872" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
     </row>
     <row r="873">
       <c r="A873" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2451957</v>
+        <v>2499177</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
     </row>
     <row r="874">
       <c r="A874" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B874" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2477151</v>
+        <v>2451957</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B875" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2498262</v>
+        <v>2477151</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
     </row>
     <row r="876">
       <c r="A876" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B876" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2512426</v>
+        <v>2498262</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
     </row>
     <row r="877">
       <c r="A877" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B877" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2532708</v>
+        <v>2512426</v>
       </c>
       <c r="H877" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
     </row>
     <row r="878">
       <c r="A878" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B878" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>2547693</v>
+        <v>2532708</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
     </row>
     <row r="879">
       <c r="A879" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B879" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2544400</v>
+        <v>2547693</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
     </row>
     <row r="880">
       <c r="A880" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B880" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>2546265</v>
+        <v>2544400</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
     </row>
     <row r="881">
       <c r="A881" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B881" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2589817</v>
+        <v>2546265</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
     </row>
     <row r="882">
       <c r="A882" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B882" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>2597630</v>
+        <v>2589817</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
     </row>
     <row r="883">
       <c r="A883" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B883" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>2616902</v>
+        <v>2597630</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
     </row>
     <row r="884">
       <c r="A884" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B884" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>2701735</v>
+        <v>2616902</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
     </row>
     <row r="885">
       <c r="A885" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B885" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>2654220</v>
+        <v>2701735</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
     </row>
     <row r="886">
       <c r="A886" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B886" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>2656484</v>
+        <v>2654220</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
     </row>
     <row r="887">
       <c r="A887" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B887" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>2687535</v>
+        <v>2656484</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
     </row>
     <row r="888">
       <c r="A888" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B888" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>2685397</v>
+        <v>2687535</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
     </row>
     <row r="889">
       <c r="A889" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B889" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>2708154</v>
+        <v>2685397</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
     </row>
     <row r="890">
       <c r="A890" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B890" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>2750625</v>
+        <v>2708154</v>
       </c>
       <c r="H890" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
     </row>
     <row r="891">
       <c r="A891" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B891" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         </is>
       </c>
       <c r="G891" t="n">
-        <v>2731513</v>
+        <v>2750625</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
     </row>
     <row r="892">
       <c r="A892" s="1" t="n">
-        <v>44469</v>
+        <v>46234</v>
       </c>
       <c r="B892" t="inlineStr">
         <is>
@@ -45877,11 +45877,11 @@
         </is>
       </c>
       <c r="C892" t="n">
-        <v>20539</v>
+        <v>20540</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -45895,11 +45895,11 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>4441056</v>
+        <v>2731513</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - total.</t>
+          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -45920,7 +45920,7 @@
     </row>
     <row r="893">
       <c r="A893" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B893" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>4511956</v>
+        <v>4441056</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
     </row>
     <row r="894">
       <c r="A894" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B894" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>4597507</v>
+        <v>4511956</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
     </row>
     <row r="895">
       <c r="A895" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B895" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>4682852</v>
+        <v>4597507</v>
       </c>
       <c r="H895" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
     </row>
     <row r="896">
       <c r="A896" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B896" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>4682131</v>
+        <v>4682852</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
     </row>
     <row r="897">
       <c r="A897" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B897" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>4727818</v>
+        <v>4682131</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
     </row>
     <row r="898">
       <c r="A898" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B898" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>4794583</v>
+        <v>4727818</v>
       </c>
       <c r="H898" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
     </row>
     <row r="899">
       <c r="A899" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B899" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>4833732</v>
+        <v>4794583</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
     </row>
     <row r="900">
       <c r="A900" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B900" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>4889397</v>
+        <v>4833732</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
     </row>
     <row r="901">
       <c r="A901" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B901" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>4965603</v>
+        <v>4889397</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
     </row>
     <row r="902">
       <c r="A902" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B902" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>4999244</v>
+        <v>4965603</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
     </row>
     <row r="903">
       <c r="A903" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B903" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>5072711</v>
+        <v>4999244</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
     </row>
     <row r="904">
       <c r="A904" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B904" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>5164775</v>
+        <v>5072711</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
     </row>
     <row r="905">
       <c r="A905" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B905" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>5215990</v>
+        <v>5164775</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
     </row>
     <row r="906">
       <c r="A906" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B906" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>5285657</v>
+        <v>5215990</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
     </row>
     <row r="907">
       <c r="A907" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B907" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>5366069</v>
+        <v>5285657</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
     </row>
     <row r="908">
       <c r="A908" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B908" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>5373231</v>
+        <v>5366069</v>
       </c>
       <c r="H908" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
     </row>
     <row r="909">
       <c r="A909" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B909" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>5370950</v>
+        <v>5373231</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
     </row>
     <row r="910">
       <c r="A910" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B910" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>5424811</v>
+        <v>5370950</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
     </row>
     <row r="911">
       <c r="A911" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B911" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>5426307</v>
+        <v>5424811</v>
       </c>
       <c r="H911" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
     </row>
     <row r="912">
       <c r="A912" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B912" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>5453708</v>
+        <v>5426307</v>
       </c>
       <c r="H912" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
     </row>
     <row r="913">
       <c r="A913" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B913" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>5479459</v>
+        <v>5453708</v>
       </c>
       <c r="H913" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
     </row>
     <row r="914">
       <c r="A914" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B914" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>5484871</v>
+        <v>5479459</v>
       </c>
       <c r="H914" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
     </row>
     <row r="915">
       <c r="A915" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B915" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>5559063</v>
+        <v>5484871</v>
       </c>
       <c r="H915" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
     </row>
     <row r="916">
       <c r="A916" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B916" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>5625945</v>
+        <v>5559063</v>
       </c>
       <c r="H916" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
     </row>
     <row r="917">
       <c r="A917" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B917" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>5653808</v>
+        <v>5625945</v>
       </c>
       <c r="H917" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
     </row>
     <row r="918">
       <c r="A918" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B918" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>5711103</v>
+        <v>5653808</v>
       </c>
       <c r="H918" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
     </row>
     <row r="919">
       <c r="A919" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B919" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>5805157</v>
+        <v>5711103</v>
       </c>
       <c r="H919" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
     </row>
     <row r="920">
       <c r="A920" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B920" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>5794707</v>
+        <v>5805157</v>
       </c>
       <c r="H920" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
     </row>
     <row r="921">
       <c r="A921" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B921" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>5815954</v>
+        <v>5794707</v>
       </c>
       <c r="H921" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
     </row>
     <row r="922">
       <c r="A922" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B922" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>5899742</v>
+        <v>5815954</v>
       </c>
       <c r="H922" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
     </row>
     <row r="923">
       <c r="A923" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B923" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>5915538</v>
+        <v>5899742</v>
       </c>
       <c r="H923" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
     </row>
     <row r="924">
       <c r="A924" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B924" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>5953960</v>
+        <v>5915538</v>
       </c>
       <c r="H924" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
     </row>
     <row r="925">
       <c r="A925" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B925" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>6041898</v>
+        <v>5953960</v>
       </c>
       <c r="H925" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
     </row>
     <row r="926">
       <c r="A926" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B926" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>6069205</v>
+        <v>6041898</v>
       </c>
       <c r="H926" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
     </row>
     <row r="927">
       <c r="A927" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B927" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>6135298</v>
+        <v>6069205</v>
       </c>
       <c r="H927" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
     </row>
     <row r="928">
       <c r="A928" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B928" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>6216528</v>
+        <v>6135298</v>
       </c>
       <c r="H928" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
     </row>
     <row r="929">
       <c r="A929" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B929" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>6275117</v>
+        <v>6216528</v>
       </c>
       <c r="H929" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
     </row>
     <row r="930">
       <c r="A930" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B930" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>6365690</v>
+        <v>6275117</v>
       </c>
       <c r="H930" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
     </row>
     <row r="931">
       <c r="A931" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B931" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>6464602</v>
+        <v>6365690</v>
       </c>
       <c r="H931" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
     </row>
     <row r="932">
       <c r="A932" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B932" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>6465016</v>
+        <v>6464602</v>
       </c>
       <c r="H932" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
     </row>
     <row r="933">
       <c r="A933" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B933" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>6511444</v>
+        <v>6465016</v>
       </c>
       <c r="H933" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
     </row>
     <row r="934">
       <c r="A934" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B934" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>6576464</v>
+        <v>6511444</v>
       </c>
       <c r="H934" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
     </row>
     <row r="935">
       <c r="A935" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B935" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>6623948</v>
+        <v>6576464</v>
       </c>
       <c r="H935" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
     </row>
     <row r="936">
       <c r="A936" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B936" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>6666287</v>
+        <v>6623948</v>
       </c>
       <c r="H936" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
     </row>
     <row r="937">
       <c r="A937" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B937" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>6703663</v>
+        <v>6666287</v>
       </c>
       <c r="H937" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
     </row>
     <row r="938">
       <c r="A938" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B938" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>6733209</v>
+        <v>6703663</v>
       </c>
       <c r="H938" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
     </row>
     <row r="939">
       <c r="A939" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B939" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>6774436</v>
+        <v>6733209</v>
       </c>
       <c r="H939" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
     </row>
     <row r="940">
       <c r="A940" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B940" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>6852705</v>
+        <v>6774436</v>
       </c>
       <c r="H940" t="inlineStr">
         <is>
@@ -48368,7 +48368,7 @@
     </row>
     <row r="941">
       <c r="A941" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B941" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>6923886</v>
+        <v>6852705</v>
       </c>
       <c r="H941" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
     </row>
     <row r="942">
       <c r="A942" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B942" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>7004223</v>
+        <v>6923886</v>
       </c>
       <c r="H942" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
     </row>
     <row r="943">
       <c r="A943" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B943" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>7137252</v>
+        <v>7004223</v>
       </c>
       <c r="H943" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B944" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>7130762</v>
+        <v>7137252</v>
       </c>
       <c r="H944" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B945" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>7157783</v>
+        <v>7130762</v>
       </c>
       <c r="H945" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
     </row>
     <row r="946">
       <c r="A946" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B946" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>7240557</v>
+        <v>7157783</v>
       </c>
       <c r="H946" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
     </row>
     <row r="947">
       <c r="A947" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B947" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>7259766</v>
+        <v>7240557</v>
       </c>
       <c r="H947" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
     </row>
     <row r="948">
       <c r="A948" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B948" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>7305306</v>
+        <v>7259766</v>
       </c>
       <c r="H948" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
     </row>
     <row r="949">
       <c r="A949" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B949" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>7353293</v>
+        <v>7305306</v>
       </c>
       <c r="H949" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
     </row>
     <row r="950">
       <c r="A950" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B950" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>7372243</v>
+        <v>7353293</v>
       </c>
       <c r="H950" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
     </row>
     <row r="951">
       <c r="A951" s="1" t="n">
-        <v>44469</v>
+        <v>46234</v>
       </c>
       <c r="B951" t="inlineStr">
         <is>
@@ -48886,34 +48886,34 @@
         </is>
       </c>
       <c r="C951" t="n">
-        <v>432</v>
+        <v>20539</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>R$ milhões</t>
         </is>
       </c>
       <c r="G951" t="n">
-        <v>6.25</v>
+        <v>7372243</v>
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Saldo da carteira de crédito - total.</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="J951" t="inlineStr">
@@ -48923,13 +48923,13 @@
       </c>
       <c r="K951" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B952" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="H952" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
     </row>
     <row r="953">
       <c r="A953" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B953" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
     </row>
     <row r="954">
       <c r="A954" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B954" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="H954" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
     </row>
     <row r="955">
       <c r="A955" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B955" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
     </row>
     <row r="956">
       <c r="A956" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B956" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>10.75</v>
+        <v>9.25</v>
       </c>
       <c r="H956" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
     </row>
     <row r="957">
       <c r="A957" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B957" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>11.75</v>
+        <v>10.75</v>
       </c>
       <c r="H957" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
     </row>
     <row r="958">
       <c r="A958" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B958" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
     </row>
     <row r="959">
       <c r="A959" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B959" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="H959" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
     </row>
     <row r="960">
       <c r="A960" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B960" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="H960" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
     </row>
     <row r="961">
       <c r="A961" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B961" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
     </row>
     <row r="962">
       <c r="A962" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B962" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>13.75</v>
+        <v>13.25</v>
       </c>
       <c r="H962" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
     </row>
     <row r="963">
       <c r="A963" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B963" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
     </row>
     <row r="964">
       <c r="A964" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B964" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
     </row>
     <row r="965">
       <c r="A965" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B965" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
     </row>
     <row r="966">
       <c r="A966" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B966" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
     </row>
     <row r="967">
       <c r="A967" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B967" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
     </row>
     <row r="968">
       <c r="A968" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B968" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
     </row>
     <row r="969">
       <c r="A969" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B969" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
     </row>
     <row r="970">
       <c r="A970" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B970" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
     </row>
     <row r="971">
       <c r="A971" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B971" t="inlineStr">
         <is>
@@ -49949,7 +49949,7 @@
     </row>
     <row r="972">
       <c r="A972" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B972" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
     </row>
     <row r="973">
       <c r="A973" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B973" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
     </row>
     <row r="974">
       <c r="A974" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B974" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="H974" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
     </row>
     <row r="975">
       <c r="A975" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B975" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="H975" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
     </row>
     <row r="976">
       <c r="A976" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B976" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
     </row>
     <row r="977">
       <c r="A977" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B977" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="H977" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
     </row>
     <row r="978">
       <c r="A978" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B978" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>11.75</v>
+        <v>12.25</v>
       </c>
       <c r="H978" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
     </row>
     <row r="979">
       <c r="A979" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B979" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
     </row>
     <row r="980">
       <c r="A980" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B980" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
       <c r="H980" t="inlineStr">
         <is>
@@ -50408,7 +50408,7 @@
     </row>
     <row r="981">
       <c r="A981" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B981" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
       <c r="H981" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
     </row>
     <row r="982">
       <c r="A982" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B982" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
     </row>
     <row r="983">
       <c r="A983" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B983" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="H983" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
     </row>
     <row r="984">
       <c r="A984" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B984" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
     </row>
     <row r="985">
       <c r="A985" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B985" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
     </row>
     <row r="986">
       <c r="A986" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B986" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
     </row>
     <row r="987">
       <c r="A987" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B987" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="H987" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
     </row>
     <row r="988">
       <c r="A988" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B988" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
     </row>
     <row r="989">
       <c r="A989" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B989" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>11.25</v>
+        <v>10.75</v>
       </c>
       <c r="H989" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
     </row>
     <row r="990">
       <c r="A990" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B990" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>12.25</v>
+        <v>11.25</v>
       </c>
       <c r="H990" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
     </row>
     <row r="991">
       <c r="A991" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B991" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>13.25</v>
+        <v>12.25</v>
       </c>
       <c r="H991" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
     </row>
     <row r="992">
       <c r="A992" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B992" t="inlineStr">
         <is>
@@ -51020,7 +51020,7 @@
     </row>
     <row r="993">
       <c r="A993" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B993" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>14.25</v>
+        <v>13.25</v>
       </c>
       <c r="H993" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
     </row>
     <row r="994">
       <c r="A994" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B994" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
     </row>
     <row r="995">
       <c r="A995" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B995" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>14.75</v>
+        <v>14.25</v>
       </c>
       <c r="H995" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
     </row>
     <row r="996">
       <c r="A996" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B996" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="H996" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
     </row>
     <row r="997">
       <c r="A997" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B997" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
     </row>
     <row r="998">
       <c r="A998" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B998" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
     </row>
     <row r="999">
       <c r="A999" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B999" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
     </row>
     <row r="1000">
       <c r="A1000" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
     </row>
     <row r="1001">
       <c r="A1001" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
     </row>
     <row r="1002">
       <c r="A1002" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
     </row>
     <row r="1003">
       <c r="A1003" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
     </row>
     <row r="1004">
       <c r="A1004" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
@@ -51632,7 +51632,7 @@
     </row>
     <row r="1005">
       <c r="A1005" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="H1005" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
     </row>
     <row r="1006">
       <c r="A1006" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
     </row>
     <row r="1007">
       <c r="A1007" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
     </row>
     <row r="1008">
       <c r="A1008" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
@@ -51811,7 +51811,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
     </row>
     <row r="1009">
       <c r="A1009" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
     </row>
     <row r="1010">
       <c r="A1010" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
     </row>
     <row r="1011">
       <c r="A1011" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
     </row>
     <row r="1012">
       <c r="A1012" s="1" t="n">
-        <v>44469</v>
+        <v>46295</v>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
@@ -51997,11 +51997,11 @@
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -52011,15 +52011,15 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>0.021256</v>
+        <v>14</v>
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -52034,13 +52034,13 @@
       </c>
       <c r="K1012" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>0.024244</v>
+        <v>0.021339</v>
       </c>
       <c r="H1013" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
     </row>
     <row r="1014">
       <c r="A1014" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>0.029256</v>
+        <v>0.024244</v>
       </c>
       <c r="H1014" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
     </row>
     <row r="1015">
       <c r="A1015" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>0.033316</v>
+        <v>0.029256</v>
       </c>
       <c r="H1015" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
     </row>
     <row r="1016">
       <c r="A1016" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.034749</v>
+        <v>0.033316</v>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
     </row>
     <row r="1017">
       <c r="A1017" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.039598</v>
+        <v>0.034749</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
     </row>
     <row r="1018">
       <c r="A1018" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
@@ -52321,7 +52321,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>0.041954</v>
+        <v>0.039598</v>
       </c>
       <c r="H1018" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
     </row>
     <row r="1019">
       <c r="A1019" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>0.043739</v>
+        <v>0.041954</v>
       </c>
       <c r="H1019" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
     </row>
     <row r="1020">
       <c r="A1020" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.046796</v>
+        <v>0.043739</v>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
     </row>
     <row r="1021">
       <c r="A1021" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
@@ -52474,7 +52474,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>0.048116</v>
+        <v>0.046796</v>
       </c>
       <c r="H1021" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
     </row>
     <row r="1022">
       <c r="A1022" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>0.049037</v>
+        <v>0.048116</v>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
     </row>
     <row r="1023">
       <c r="A1023" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
@@ -52576,7 +52576,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>0.05056</v>
+        <v>0.049037</v>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
     </row>
     <row r="1024">
       <c r="A1024" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>0.050788</v>
+        <v>0.05056</v>
       </c>
       <c r="H1024" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
     </row>
     <row r="1025">
       <c r="A1025" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
     </row>
     <row r="1026">
       <c r="A1026" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
     </row>
     <row r="1027">
       <c r="A1027" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
     </row>
     <row r="1028">
       <c r="A1028" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
     </row>
     <row r="1029">
       <c r="A1029" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
     </row>
     <row r="1030">
       <c r="A1030" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
     </row>
     <row r="1031">
       <c r="A1031" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
     </row>
     <row r="1032">
       <c r="A1032" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
     </row>
     <row r="1033">
       <c r="A1033" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
     </row>
     <row r="1034">
       <c r="A1034" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
     </row>
     <row r="1035">
       <c r="A1035" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>0.049189</v>
+        <v>0.050788</v>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
     </row>
     <row r="1036">
       <c r="A1036" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>0.048422</v>
+        <v>0.049189</v>
       </c>
       <c r="H1036" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
     </row>
     <row r="1037">
       <c r="A1037" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
@@ -53290,7 +53290,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>0.047279</v>
+        <v>0.048422</v>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
     </row>
     <row r="1038">
       <c r="A1038" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
@@ -53341,7 +53341,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>0.045601</v>
+        <v>0.047279</v>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
     </row>
     <row r="1039">
       <c r="A1039" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>0.044537</v>
+        <v>0.045601</v>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
     </row>
     <row r="1040">
       <c r="A1040" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>0.043739</v>
+        <v>0.044537</v>
       </c>
       <c r="H1040" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
     </row>
     <row r="1041">
       <c r="A1041" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>0.041957</v>
+        <v>0.043739</v>
       </c>
       <c r="H1041" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
     </row>
     <row r="1042">
       <c r="A1042" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>0.04142</v>
+        <v>0.041957</v>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
     </row>
     <row r="1043">
       <c r="A1043" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>0.040168</v>
+        <v>0.04142</v>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
     </row>
     <row r="1044">
       <c r="A1044" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>0.039484</v>
+        <v>0.040168</v>
       </c>
       <c r="H1044" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
     </row>
     <row r="1045">
       <c r="A1045" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
@@ -53698,7 +53698,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>0.03927</v>
+        <v>0.039484</v>
       </c>
       <c r="H1045" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
     </row>
     <row r="1046">
       <c r="A1046" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
     </row>
     <row r="1047">
       <c r="A1047" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
     </row>
     <row r="1048">
       <c r="A1048" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>0.039612</v>
+        <v>0.03927</v>
       </c>
       <c r="H1048" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
     </row>
     <row r="1049">
       <c r="A1049" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.040168</v>
+        <v>0.039612</v>
       </c>
       <c r="H1049" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
     </row>
     <row r="1050">
       <c r="A1050" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.04158</v>
+        <v>0.040168</v>
       </c>
       <c r="H1050" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
     </row>
     <row r="1051">
       <c r="A1051" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>0.044158</v>
+        <v>0.04158</v>
       </c>
       <c r="H1051" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
     </row>
     <row r="1052">
       <c r="A1052" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>0.045833</v>
+        <v>0.044158</v>
       </c>
       <c r="H1052" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
     </row>
     <row r="1053">
       <c r="A1053" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>0.049037</v>
+        <v>0.045833</v>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
     </row>
     <row r="1054">
       <c r="A1054" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>0.050508</v>
+        <v>0.049037</v>
       </c>
       <c r="H1054" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
     </row>
     <row r="1055">
       <c r="A1055" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>0.052531</v>
+        <v>0.050508</v>
       </c>
       <c r="H1055" t="inlineStr">
         <is>
@@ -54233,7 +54233,7 @@
     </row>
     <row r="1056">
       <c r="A1056" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>0.053936</v>
+        <v>0.052531</v>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
     </row>
     <row r="1057">
       <c r="A1057" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>0.054569</v>
+        <v>0.053936</v>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
     </row>
     <row r="1058">
       <c r="A1058" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>0.055131</v>
+        <v>0.054569</v>
       </c>
       <c r="H1058" t="inlineStr">
         <is>
@@ -54386,7 +54386,7 @@
     </row>
     <row r="1059">
       <c r="A1059" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
     </row>
     <row r="1060">
       <c r="A1060" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
     </row>
     <row r="1061">
       <c r="A1061" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
     </row>
     <row r="1062">
       <c r="A1062" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
     </row>
     <row r="1063">
       <c r="A1063" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
     </row>
     <row r="1064">
       <c r="A1064" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
     </row>
     <row r="1065">
       <c r="A1065" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
     </row>
     <row r="1066">
       <c r="A1066" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>0.054777</v>
+        <v>0.055131</v>
       </c>
       <c r="H1066" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
     </row>
     <row r="1067">
       <c r="A1067" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.054223</v>
+        <v>0.054777</v>
       </c>
       <c r="H1067" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
     </row>
     <row r="1068">
       <c r="A1068" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>0.0534</v>
+        <v>0.054223</v>
       </c>
       <c r="H1068" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
     </row>
     <row r="1069">
       <c r="A1069" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>0.053028</v>
+        <v>0.0534</v>
       </c>
       <c r="H1069" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
     </row>
     <row r="1070">
       <c r="A1070" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>0.052531</v>
+        <v>0.053028</v>
       </c>
       <c r="H1070" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
     </row>
     <row r="1071">
       <c r="A1071" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         </is>
       </c>
       <c r="G1071" t="n">
-        <v>0.051784</v>
+        <v>0.052531</v>
       </c>
       <c r="H1071" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
     </row>
     <row r="1072">
       <c r="A1072" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
@@ -55075,24 +55075,75 @@
         </is>
       </c>
       <c r="G1072" t="n">
+        <v>0.051784</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
         <v>0.05166</v>
       </c>
-      <c r="H1072" t="inlineStr">
+      <c r="H1073" t="inlineStr">
         <is>
           <t>Taxa Selic over.</t>
         </is>
       </c>
-      <c r="I1072" t="inlineStr">
+      <c r="I1073" t="inlineStr">
         <is>
           <t>diaria</t>
         </is>
       </c>
-      <c r="J1072" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1072" t="inlineStr">
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr">
         <is>
           <t>media</t>
         </is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.085</v>
+        <v>5.0973</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.0856</v>
+        <v>5.0979</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="H1013" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1073"/>
+  <dimension ref="A1:K1075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.0973</v>
+        <v>5.1143</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.0979</v>
+        <v>5.1149</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
     </row>
     <row r="597">
       <c r="A597" s="1" t="n">
-        <v>44469</v>
+        <v>46265</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -30832,11 +30832,11 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>433</v>
+        <v>188</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -30850,11 +30850,11 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>1.16</v>
+        <v>-0.32</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -30875,7 +30875,7 @@
     </row>
     <row r="598">
       <c r="A598" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="H598" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
     </row>
     <row r="599">
       <c r="A599" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
     </row>
     <row r="600">
       <c r="A600" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
     </row>
     <row r="601">
       <c r="A601" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H601" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
     </row>
     <row r="602">
       <c r="A602" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>1.01</v>
+        <v>0.54</v>
       </c>
       <c r="H602" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
     </row>
     <row r="603">
       <c r="A603" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
     </row>
     <row r="604">
       <c r="A604" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
     </row>
     <row r="605">
       <c r="A605" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>0.47</v>
+        <v>1.06</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
     </row>
     <row r="606">
       <c r="A606" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
     </row>
     <row r="607">
       <c r="A607" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>-0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H607" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
     </row>
     <row r="608">
       <c r="A608" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>-0.36</v>
+        <v>-0.68</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
     </row>
     <row r="609">
       <c r="A609" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
     </row>
     <row r="610">
       <c r="A610" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>0.59</v>
+        <v>-0.29</v>
       </c>
       <c r="H610" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
     </row>
     <row r="611">
       <c r="A611" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
       <c r="H611" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
     </row>
     <row r="612">
       <c r="A612" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
     </row>
     <row r="613">
       <c r="A613" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
     </row>
     <row r="614">
       <c r="A614" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>0.84</v>
+        <v>0.53</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
     </row>
     <row r="615">
       <c r="A615" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
     </row>
     <row r="616">
       <c r="A616" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H616" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
     </row>
     <row r="617">
       <c r="A617" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
     </row>
     <row r="618">
       <c r="A618" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>-0.08</v>
+        <v>0.23</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
     </row>
     <row r="619">
       <c r="A619" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="H619" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
     </row>
     <row r="620">
       <c r="A620" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
     </row>
     <row r="621">
       <c r="A621" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
     </row>
     <row r="622">
       <c r="A622" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
     </row>
     <row r="623">
       <c r="A623" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
     </row>
     <row r="624">
       <c r="A624" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
     </row>
     <row r="625">
       <c r="A625" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H625" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
     </row>
     <row r="626">
       <c r="A626" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
     </row>
     <row r="627">
       <c r="A627" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>0.16</v>
+        <v>0.83</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
     </row>
     <row r="628">
       <c r="A628" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="H628" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
     </row>
     <row r="629">
       <c r="A629" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
     </row>
     <row r="630">
       <c r="A630" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
     </row>
     <row r="631">
       <c r="A631" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
     </row>
     <row r="632">
       <c r="A632" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
     </row>
     <row r="633">
       <c r="A633" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>0.44</v>
+        <v>-0.02</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
     </row>
     <row r="634">
       <c r="A634" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
     </row>
     <row r="635">
       <c r="A635" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>0.39</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
     </row>
     <row r="636">
       <c r="A636" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
     </row>
     <row r="637">
       <c r="A637" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>0.16</v>
+        <v>0.52</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
     </row>
     <row r="638">
       <c r="A638" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>1.31</v>
+        <v>0.16</v>
       </c>
       <c r="H638" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
     </row>
     <row r="639">
       <c r="A639" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
     </row>
     <row r="640">
       <c r="A640" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
@@ -33068,7 +33068,7 @@
     </row>
     <row r="641">
       <c r="A641" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
     </row>
     <row r="642">
       <c r="A642" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
     </row>
     <row r="643">
       <c r="A643" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
     </row>
     <row r="644">
       <c r="A644" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>-0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
     </row>
     <row r="645">
       <c r="A645" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>0.48</v>
+        <v>-0.11</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
     </row>
     <row r="646">
       <c r="A646" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="H646" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
     </row>
     <row r="647">
       <c r="A647" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="H647" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
     </row>
     <row r="648">
       <c r="A648" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
     </row>
     <row r="649">
       <c r="A649" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
     </row>
     <row r="650">
       <c r="A650" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
     </row>
     <row r="651">
       <c r="A651" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
     </row>
     <row r="652">
       <c r="A652" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="H652" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
     </row>
     <row r="653">
       <c r="A653" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
     </row>
     <row r="654">
       <c r="A654" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>0.16</v>
+        <v>0.58</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
     </row>
     <row r="655">
       <c r="A655" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
     </row>
     <row r="656">
       <c r="A656" s="1" t="n">
-        <v>44469</v>
+        <v>46234</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -33841,29 +33841,29 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>20714</v>
+        <v>433</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.m.</t>
         </is>
       </c>
       <c r="G656" t="n">
-        <v>21.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Taxa média de juros das operações de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -33884,7 +33884,7 @@
     </row>
     <row r="657">
       <c r="A657" s="1" t="n">
-        <v>44500</v>
+        <v>46265</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -33892,29 +33892,29 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>20714</v>
+        <v>433</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>juros_credito_total</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.m.</t>
         </is>
       </c>
       <c r="G657" t="n">
-        <v>22.89</v>
+        <v>-0.32</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Taxa média de juros das operações de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -33935,7 +33935,7 @@
     </row>
     <row r="658">
       <c r="A658" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>23.91</v>
+        <v>21.42</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
     </row>
     <row r="659">
       <c r="A659" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>24.21</v>
+        <v>22.89</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
     </row>
     <row r="660">
       <c r="A660" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>25.23</v>
+        <v>23.91</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
     </row>
     <row r="661">
       <c r="A661" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         </is>
       </c>
       <c r="G661" t="n">
-        <v>25.63</v>
+        <v>24.21</v>
       </c>
       <c r="H661" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
     </row>
     <row r="662">
       <c r="A662" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>26.54</v>
+        <v>25.23</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
     </row>
     <row r="663">
       <c r="A663" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>27.46</v>
+        <v>25.63</v>
       </c>
       <c r="H663" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
     </row>
     <row r="664">
       <c r="A664" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>27.42</v>
+        <v>26.54</v>
       </c>
       <c r="H664" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
     </row>
     <row r="665">
       <c r="A665" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>27.88</v>
+        <v>27.46</v>
       </c>
       <c r="H665" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
     </row>
     <row r="666">
       <c r="A666" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>29.24</v>
+        <v>27.42</v>
       </c>
       <c r="H666" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
     </row>
     <row r="667">
       <c r="A667" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>28.6</v>
+        <v>27.88</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
     </row>
     <row r="668">
       <c r="A668" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>28.57</v>
+        <v>29.24</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
     </row>
     <row r="669">
       <c r="A669" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>29.68</v>
+        <v>28.6</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
     </row>
     <row r="670">
       <c r="A670" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>30.52</v>
+        <v>28.57</v>
       </c>
       <c r="H670" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         </is>
       </c>
       <c r="G671" t="n">
-        <v>29.64</v>
+        <v>29.68</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
     </row>
     <row r="672">
       <c r="A672" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>30.54</v>
+        <v>30.52</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
     </row>
     <row r="673">
       <c r="A673" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>30.48</v>
+        <v>29.64</v>
       </c>
       <c r="H673" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
     </row>
     <row r="674">
       <c r="A674" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>30.99</v>
+        <v>30.54</v>
       </c>
       <c r="H674" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
     </row>
     <row r="675">
       <c r="A675" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>31.62</v>
+        <v>30.48</v>
       </c>
       <c r="H675" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
     </row>
     <row r="676">
       <c r="A676" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         </is>
       </c>
       <c r="G676" t="n">
-        <v>31.63</v>
+        <v>30.99</v>
       </c>
       <c r="H676" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
     </row>
     <row r="677">
       <c r="A677" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         </is>
       </c>
       <c r="G677" t="n">
-        <v>30.85</v>
+        <v>31.62</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
     </row>
     <row r="678">
       <c r="A678" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>30.43</v>
+        <v>31.63</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
     </row>
     <row r="679">
       <c r="A679" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>29.92</v>
+        <v>30.85</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
     </row>
     <row r="680">
       <c r="A680" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>29.66</v>
+        <v>30.43</v>
       </c>
       <c r="H680" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
     </row>
     <row r="681">
       <c r="A681" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>29.24</v>
+        <v>29.92</v>
       </c>
       <c r="H681" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
     </row>
     <row r="682">
       <c r="A682" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         </is>
       </c>
       <c r="G682" t="n">
-        <v>29.01</v>
+        <v>29.66</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
     </row>
     <row r="683">
       <c r="A683" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         </is>
       </c>
       <c r="G683" t="n">
-        <v>28.14</v>
+        <v>29.24</v>
       </c>
       <c r="H683" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
     </row>
     <row r="684">
       <c r="A684" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         </is>
       </c>
       <c r="G684" t="n">
-        <v>28</v>
+        <v>29.01</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
     </row>
     <row r="685">
       <c r="A685" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>27.85</v>
+        <v>28.14</v>
       </c>
       <c r="H685" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
     </row>
     <row r="686">
       <c r="A686" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         </is>
       </c>
       <c r="G686" t="n">
-        <v>28.14</v>
+        <v>28</v>
       </c>
       <c r="H686" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
     </row>
     <row r="687">
       <c r="A687" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>27.86</v>
+        <v>27.85</v>
       </c>
       <c r="H687" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
     </row>
     <row r="688">
       <c r="A688" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         </is>
       </c>
       <c r="G688" t="n">
-        <v>27.75</v>
+        <v>28.14</v>
       </c>
       <c r="H688" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
     </row>
     <row r="689">
       <c r="A689" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         </is>
       </c>
       <c r="G689" t="n">
-        <v>27.81</v>
+        <v>27.86</v>
       </c>
       <c r="H689" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
     </row>
     <row r="690">
       <c r="A690" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         </is>
       </c>
       <c r="G690" t="n">
-        <v>27.74</v>
+        <v>27.75</v>
       </c>
       <c r="H690" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
     </row>
     <row r="691">
       <c r="A691" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="G691" t="n">
-        <v>27.59</v>
+        <v>27.81</v>
       </c>
       <c r="H691" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
     </row>
     <row r="692">
       <c r="A692" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="G692" t="n">
-        <v>27.49</v>
+        <v>27.74</v>
       </c>
       <c r="H692" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
     </row>
     <row r="693">
       <c r="A693" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         </is>
       </c>
       <c r="G693" t="n">
-        <v>27.94</v>
+        <v>27.59</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
     </row>
     <row r="694">
       <c r="A694" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         </is>
       </c>
       <c r="G694" t="n">
-        <v>28.45</v>
+        <v>27.49</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
     </row>
     <row r="695">
       <c r="A695" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         </is>
       </c>
       <c r="G695" t="n">
-        <v>28.5</v>
+        <v>27.94</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
     </row>
     <row r="696">
       <c r="A696" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         </is>
       </c>
       <c r="G696" t="n">
-        <v>29.88</v>
+        <v>28.45</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
     </row>
     <row r="697">
       <c r="A697" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         </is>
       </c>
       <c r="G697" t="n">
-        <v>30.53</v>
+        <v>28.5</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
     </row>
     <row r="698">
       <c r="A698" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="G698" t="n">
-        <v>31.34</v>
+        <v>29.88</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
     </row>
     <row r="699">
       <c r="A699" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         </is>
       </c>
       <c r="G699" t="n">
-        <v>31.63</v>
+        <v>30.53</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
     </row>
     <row r="700">
       <c r="A700" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         </is>
       </c>
       <c r="G700" t="n">
-        <v>31.7</v>
+        <v>31.34</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
     </row>
     <row r="701">
       <c r="A701" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         </is>
       </c>
       <c r="G701" t="n">
-        <v>31.85</v>
+        <v>31.63</v>
       </c>
       <c r="H701" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
     </row>
     <row r="702">
       <c r="A702" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         </is>
       </c>
       <c r="G702" t="n">
-        <v>31.75</v>
+        <v>31.7</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
     </row>
     <row r="703">
       <c r="A703" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         </is>
       </c>
       <c r="G703" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
     </row>
     <row r="704">
       <c r="A704" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         </is>
       </c>
       <c r="G704" t="n">
-        <v>31.47</v>
+        <v>31.75</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
     </row>
     <row r="705">
       <c r="A705" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         </is>
       </c>
       <c r="G705" t="n">
-        <v>32.04</v>
+        <v>31.87</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
     </row>
     <row r="706">
       <c r="A706" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         </is>
       </c>
       <c r="G706" t="n">
-        <v>32.2</v>
+        <v>31.47</v>
       </c>
       <c r="H706" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
     </row>
     <row r="707">
       <c r="A707" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         </is>
       </c>
       <c r="G707" t="n">
-        <v>31.87</v>
+        <v>32.04</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
     </row>
     <row r="708">
       <c r="A708" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         </is>
       </c>
       <c r="G708" t="n">
-        <v>32.45</v>
+        <v>32.2</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
     </row>
     <row r="709">
       <c r="A709" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         </is>
       </c>
       <c r="G709" t="n">
-        <v>32.63</v>
+        <v>31.87</v>
       </c>
       <c r="H709" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
     </row>
     <row r="710">
       <c r="A710" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         </is>
       </c>
       <c r="G710" t="n">
-        <v>32.84</v>
+        <v>32.45</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
     </row>
     <row r="711">
       <c r="A711" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         </is>
       </c>
       <c r="G711" t="n">
-        <v>33.36</v>
+        <v>32.63</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
     </row>
     <row r="712">
       <c r="A712" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         </is>
       </c>
       <c r="G712" t="n">
-        <v>33.1</v>
+        <v>32.84</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
     </row>
     <row r="713">
       <c r="A713" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         </is>
       </c>
       <c r="G713" t="n">
-        <v>33.33</v>
+        <v>33.36</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
     </row>
     <row r="714">
       <c r="A714" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         </is>
       </c>
       <c r="G714" t="n">
-        <v>32.08</v>
+        <v>33.1</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
     </row>
     <row r="715">
       <c r="A715" s="1" t="n">
-        <v>44469</v>
+        <v>46203</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
@@ -36850,34 +36850,34 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>3546</v>
+        <v>20714</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>US$ milhões</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G715" t="n">
-        <v>368886</v>
+        <v>33.33</v>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Reservas internacionais.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
@@ -36887,13 +36887,13 @@
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="1" t="n">
-        <v>44500</v>
+        <v>46234</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -36901,34 +36901,34 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>3546</v>
+        <v>20714</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>reservas_internacionais</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>US$ milhões</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G716" t="n">
-        <v>367927</v>
+        <v>32.08</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Reservas internacionais.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
@@ -36938,13 +36938,13 @@
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         </is>
       </c>
       <c r="G717" t="n">
-        <v>367772</v>
+        <v>368886</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
     </row>
     <row r="718">
       <c r="A718" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         </is>
       </c>
       <c r="G718" t="n">
-        <v>362204</v>
+        <v>367927</v>
       </c>
       <c r="H718" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
     </row>
     <row r="719">
       <c r="A719" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         </is>
       </c>
       <c r="G719" t="n">
-        <v>358398</v>
+        <v>367772</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
     </row>
     <row r="720">
       <c r="A720" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         </is>
       </c>
       <c r="G720" t="n">
-        <v>357740</v>
+        <v>362204</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
     </row>
     <row r="721">
       <c r="A721" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         </is>
       </c>
       <c r="G721" t="n">
-        <v>353169</v>
+        <v>358398</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
     </row>
     <row r="722">
       <c r="A722" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         </is>
       </c>
       <c r="G722" t="n">
-        <v>345097</v>
+        <v>357740</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
     </row>
     <row r="723">
       <c r="A723" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         </is>
       </c>
       <c r="G723" t="n">
-        <v>346415</v>
+        <v>353169</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
     </row>
     <row r="724">
       <c r="A724" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         </is>
       </c>
       <c r="G724" t="n">
-        <v>341958</v>
+        <v>345097</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
     </row>
     <row r="725">
       <c r="A725" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         </is>
       </c>
       <c r="G725" t="n">
-        <v>346403</v>
+        <v>346415</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
     </row>
     <row r="726">
       <c r="A726" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         </is>
       </c>
       <c r="G726" t="n">
-        <v>339664</v>
+        <v>341958</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
     </row>
     <row r="727">
       <c r="A727" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         </is>
       </c>
       <c r="G727" t="n">
-        <v>327580</v>
+        <v>346403</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
     </row>
     <row r="728">
       <c r="A728" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         </is>
       </c>
       <c r="G728" t="n">
-        <v>325546</v>
+        <v>339664</v>
       </c>
       <c r="H728" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
     </row>
     <row r="729">
       <c r="A729" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         </is>
       </c>
       <c r="G729" t="n">
-        <v>331505</v>
+        <v>327580</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
     </row>
     <row r="730">
       <c r="A730" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         </is>
       </c>
       <c r="G730" t="n">
-        <v>324703</v>
+        <v>325546</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
     </row>
     <row r="731">
       <c r="A731" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         </is>
       </c>
       <c r="G731" t="n">
-        <v>331122</v>
+        <v>331505</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
     </row>
     <row r="732">
       <c r="A732" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         </is>
       </c>
       <c r="G732" t="n">
-        <v>328098</v>
+        <v>324703</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
     </row>
     <row r="733">
       <c r="A733" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         </is>
       </c>
       <c r="G733" t="n">
-        <v>341158</v>
+        <v>331122</v>
       </c>
       <c r="H733" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
     </row>
     <row r="734">
       <c r="A734" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         </is>
       </c>
       <c r="G734" t="n">
-        <v>345725</v>
+        <v>328098</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
     </row>
     <row r="735">
       <c r="A735" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         </is>
       </c>
       <c r="G735" t="n">
-        <v>343489</v>
+        <v>341158</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
     </row>
     <row r="736">
       <c r="A736" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         </is>
       </c>
       <c r="G736" t="n">
-        <v>343620</v>
+        <v>345725</v>
       </c>
       <c r="H736" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
     </row>
     <row r="737">
       <c r="A737" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         </is>
       </c>
       <c r="G737" t="n">
-        <v>345476</v>
+        <v>343489</v>
       </c>
       <c r="H737" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
     </row>
     <row r="738">
       <c r="A738" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         </is>
       </c>
       <c r="G738" t="n">
-        <v>344177</v>
+        <v>343620</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
     </row>
     <row r="739">
       <c r="A739" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="G739" t="n">
-        <v>340324</v>
+        <v>345476</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
     </row>
     <row r="740">
       <c r="A740" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         </is>
       </c>
       <c r="G740" t="n">
-        <v>340247</v>
+        <v>344177</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
     </row>
     <row r="741">
       <c r="A741" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         </is>
       </c>
       <c r="G741" t="n">
-        <v>348406</v>
+        <v>340324</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
     </row>
     <row r="742">
       <c r="A742" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         </is>
       </c>
       <c r="G742" t="n">
-        <v>355034</v>
+        <v>340247</v>
       </c>
       <c r="H742" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
     </row>
     <row r="743">
       <c r="A743" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         </is>
       </c>
       <c r="G743" t="n">
-        <v>355066</v>
+        <v>348406</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
     </row>
     <row r="744">
       <c r="A744" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         </is>
       </c>
       <c r="G744" t="n">
-        <v>352705</v>
+        <v>355034</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
     </row>
     <row r="745">
       <c r="A745" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         </is>
       </c>
       <c r="G745" t="n">
-        <v>355008</v>
+        <v>355066</v>
       </c>
       <c r="H745" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
     </row>
     <row r="746">
       <c r="A746" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         </is>
       </c>
       <c r="G746" t="n">
-        <v>351599</v>
+        <v>352705</v>
       </c>
       <c r="H746" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
     </row>
     <row r="747">
       <c r="A747" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         </is>
       </c>
       <c r="G747" t="n">
-        <v>355560</v>
+        <v>355008</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
     </row>
     <row r="748">
       <c r="A748" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         </is>
       </c>
       <c r="G748" t="n">
-        <v>357827</v>
+        <v>351599</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
     </row>
     <row r="749">
       <c r="A749" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         </is>
       </c>
       <c r="G749" t="n">
-        <v>363282</v>
+        <v>355560</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
     </row>
     <row r="750">
       <c r="A750" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         </is>
       </c>
       <c r="G750" t="n">
-        <v>369214</v>
+        <v>357827</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
     </row>
     <row r="751">
       <c r="A751" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         </is>
       </c>
       <c r="G751" t="n">
-        <v>372016</v>
+        <v>363282</v>
       </c>
       <c r="H751" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
     </row>
     <row r="752">
       <c r="A752" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="G752" t="n">
-        <v>366096</v>
+        <v>369214</v>
       </c>
       <c r="H752" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
     </row>
     <row r="753">
       <c r="A753" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         </is>
       </c>
       <c r="G753" t="n">
-        <v>363003</v>
+        <v>372016</v>
       </c>
       <c r="H753" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
     </row>
     <row r="754">
       <c r="A754" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         </is>
       </c>
       <c r="G754" t="n">
-        <v>329730</v>
+        <v>366096</v>
       </c>
       <c r="H754" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
     </row>
     <row r="755">
       <c r="A755" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>328303</v>
+        <v>363003</v>
       </c>
       <c r="H755" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
     </row>
     <row r="756">
       <c r="A756" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         </is>
       </c>
       <c r="G756" t="n">
-        <v>332508</v>
+        <v>329730</v>
       </c>
       <c r="H756" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
     </row>
     <row r="757">
       <c r="A757" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="G757" t="n">
-        <v>336157</v>
+        <v>328303</v>
       </c>
       <c r="H757" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
     </row>
     <row r="758">
       <c r="A758" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         </is>
       </c>
       <c r="G758" t="n">
-        <v>340789</v>
+        <v>332508</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
     </row>
     <row r="759">
       <c r="A759" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>341459</v>
+        <v>336157</v>
       </c>
       <c r="H759" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
     </row>
     <row r="760">
       <c r="A760" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>344440</v>
+        <v>340789</v>
       </c>
       <c r="H760" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
     </row>
     <row r="761">
       <c r="A761" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         </is>
       </c>
       <c r="G761" t="n">
-        <v>345111</v>
+        <v>341459</v>
       </c>
       <c r="H761" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
     </row>
     <row r="762">
       <c r="A762" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         </is>
       </c>
       <c r="G762" t="n">
-        <v>350767</v>
+        <v>344440</v>
       </c>
       <c r="H762" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
     </row>
     <row r="763">
       <c r="A763" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>356582</v>
+        <v>345111</v>
       </c>
       <c r="H763" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
     </row>
     <row r="764">
       <c r="A764" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>357103</v>
+        <v>350767</v>
       </c>
       <c r="H764" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
     </row>
     <row r="765">
       <c r="A765" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>360578</v>
+        <v>356582</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
     </row>
     <row r="766">
       <c r="A766" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>358234</v>
+        <v>357103</v>
       </c>
       <c r="H766" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
     </row>
     <row r="767">
       <c r="A767" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>364367</v>
+        <v>360578</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
     </row>
     <row r="768">
       <c r="A768" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         </is>
       </c>
       <c r="G768" t="n">
-        <v>371074</v>
+        <v>358234</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
     </row>
     <row r="769">
       <c r="A769" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
@@ -39622,7 +39622,7 @@
         </is>
       </c>
       <c r="G769" t="n">
-        <v>362002</v>
+        <v>364367</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
     </row>
     <row r="770">
       <c r="A770" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         </is>
       </c>
       <c r="G770" t="n">
-        <v>366913</v>
+        <v>371074</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
     </row>
     <row r="771">
       <c r="A771" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         </is>
       </c>
       <c r="G771" t="n">
-        <v>371137</v>
+        <v>362002</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
     </row>
     <row r="772">
       <c r="A772" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         </is>
       </c>
       <c r="G772" t="n">
-        <v>367558</v>
+        <v>366913</v>
       </c>
       <c r="H772" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
     </row>
     <row r="773">
       <c r="A773" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         </is>
       </c>
       <c r="G773" t="n">
-        <v>369742</v>
+        <v>371137</v>
       </c>
       <c r="H773" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
     </row>
     <row r="774">
       <c r="A774" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         </is>
       </c>
       <c r="G774" t="n">
-        <v>372616</v>
+        <v>367558</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
     </row>
     <row r="775">
       <c r="A775" s="1" t="n">
-        <v>44469</v>
+        <v>46234</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -39910,34 +39910,34 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>20541</v>
+        <v>3546</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>R$ milhões</t>
+          <t>US$ milhões</t>
         </is>
       </c>
       <c r="G775" t="n">
-        <v>2546936</v>
+        <v>369742</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas físicas.</t>
+          <t>Reservas internacionais.</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -39947,13 +39947,13 @@
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" s="1" t="n">
-        <v>44500</v>
+        <v>46265</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -39961,34 +39961,34 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>20541</v>
+        <v>3546</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>R$ milhões</t>
+          <t>US$ milhões</t>
         </is>
       </c>
       <c r="G776" t="n">
-        <v>2601017</v>
+        <v>372616</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas físicas.</t>
+          <t>Reservas internacionais.</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
@@ -39998,13 +39998,13 @@
       </c>
       <c r="K776" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         </is>
       </c>
       <c r="G777" t="n">
-        <v>2664395</v>
+        <v>2546936</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
     </row>
     <row r="778">
       <c r="A778" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         </is>
       </c>
       <c r="G778" t="n">
-        <v>2708461</v>
+        <v>2601017</v>
       </c>
       <c r="H778" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
     </row>
     <row r="779">
       <c r="A779" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         </is>
       </c>
       <c r="G779" t="n">
-        <v>2735096</v>
+        <v>2664395</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
     </row>
     <row r="780">
       <c r="A780" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         </is>
       </c>
       <c r="G780" t="n">
-        <v>2756295</v>
+        <v>2708461</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
     </row>
     <row r="781">
       <c r="A781" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         </is>
       </c>
       <c r="G781" t="n">
-        <v>2800464</v>
+        <v>2735096</v>
       </c>
       <c r="H781" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
     </row>
     <row r="782">
       <c r="A782" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         </is>
       </c>
       <c r="G782" t="n">
-        <v>2830420</v>
+        <v>2756295</v>
       </c>
       <c r="H782" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         </is>
       </c>
       <c r="G783" t="n">
-        <v>2875671</v>
+        <v>2800464</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         </is>
       </c>
       <c r="G784" t="n">
-        <v>2913035</v>
+        <v>2830420</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         </is>
       </c>
       <c r="G785" t="n">
-        <v>2952207</v>
+        <v>2875671</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         </is>
       </c>
       <c r="G786" t="n">
-        <v>3008528</v>
+        <v>2913035</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         </is>
       </c>
       <c r="G787" t="n">
-        <v>3054969</v>
+        <v>2952207</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         </is>
       </c>
       <c r="G788" t="n">
-        <v>3110134</v>
+        <v>3008528</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>3155345</v>
+        <v>3054969</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         </is>
       </c>
       <c r="G790" t="n">
-        <v>3187833</v>
+        <v>3110134</v>
       </c>
       <c r="H790" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         </is>
       </c>
       <c r="G791" t="n">
-        <v>3221831</v>
+        <v>3155345</v>
       </c>
       <c r="H791" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         </is>
       </c>
       <c r="G792" t="n">
-        <v>3234845</v>
+        <v>3187833</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         </is>
       </c>
       <c r="G793" t="n">
-        <v>3269910</v>
+        <v>3221831</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="G794" t="n">
-        <v>3281308</v>
+        <v>3234845</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
     </row>
     <row r="795">
       <c r="A795" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         </is>
       </c>
       <c r="G795" t="n">
-        <v>3308178</v>
+        <v>3269910</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
     </row>
     <row r="796">
       <c r="A796" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         </is>
       </c>
       <c r="G796" t="n">
-        <v>3309846</v>
+        <v>3281308</v>
       </c>
       <c r="H796" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
     </row>
     <row r="797">
       <c r="A797" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         </is>
       </c>
       <c r="G797" t="n">
-        <v>3331330</v>
+        <v>3308178</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
     </row>
     <row r="798">
       <c r="A798" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         </is>
       </c>
       <c r="G798" t="n">
-        <v>3386405</v>
+        <v>3309846</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
     </row>
     <row r="799">
       <c r="A799" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         </is>
       </c>
       <c r="G799" t="n">
-        <v>3410769</v>
+        <v>3331330</v>
       </c>
       <c r="H799" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
     </row>
     <row r="800">
       <c r="A800" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="G800" t="n">
-        <v>3449000</v>
+        <v>3386405</v>
       </c>
       <c r="H800" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>3490337</v>
+        <v>3410769</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3521672</v>
+        <v>3449000</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3560345</v>
+        <v>3490337</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3580652</v>
+        <v>3521672</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         </is>
       </c>
       <c r="G805" t="n">
-        <v>3613967</v>
+        <v>3560345</v>
       </c>
       <c r="H805" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         </is>
       </c>
       <c r="G806" t="n">
-        <v>3646659</v>
+        <v>3580652</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         </is>
       </c>
       <c r="G807" t="n">
-        <v>3675652</v>
+        <v>3613967</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         </is>
       </c>
       <c r="G808" t="n">
-        <v>3705041</v>
+        <v>3646659</v>
       </c>
       <c r="H808" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         </is>
       </c>
       <c r="G809" t="n">
-        <v>3745844</v>
+        <v>3675652</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         </is>
       </c>
       <c r="G810" t="n">
-        <v>3790900</v>
+        <v>3705041</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="G811" t="n">
-        <v>3831700</v>
+        <v>3745844</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         </is>
       </c>
       <c r="G812" t="n">
-        <v>3877584</v>
+        <v>3790900</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="G813" t="n">
-        <v>3929668</v>
+        <v>3831700</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         </is>
       </c>
       <c r="G814" t="n">
-        <v>3965425</v>
+        <v>3877584</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         </is>
       </c>
       <c r="G815" t="n">
-        <v>4013059</v>
+        <v>3929668</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         </is>
       </c>
       <c r="G816" t="n">
-        <v>4034293</v>
+        <v>3965425</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         </is>
       </c>
       <c r="G817" t="n">
-        <v>4078202</v>
+        <v>4013059</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         </is>
       </c>
       <c r="G818" t="n">
-        <v>4111522</v>
+        <v>4034293</v>
       </c>
       <c r="H818" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
     </row>
     <row r="819">
       <c r="A819" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         </is>
       </c>
       <c r="G819" t="n">
-        <v>4133579</v>
+        <v>4078202</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
     </row>
     <row r="820">
       <c r="A820" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         </is>
       </c>
       <c r="G820" t="n">
-        <v>4155970</v>
+        <v>4111522</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
     </row>
     <row r="821">
       <c r="A821" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         </is>
       </c>
       <c r="G821" t="n">
-        <v>4188808</v>
+        <v>4133579</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
     </row>
     <row r="822">
       <c r="A822" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         </is>
       </c>
       <c r="G822" t="n">
-        <v>4228171</v>
+        <v>4155970</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
     </row>
     <row r="823">
       <c r="A823" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         </is>
       </c>
       <c r="G823" t="n">
-        <v>4262888</v>
+        <v>4188808</v>
       </c>
       <c r="H823" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
     </row>
     <row r="824">
       <c r="A824" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         </is>
       </c>
       <c r="G824" t="n">
-        <v>4326256</v>
+        <v>4228171</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
     </row>
     <row r="825">
       <c r="A825" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         </is>
       </c>
       <c r="G825" t="n">
-        <v>4387321</v>
+        <v>4262888</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
     </row>
     <row r="826">
       <c r="A826" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="G826" t="n">
-        <v>4435517</v>
+        <v>4326256</v>
       </c>
       <c r="H826" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
     </row>
     <row r="827">
       <c r="A827" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         </is>
       </c>
       <c r="G827" t="n">
-        <v>4476542</v>
+        <v>4387321</v>
       </c>
       <c r="H827" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
     </row>
     <row r="828">
       <c r="A828" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         </is>
       </c>
       <c r="G828" t="n">
-        <v>4501299</v>
+        <v>4435517</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>4553022</v>
+        <v>4476542</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
     </row>
     <row r="830">
       <c r="A830" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>4574368</v>
+        <v>4501299</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
     </row>
     <row r="831">
       <c r="A831" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>4597152</v>
+        <v>4553022</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
     </row>
     <row r="832">
       <c r="A832" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>4602668</v>
+        <v>4574368</v>
       </c>
       <c r="H832" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
     </row>
     <row r="833">
       <c r="A833" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         </is>
       </c>
       <c r="G833" t="n">
-        <v>4640730</v>
+        <v>4597152</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
     </row>
     <row r="834">
       <c r="A834" s="1" t="n">
-        <v>44469</v>
+        <v>46203</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -42919,11 +42919,11 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>20540</v>
+        <v>20541</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -42937,11 +42937,11 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>1894119</v>
+        <v>4602668</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
+          <t>Saldo da carteira de crédito - pessoas físicas.</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -42962,7 +42962,7 @@
     </row>
     <row r="835">
       <c r="A835" s="1" t="n">
-        <v>44500</v>
+        <v>46234</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -42970,11 +42970,11 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>20540</v>
+        <v>20541</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -42988,11 +42988,11 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1910940</v>
+        <v>4640730</v>
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
+          <t>Saldo da carteira de crédito - pessoas físicas.</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -43013,7 +43013,7 @@
     </row>
     <row r="836">
       <c r="A836" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>1933111</v>
+        <v>1894119</v>
       </c>
       <c r="H836" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
     </row>
     <row r="837">
       <c r="A837" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="G837" t="n">
-        <v>1974391</v>
+        <v>1910940</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
     </row>
     <row r="838">
       <c r="A838" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         </is>
       </c>
       <c r="G838" t="n">
-        <v>1947035</v>
+        <v>1933111</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>1971524</v>
+        <v>1974391</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         </is>
       </c>
       <c r="G840" t="n">
-        <v>1994119</v>
+        <v>1947035</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
     </row>
     <row r="841">
       <c r="A841" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>2003312</v>
+        <v>1971524</v>
       </c>
       <c r="H841" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     </row>
     <row r="842">
       <c r="A842" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>2013726</v>
+        <v>1994119</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
     </row>
     <row r="843">
       <c r="A843" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>2052569</v>
+        <v>2003312</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
     </row>
     <row r="844">
       <c r="A844" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         </is>
       </c>
       <c r="G844" t="n">
-        <v>2047038</v>
+        <v>2013726</v>
       </c>
       <c r="H844" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
     </row>
     <row r="845">
       <c r="A845" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         </is>
       </c>
       <c r="G845" t="n">
-        <v>2064183</v>
+        <v>2052569</v>
       </c>
       <c r="H845" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
     </row>
     <row r="846">
       <c r="A846" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         </is>
       </c>
       <c r="G846" t="n">
-        <v>2109806</v>
+        <v>2047038</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
     </row>
     <row r="847">
       <c r="A847" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>2105856</v>
+        <v>2064183</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
     </row>
     <row r="848">
       <c r="A848" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>2130312</v>
+        <v>2109806</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
     </row>
     <row r="849">
       <c r="A849" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>2178236</v>
+        <v>2105856</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
     </row>
     <row r="850">
       <c r="A850" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>2151399</v>
+        <v>2130312</v>
       </c>
       <c r="H850" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
     </row>
     <row r="851">
       <c r="A851" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>2136105</v>
+        <v>2178236</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
     </row>
     <row r="852">
       <c r="A852" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>2154900</v>
+        <v>2151399</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         </is>
       </c>
       <c r="G853" t="n">
-        <v>2145000</v>
+        <v>2136105</v>
       </c>
       <c r="H853" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
     </row>
     <row r="854">
       <c r="A854" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>2145530</v>
+        <v>2154900</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>2169613</v>
+        <v>2145000</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>2153541</v>
+        <v>2145530</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
     </row>
     <row r="857">
       <c r="A857" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>2172658</v>
+        <v>2169613</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
     </row>
     <row r="858">
       <c r="A858" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>2215175</v>
+        <v>2153541</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
     </row>
     <row r="859">
       <c r="A859" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>2204808</v>
+        <v>2172658</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
     </row>
     <row r="860">
       <c r="A860" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>2220766</v>
+        <v>2215175</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
     </row>
     <row r="861">
       <c r="A861" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="G861" t="n">
-        <v>2283485</v>
+        <v>2204808</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
     </row>
     <row r="862">
       <c r="A862" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2234362</v>
+        <v>2220766</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
     </row>
     <row r="863">
       <c r="A863" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>2235302</v>
+        <v>2283485</v>
       </c>
       <c r="H863" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
     </row>
     <row r="864">
       <c r="A864" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>2285775</v>
+        <v>2234362</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
     </row>
     <row r="865">
       <c r="A865" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>2268879</v>
+        <v>2235302</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
     </row>
     <row r="866">
       <c r="A866" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>2278309</v>
+        <v>2285775</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
     </row>
     <row r="867">
       <c r="A867" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>2336858</v>
+        <v>2268879</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
     </row>
     <row r="868">
       <c r="A868" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2323362</v>
+        <v>2278309</v>
       </c>
       <c r="H868" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
     </row>
     <row r="869">
       <c r="A869" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2344397</v>
+        <v>2336858</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
     </row>
     <row r="870">
       <c r="A870" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2384828</v>
+        <v>2323362</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
     </row>
     <row r="871">
       <c r="A871" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2397533</v>
+        <v>2344397</v>
       </c>
       <c r="H871" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
     </row>
     <row r="872">
       <c r="A872" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2436022</v>
+        <v>2384828</v>
       </c>
       <c r="H872" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
     </row>
     <row r="873">
       <c r="A873" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2499177</v>
+        <v>2397533</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
     </row>
     <row r="874">
       <c r="A874" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B874" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2451957</v>
+        <v>2436022</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B875" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2477151</v>
+        <v>2499177</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
     </row>
     <row r="876">
       <c r="A876" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B876" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2498262</v>
+        <v>2451957</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
     </row>
     <row r="877">
       <c r="A877" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B877" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2512426</v>
+        <v>2477151</v>
       </c>
       <c r="H877" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
     </row>
     <row r="878">
       <c r="A878" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B878" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>2532708</v>
+        <v>2498262</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
     </row>
     <row r="879">
       <c r="A879" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B879" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2547693</v>
+        <v>2512426</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
     </row>
     <row r="880">
       <c r="A880" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B880" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>2544400</v>
+        <v>2532708</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
     </row>
     <row r="881">
       <c r="A881" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B881" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2546265</v>
+        <v>2547693</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
     </row>
     <row r="882">
       <c r="A882" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B882" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>2589817</v>
+        <v>2544400</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
     </row>
     <row r="883">
       <c r="A883" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B883" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>2597630</v>
+        <v>2546265</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
     </row>
     <row r="884">
       <c r="A884" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B884" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>2616902</v>
+        <v>2589817</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
     </row>
     <row r="885">
       <c r="A885" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B885" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>2701735</v>
+        <v>2597630</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
     </row>
     <row r="886">
       <c r="A886" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B886" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>2654220</v>
+        <v>2616902</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
     </row>
     <row r="887">
       <c r="A887" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B887" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>2656484</v>
+        <v>2701735</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
     </row>
     <row r="888">
       <c r="A888" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B888" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>2687535</v>
+        <v>2654220</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
     </row>
     <row r="889">
       <c r="A889" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B889" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>2685397</v>
+        <v>2656484</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
     </row>
     <row r="890">
       <c r="A890" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B890" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>2708154</v>
+        <v>2687535</v>
       </c>
       <c r="H890" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
     </row>
     <row r="891">
       <c r="A891" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B891" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         </is>
       </c>
       <c r="G891" t="n">
-        <v>2750625</v>
+        <v>2685397</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
     </row>
     <row r="892">
       <c r="A892" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B892" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>2731513</v>
+        <v>2708154</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
     </row>
     <row r="893">
       <c r="A893" s="1" t="n">
-        <v>44469</v>
+        <v>46203</v>
       </c>
       <c r="B893" t="inlineStr">
         <is>
@@ -45928,11 +45928,11 @@
         </is>
       </c>
       <c r="C893" t="n">
-        <v>20539</v>
+        <v>20540</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -45946,11 +45946,11 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>4441056</v>
+        <v>2750625</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - total.</t>
+          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -45971,7 +45971,7 @@
     </row>
     <row r="894">
       <c r="A894" s="1" t="n">
-        <v>44500</v>
+        <v>46234</v>
       </c>
       <c r="B894" t="inlineStr">
         <is>
@@ -45979,11 +45979,11 @@
         </is>
       </c>
       <c r="C894" t="n">
-        <v>20539</v>
+        <v>20540</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -45997,11 +45997,11 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>4511956</v>
+        <v>2731513</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - total.</t>
+          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -46022,7 +46022,7 @@
     </row>
     <row r="895">
       <c r="A895" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B895" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>4597507</v>
+        <v>4441056</v>
       </c>
       <c r="H895" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
     </row>
     <row r="896">
       <c r="A896" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B896" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>4682852</v>
+        <v>4511956</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
     </row>
     <row r="897">
       <c r="A897" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B897" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>4682131</v>
+        <v>4597507</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
     </row>
     <row r="898">
       <c r="A898" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B898" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>4727818</v>
+        <v>4682852</v>
       </c>
       <c r="H898" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
     </row>
     <row r="899">
       <c r="A899" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B899" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>4794583</v>
+        <v>4682131</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
     </row>
     <row r="900">
       <c r="A900" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B900" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>4833732</v>
+        <v>4727818</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
     </row>
     <row r="901">
       <c r="A901" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B901" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>4889397</v>
+        <v>4794583</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
     </row>
     <row r="902">
       <c r="A902" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B902" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>4965603</v>
+        <v>4833732</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
     </row>
     <row r="903">
       <c r="A903" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B903" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>4999244</v>
+        <v>4889397</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
     </row>
     <row r="904">
       <c r="A904" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B904" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>5072711</v>
+        <v>4965603</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
     </row>
     <row r="905">
       <c r="A905" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B905" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>5164775</v>
+        <v>4999244</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
     </row>
     <row r="906">
       <c r="A906" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B906" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>5215990</v>
+        <v>5072711</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
     </row>
     <row r="907">
       <c r="A907" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B907" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>5285657</v>
+        <v>5164775</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
     </row>
     <row r="908">
       <c r="A908" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B908" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>5366069</v>
+        <v>5215990</v>
       </c>
       <c r="H908" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
     </row>
     <row r="909">
       <c r="A909" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B909" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>5373231</v>
+        <v>5285657</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
     </row>
     <row r="910">
       <c r="A910" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B910" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>5370950</v>
+        <v>5366069</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
     </row>
     <row r="911">
       <c r="A911" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B911" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>5424811</v>
+        <v>5373231</v>
       </c>
       <c r="H911" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
     </row>
     <row r="912">
       <c r="A912" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B912" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>5426307</v>
+        <v>5370950</v>
       </c>
       <c r="H912" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
     </row>
     <row r="913">
       <c r="A913" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B913" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>5453708</v>
+        <v>5424811</v>
       </c>
       <c r="H913" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
     </row>
     <row r="914">
       <c r="A914" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B914" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>5479459</v>
+        <v>5426307</v>
       </c>
       <c r="H914" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
     </row>
     <row r="915">
       <c r="A915" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B915" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>5484871</v>
+        <v>5453708</v>
       </c>
       <c r="H915" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
     </row>
     <row r="916">
       <c r="A916" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B916" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>5559063</v>
+        <v>5479459</v>
       </c>
       <c r="H916" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
     </row>
     <row r="917">
       <c r="A917" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B917" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>5625945</v>
+        <v>5484871</v>
       </c>
       <c r="H917" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
     </row>
     <row r="918">
       <c r="A918" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B918" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>5653808</v>
+        <v>5559063</v>
       </c>
       <c r="H918" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
     </row>
     <row r="919">
       <c r="A919" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B919" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>5711103</v>
+        <v>5625945</v>
       </c>
       <c r="H919" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
     </row>
     <row r="920">
       <c r="A920" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B920" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>5805157</v>
+        <v>5653808</v>
       </c>
       <c r="H920" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
     </row>
     <row r="921">
       <c r="A921" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B921" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>5794707</v>
+        <v>5711103</v>
       </c>
       <c r="H921" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
     </row>
     <row r="922">
       <c r="A922" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B922" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>5815954</v>
+        <v>5805157</v>
       </c>
       <c r="H922" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
     </row>
     <row r="923">
       <c r="A923" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B923" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>5899742</v>
+        <v>5794707</v>
       </c>
       <c r="H923" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
     </row>
     <row r="924">
       <c r="A924" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B924" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>5915538</v>
+        <v>5815954</v>
       </c>
       <c r="H924" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
     </row>
     <row r="925">
       <c r="A925" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B925" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>5953960</v>
+        <v>5899742</v>
       </c>
       <c r="H925" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
     </row>
     <row r="926">
       <c r="A926" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B926" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>6041898</v>
+        <v>5915538</v>
       </c>
       <c r="H926" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
     </row>
     <row r="927">
       <c r="A927" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B927" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>6069205</v>
+        <v>5953960</v>
       </c>
       <c r="H927" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
     </row>
     <row r="928">
       <c r="A928" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B928" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>6135298</v>
+        <v>6041898</v>
       </c>
       <c r="H928" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
     </row>
     <row r="929">
       <c r="A929" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B929" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>6216528</v>
+        <v>6069205</v>
       </c>
       <c r="H929" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
     </row>
     <row r="930">
       <c r="A930" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B930" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>6275117</v>
+        <v>6135298</v>
       </c>
       <c r="H930" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
     </row>
     <row r="931">
       <c r="A931" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B931" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>6365690</v>
+        <v>6216528</v>
       </c>
       <c r="H931" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
     </row>
     <row r="932">
       <c r="A932" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B932" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>6464602</v>
+        <v>6275117</v>
       </c>
       <c r="H932" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
     </row>
     <row r="933">
       <c r="A933" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B933" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>6465016</v>
+        <v>6365690</v>
       </c>
       <c r="H933" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
     </row>
     <row r="934">
       <c r="A934" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B934" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>6511444</v>
+        <v>6464602</v>
       </c>
       <c r="H934" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
     </row>
     <row r="935">
       <c r="A935" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B935" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>6576464</v>
+        <v>6465016</v>
       </c>
       <c r="H935" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
     </row>
     <row r="936">
       <c r="A936" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B936" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>6623948</v>
+        <v>6511444</v>
       </c>
       <c r="H936" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
     </row>
     <row r="937">
       <c r="A937" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B937" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>6666287</v>
+        <v>6576464</v>
       </c>
       <c r="H937" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
     </row>
     <row r="938">
       <c r="A938" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B938" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>6703663</v>
+        <v>6623948</v>
       </c>
       <c r="H938" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
     </row>
     <row r="939">
       <c r="A939" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B939" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>6733209</v>
+        <v>6666287</v>
       </c>
       <c r="H939" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
     </row>
     <row r="940">
       <c r="A940" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B940" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>6774436</v>
+        <v>6703663</v>
       </c>
       <c r="H940" t="inlineStr">
         <is>
@@ -48368,7 +48368,7 @@
     </row>
     <row r="941">
       <c r="A941" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B941" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>6852705</v>
+        <v>6733209</v>
       </c>
       <c r="H941" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
     </row>
     <row r="942">
       <c r="A942" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B942" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>6923886</v>
+        <v>6774436</v>
       </c>
       <c r="H942" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
     </row>
     <row r="943">
       <c r="A943" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B943" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>7004223</v>
+        <v>6852705</v>
       </c>
       <c r="H943" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B944" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>7137252</v>
+        <v>6923886</v>
       </c>
       <c r="H944" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B945" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>7130762</v>
+        <v>7004223</v>
       </c>
       <c r="H945" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
     </row>
     <row r="946">
       <c r="A946" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B946" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>7157783</v>
+        <v>7137252</v>
       </c>
       <c r="H946" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
     </row>
     <row r="947">
       <c r="A947" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B947" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>7240557</v>
+        <v>7130762</v>
       </c>
       <c r="H947" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
     </row>
     <row r="948">
       <c r="A948" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B948" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>7259766</v>
+        <v>7157783</v>
       </c>
       <c r="H948" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
     </row>
     <row r="949">
       <c r="A949" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B949" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>7305306</v>
+        <v>7240557</v>
       </c>
       <c r="H949" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
     </row>
     <row r="950">
       <c r="A950" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B950" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>7353293</v>
+        <v>7259766</v>
       </c>
       <c r="H950" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
     </row>
     <row r="951">
       <c r="A951" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B951" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>7372243</v>
+        <v>7305306</v>
       </c>
       <c r="H951" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
     </row>
     <row r="952">
       <c r="A952" s="1" t="n">
-        <v>44469</v>
+        <v>46203</v>
       </c>
       <c r="B952" t="inlineStr">
         <is>
@@ -48937,34 +48937,34 @@
         </is>
       </c>
       <c r="C952" t="n">
-        <v>432</v>
+        <v>20539</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>R$ milhões</t>
         </is>
       </c>
       <c r="G952" t="n">
-        <v>6.25</v>
+        <v>7353293</v>
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Saldo da carteira de crédito - total.</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="J952" t="inlineStr">
@@ -48974,13 +48974,13 @@
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" s="1" t="n">
-        <v>44500</v>
+        <v>46234</v>
       </c>
       <c r="B953" t="inlineStr">
         <is>
@@ -48988,34 +48988,34 @@
         </is>
       </c>
       <c r="C953" t="n">
-        <v>432</v>
+        <v>20539</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>R$ milhões</t>
         </is>
       </c>
       <c r="G953" t="n">
-        <v>7.75</v>
+        <v>7372243</v>
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Saldo da carteira de crédito - total.</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="J953" t="inlineStr">
@@ -49025,13 +49025,13 @@
       </c>
       <c r="K953" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B954" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         </is>
       </c>
       <c r="G954" t="n">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="H954" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
     </row>
     <row r="955">
       <c r="A955" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B955" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="H955" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
     </row>
     <row r="956">
       <c r="A956" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B956" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>9.25</v>
+        <v>7.75</v>
       </c>
       <c r="H956" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
     </row>
     <row r="957">
       <c r="A957" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B957" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>10.75</v>
+        <v>9.25</v>
       </c>
       <c r="H957" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
     </row>
     <row r="958">
       <c r="A958" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B958" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>11.75</v>
+        <v>9.25</v>
       </c>
       <c r="H958" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
     </row>
     <row r="959">
       <c r="A959" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B959" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>11.75</v>
+        <v>10.75</v>
       </c>
       <c r="H959" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
     </row>
     <row r="960">
       <c r="A960" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B960" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="H960" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
     </row>
     <row r="961">
       <c r="A961" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B961" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>13.25</v>
+        <v>11.75</v>
       </c>
       <c r="H961" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
     </row>
     <row r="962">
       <c r="A962" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B962" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="H962" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
     </row>
     <row r="963">
       <c r="A963" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B963" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         </is>
       </c>
       <c r="G963" t="n">
-        <v>13.75</v>
+        <v>13.25</v>
       </c>
       <c r="H963" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
     </row>
     <row r="964">
       <c r="A964" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B964" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         </is>
       </c>
       <c r="G964" t="n">
-        <v>13.75</v>
+        <v>13.25</v>
       </c>
       <c r="H964" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
     </row>
     <row r="965">
       <c r="A965" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B965" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
     </row>
     <row r="966">
       <c r="A966" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B966" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
     </row>
     <row r="967">
       <c r="A967" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B967" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
     </row>
     <row r="968">
       <c r="A968" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B968" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
     </row>
     <row r="969">
       <c r="A969" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B969" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
     </row>
     <row r="970">
       <c r="A970" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B970" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
     </row>
     <row r="971">
       <c r="A971" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B971" t="inlineStr">
         <is>
@@ -49949,7 +49949,7 @@
     </row>
     <row r="972">
       <c r="A972" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B972" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
     </row>
     <row r="973">
       <c r="A973" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B973" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
     </row>
     <row r="974">
       <c r="A974" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B974" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
     </row>
     <row r="975">
       <c r="A975" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B975" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="H975" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
     </row>
     <row r="976">
       <c r="A976" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B976" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="H976" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
     </row>
     <row r="977">
       <c r="A977" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B977" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="H977" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
     </row>
     <row r="978">
       <c r="A978" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B978" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="H978" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
     </row>
     <row r="979">
       <c r="A979" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B979" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="H979" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
     </row>
     <row r="980">
       <c r="A980" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B980" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>11.75</v>
+        <v>12.25</v>
       </c>
       <c r="H980" t="inlineStr">
         <is>
@@ -50408,7 +50408,7 @@
     </row>
     <row r="981">
       <c r="A981" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B981" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
       <c r="H981" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
     </row>
     <row r="982">
       <c r="A982" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B982" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>10.75</v>
+        <v>11.75</v>
       </c>
       <c r="H982" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
     </row>
     <row r="983">
       <c r="A983" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B983" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
       <c r="H983" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
     </row>
     <row r="984">
       <c r="A984" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B984" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="H984" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
     </row>
     <row r="985">
       <c r="A985" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B985" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="H985" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
     </row>
     <row r="986">
       <c r="A986" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B986" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
     </row>
     <row r="987">
       <c r="A987" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B987" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
     </row>
     <row r="988">
       <c r="A988" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B988" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="H988" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
     </row>
     <row r="989">
       <c r="A989" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B989" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="H989" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
     </row>
     <row r="990">
       <c r="A990" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B990" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>11.25</v>
+        <v>10.75</v>
       </c>
       <c r="H990" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
     </row>
     <row r="991">
       <c r="A991" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B991" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>12.25</v>
+        <v>10.75</v>
       </c>
       <c r="H991" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
     </row>
     <row r="992">
       <c r="A992" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B992" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>13.25</v>
+        <v>11.25</v>
       </c>
       <c r="H992" t="inlineStr">
         <is>
@@ -51020,7 +51020,7 @@
     </row>
     <row r="993">
       <c r="A993" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B993" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>13.25</v>
+        <v>12.25</v>
       </c>
       <c r="H993" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
     </row>
     <row r="994">
       <c r="A994" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B994" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         </is>
       </c>
       <c r="G994" t="n">
-        <v>14.25</v>
+        <v>13.25</v>
       </c>
       <c r="H994" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
     </row>
     <row r="995">
       <c r="A995" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B995" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>14.25</v>
+        <v>13.25</v>
       </c>
       <c r="H995" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
     </row>
     <row r="996">
       <c r="A996" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B996" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>14.75</v>
+        <v>14.25</v>
       </c>
       <c r="H996" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
     </row>
     <row r="997">
       <c r="A997" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B997" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>15</v>
+        <v>14.25</v>
       </c>
       <c r="H997" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
     </row>
     <row r="998">
       <c r="A998" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B998" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="H998" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
     </row>
     <row r="999">
       <c r="A999" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B999" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
     </row>
     <row r="1000">
       <c r="A1000" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
     </row>
     <row r="1001">
       <c r="A1001" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
     </row>
     <row r="1002">
       <c r="A1002" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
     </row>
     <row r="1003">
       <c r="A1003" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
     </row>
     <row r="1004">
       <c r="A1004" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
@@ -51632,7 +51632,7 @@
     </row>
     <row r="1005">
       <c r="A1005" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
     </row>
     <row r="1006">
       <c r="A1006" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
     </row>
     <row r="1007">
       <c r="A1007" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
     </row>
     <row r="1008">
       <c r="A1008" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
@@ -51811,7 +51811,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
     </row>
     <row r="1009">
       <c r="A1009" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="H1009" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
     </row>
     <row r="1010">
       <c r="A1010" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
     </row>
     <row r="1011">
       <c r="A1011" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="H1011" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
     </row>
     <row r="1012">
       <c r="A1012" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="H1012" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
     </row>
     <row r="1013">
       <c r="A1013" s="1" t="n">
-        <v>44469</v>
+        <v>46265</v>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
@@ -52048,11 +52048,11 @@
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
@@ -52062,15 +52062,15 @@
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>0.021433</v>
+        <v>14</v>
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
@@ -52085,13 +52085,13 @@
       </c>
       <c r="K1013" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" s="1" t="n">
-        <v>44500</v>
+        <v>46295</v>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
@@ -52099,11 +52099,11 @@
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
@@ -52113,15 +52113,15 @@
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>0.024244</v>
+        <v>14</v>
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -52136,13 +52136,13 @@
       </c>
       <c r="K1014" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" s="1" t="n">
-        <v>44530</v>
+        <v>44469</v>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>0.029256</v>
+        <v>0.02154</v>
       </c>
       <c r="H1015" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
     </row>
     <row r="1016">
       <c r="A1016" s="1" t="n">
-        <v>44561</v>
+        <v>44500</v>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.033316</v>
+        <v>0.024244</v>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
     </row>
     <row r="1017">
       <c r="A1017" s="1" t="n">
-        <v>44592</v>
+        <v>44530</v>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.034749</v>
+        <v>0.029256</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
     </row>
     <row r="1018">
       <c r="A1018" s="1" t="n">
-        <v>44620</v>
+        <v>44561</v>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
@@ -52321,7 +52321,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>0.039598</v>
+        <v>0.033316</v>
       </c>
       <c r="H1018" t="inlineStr">
         <is>
@@ -52346,7 +52346,7 @@
     </row>
     <row r="1019">
       <c r="A1019" s="1" t="n">
-        <v>44651</v>
+        <v>44592</v>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>0.041954</v>
+        <v>0.034749</v>
       </c>
       <c r="H1019" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
     </row>
     <row r="1020">
       <c r="A1020" s="1" t="n">
-        <v>44681</v>
+        <v>44620</v>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.043739</v>
+        <v>0.039598</v>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
     </row>
     <row r="1021">
       <c r="A1021" s="1" t="n">
-        <v>44712</v>
+        <v>44651</v>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
@@ -52474,7 +52474,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>0.046796</v>
+        <v>0.041954</v>
       </c>
       <c r="H1021" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
     </row>
     <row r="1022">
       <c r="A1022" s="1" t="n">
-        <v>44742</v>
+        <v>44681</v>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>0.048116</v>
+        <v>0.043739</v>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
     </row>
     <row r="1023">
       <c r="A1023" s="1" t="n">
-        <v>44773</v>
+        <v>44712</v>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
@@ -52576,7 +52576,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>0.049037</v>
+        <v>0.046796</v>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
     </row>
     <row r="1024">
       <c r="A1024" s="1" t="n">
-        <v>44804</v>
+        <v>44742</v>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>0.05056</v>
+        <v>0.048116</v>
       </c>
       <c r="H1024" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
     </row>
     <row r="1025">
       <c r="A1025" s="1" t="n">
-        <v>44834</v>
+        <v>44773</v>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>0.050788</v>
+        <v>0.049037</v>
       </c>
       <c r="H1025" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
     </row>
     <row r="1026">
       <c r="A1026" s="1" t="n">
-        <v>44865</v>
+        <v>44804</v>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>0.050788</v>
+        <v>0.05056</v>
       </c>
       <c r="H1026" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
     </row>
     <row r="1027">
       <c r="A1027" s="1" t="n">
-        <v>44895</v>
+        <v>44834</v>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
     </row>
     <row r="1028">
       <c r="A1028" s="1" t="n">
-        <v>44926</v>
+        <v>44865</v>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
     </row>
     <row r="1029">
       <c r="A1029" s="1" t="n">
-        <v>44957</v>
+        <v>44895</v>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
     </row>
     <row r="1030">
       <c r="A1030" s="1" t="n">
-        <v>44985</v>
+        <v>44926</v>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
     </row>
     <row r="1031">
       <c r="A1031" s="1" t="n">
-        <v>45016</v>
+        <v>44957</v>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
     </row>
     <row r="1032">
       <c r="A1032" s="1" t="n">
-        <v>45046</v>
+        <v>44985</v>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
     </row>
     <row r="1033">
       <c r="A1033" s="1" t="n">
-        <v>45077</v>
+        <v>45016</v>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
     </row>
     <row r="1034">
       <c r="A1034" s="1" t="n">
-        <v>45107</v>
+        <v>45046</v>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
     </row>
     <row r="1035">
       <c r="A1035" s="1" t="n">
-        <v>45138</v>
+        <v>45077</v>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
     </row>
     <row r="1036">
       <c r="A1036" s="1" t="n">
-        <v>45169</v>
+        <v>45107</v>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>0.049189</v>
+        <v>0.050788</v>
       </c>
       <c r="H1036" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
     </row>
     <row r="1037">
       <c r="A1037" s="1" t="n">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
@@ -53290,7 +53290,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>0.048422</v>
+        <v>0.050788</v>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
     </row>
     <row r="1038">
       <c r="A1038" s="1" t="n">
-        <v>45230</v>
+        <v>45169</v>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
@@ -53341,7 +53341,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>0.047279</v>
+        <v>0.049189</v>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
     </row>
     <row r="1039">
       <c r="A1039" s="1" t="n">
-        <v>45260</v>
+        <v>45199</v>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>0.045601</v>
+        <v>0.048422</v>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
     </row>
     <row r="1040">
       <c r="A1040" s="1" t="n">
-        <v>45291</v>
+        <v>45230</v>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>0.044537</v>
+        <v>0.047279</v>
       </c>
       <c r="H1040" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
     </row>
     <row r="1041">
       <c r="A1041" s="1" t="n">
-        <v>45322</v>
+        <v>45260</v>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>0.043739</v>
+        <v>0.045601</v>
       </c>
       <c r="H1041" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
     </row>
     <row r="1042">
       <c r="A1042" s="1" t="n">
-        <v>45351</v>
+        <v>45291</v>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>0.041957</v>
+        <v>0.044537</v>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
     </row>
     <row r="1043">
       <c r="A1043" s="1" t="n">
-        <v>45382</v>
+        <v>45322</v>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>0.04142</v>
+        <v>0.043739</v>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
     </row>
     <row r="1044">
       <c r="A1044" s="1" t="n">
-        <v>45412</v>
+        <v>45351</v>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>0.040168</v>
+        <v>0.041957</v>
       </c>
       <c r="H1044" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
     </row>
     <row r="1045">
       <c r="A1045" s="1" t="n">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
@@ -53698,7 +53698,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>0.039484</v>
+        <v>0.04142</v>
       </c>
       <c r="H1045" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
     </row>
     <row r="1046">
       <c r="A1046" s="1" t="n">
-        <v>45473</v>
+        <v>45412</v>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>0.03927</v>
+        <v>0.040168</v>
       </c>
       <c r="H1046" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
     </row>
     <row r="1047">
       <c r="A1047" s="1" t="n">
-        <v>45504</v>
+        <v>45443</v>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>0.03927</v>
+        <v>0.039484</v>
       </c>
       <c r="H1047" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
     </row>
     <row r="1048">
       <c r="A1048" s="1" t="n">
-        <v>45535</v>
+        <v>45473</v>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
     </row>
     <row r="1049">
       <c r="A1049" s="1" t="n">
-        <v>45565</v>
+        <v>45504</v>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.039612</v>
+        <v>0.03927</v>
       </c>
       <c r="H1049" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
     </row>
     <row r="1050">
       <c r="A1050" s="1" t="n">
-        <v>45596</v>
+        <v>45535</v>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.040168</v>
+        <v>0.03927</v>
       </c>
       <c r="H1050" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
     </row>
     <row r="1051">
       <c r="A1051" s="1" t="n">
-        <v>45626</v>
+        <v>45565</v>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>0.04158</v>
+        <v>0.039612</v>
       </c>
       <c r="H1051" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
     </row>
     <row r="1052">
       <c r="A1052" s="1" t="n">
-        <v>45657</v>
+        <v>45596</v>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>0.044158</v>
+        <v>0.040168</v>
       </c>
       <c r="H1052" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
     </row>
     <row r="1053">
       <c r="A1053" s="1" t="n">
-        <v>45688</v>
+        <v>45626</v>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>0.045833</v>
+        <v>0.04158</v>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
     </row>
     <row r="1054">
       <c r="A1054" s="1" t="n">
-        <v>45716</v>
+        <v>45657</v>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>0.049037</v>
+        <v>0.044158</v>
       </c>
       <c r="H1054" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
     </row>
     <row r="1055">
       <c r="A1055" s="1" t="n">
-        <v>45747</v>
+        <v>45688</v>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>0.050508</v>
+        <v>0.045833</v>
       </c>
       <c r="H1055" t="inlineStr">
         <is>
@@ -54233,7 +54233,7 @@
     </row>
     <row r="1056">
       <c r="A1056" s="1" t="n">
-        <v>45777</v>
+        <v>45716</v>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>0.052531</v>
+        <v>0.049037</v>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
     </row>
     <row r="1057">
       <c r="A1057" s="1" t="n">
-        <v>45808</v>
+        <v>45747</v>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>0.053936</v>
+        <v>0.050508</v>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
     </row>
     <row r="1058">
       <c r="A1058" s="1" t="n">
-        <v>45838</v>
+        <v>45777</v>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>0.054569</v>
+        <v>0.052531</v>
       </c>
       <c r="H1058" t="inlineStr">
         <is>
@@ -54386,7 +54386,7 @@
     </row>
     <row r="1059">
       <c r="A1059" s="1" t="n">
-        <v>45869</v>
+        <v>45808</v>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>0.055131</v>
+        <v>0.053936</v>
       </c>
       <c r="H1059" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
     </row>
     <row r="1060">
       <c r="A1060" s="1" t="n">
-        <v>45900</v>
+        <v>45838</v>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
@@ -54463,7 +54463,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>0.055131</v>
+        <v>0.054569</v>
       </c>
       <c r="H1060" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
     </row>
     <row r="1061">
       <c r="A1061" s="1" t="n">
-        <v>45930</v>
+        <v>45869</v>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
     </row>
     <row r="1062">
       <c r="A1062" s="1" t="n">
-        <v>45961</v>
+        <v>45900</v>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
     </row>
     <row r="1063">
       <c r="A1063" s="1" t="n">
-        <v>45991</v>
+        <v>45930</v>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
     </row>
     <row r="1064">
       <c r="A1064" s="1" t="n">
-        <v>46022</v>
+        <v>45961</v>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
     </row>
     <row r="1065">
       <c r="A1065" s="1" t="n">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
     </row>
     <row r="1066">
       <c r="A1066" s="1" t="n">
-        <v>46081</v>
+        <v>46022</v>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
     </row>
     <row r="1067">
       <c r="A1067" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.054777</v>
+        <v>0.055131</v>
       </c>
       <c r="H1067" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
     </row>
     <row r="1068">
       <c r="A1068" s="1" t="n">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>0.054223</v>
+        <v>0.055131</v>
       </c>
       <c r="H1068" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
     </row>
     <row r="1069">
       <c r="A1069" s="1" t="n">
-        <v>46173</v>
+        <v>46112</v>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>0.0534</v>
+        <v>0.054777</v>
       </c>
       <c r="H1069" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
     </row>
     <row r="1070">
       <c r="A1070" s="1" t="n">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>0.053028</v>
+        <v>0.054223</v>
       </c>
       <c r="H1070" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
     </row>
     <row r="1071">
       <c r="A1071" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         </is>
       </c>
       <c r="G1071" t="n">
-        <v>0.052531</v>
+        <v>0.0534</v>
       </c>
       <c r="H1071" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
     </row>
     <row r="1072">
       <c r="A1072" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>0.051784</v>
+        <v>0.053028</v>
       </c>
       <c r="H1072" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
     </row>
     <row r="1073">
       <c r="A1073" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
@@ -55126,24 +55126,126 @@
         </is>
       </c>
       <c r="G1073" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1074" t="n">
+        <v>0.051784</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1075" t="n">
         <v>0.05166</v>
       </c>
-      <c r="H1073" t="inlineStr">
+      <c r="H1075" t="inlineStr">
         <is>
           <t>Taxa Selic over.</t>
         </is>
       </c>
-      <c r="I1073" t="inlineStr">
+      <c r="I1075" t="inlineStr">
         <is>
           <t>diaria</t>
         </is>
       </c>
-      <c r="J1073" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1073" t="inlineStr">
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1075" t="inlineStr">
         <is>
           <t>media</t>
         </is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.0912</v>
+        <v>5.169</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.0918</v>
+        <v>5.1696</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="H1015" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.1484</v>
+        <v>5.152</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.149</v>
+        <v>5.1527</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.1155</v>
+        <v>5.1408</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.1161</v>
+        <v>5.1414</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="H1077" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.1408</v>
+        <v>5.1789</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.1414</v>
+        <v>5.1795</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="H1077" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1085"/>
+  <dimension ref="A1:K1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.2132</v>
+        <v>5.2204</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -49549,11 +49549,11 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -49563,15 +49563,15 @@
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G964" t="n">
-        <v>6.25</v>
+        <v>0.023687</v>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -49586,7 +49586,7 @@
       </c>
       <c r="K964" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49600,11 +49600,11 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -49614,15 +49614,15 @@
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G965" t="n">
-        <v>7.75</v>
+        <v>0.024244</v>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -49637,7 +49637,7 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49651,11 +49651,11 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -49665,15 +49665,15 @@
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G966" t="n">
-        <v>7.75</v>
+        <v>0.029256</v>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
@@ -49688,7 +49688,7 @@
       </c>
       <c r="K966" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49702,11 +49702,11 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -49716,15 +49716,15 @@
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G967" t="n">
-        <v>9.25</v>
+        <v>0.033316</v>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -49739,7 +49739,7 @@
       </c>
       <c r="K967" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49753,11 +49753,11 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
@@ -49767,15 +49767,15 @@
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G968" t="n">
-        <v>9.25</v>
+        <v>0.034749</v>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I968" t="inlineStr">
@@ -49790,7 +49790,7 @@
       </c>
       <c r="K968" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49804,11 +49804,11 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -49818,15 +49818,15 @@
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G969" t="n">
-        <v>10.75</v>
+        <v>0.039598</v>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
@@ -49841,7 +49841,7 @@
       </c>
       <c r="K969" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49855,11 +49855,11 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -49869,15 +49869,15 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G970" t="n">
-        <v>11.75</v>
+        <v>0.041954</v>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
@@ -49892,7 +49892,7 @@
       </c>
       <c r="K970" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49906,11 +49906,11 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -49920,15 +49920,15 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G971" t="n">
-        <v>11.75</v>
+        <v>0.043739</v>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
@@ -49943,7 +49943,7 @@
       </c>
       <c r="K971" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -49957,11 +49957,11 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
@@ -49971,15 +49971,15 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G972" t="n">
-        <v>12.75</v>
+        <v>0.046796</v>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -49994,7 +49994,7 @@
       </c>
       <c r="K972" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50008,11 +50008,11 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
@@ -50022,15 +50022,15 @@
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G973" t="n">
-        <v>13.25</v>
+        <v>0.048116</v>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
@@ -50045,7 +50045,7 @@
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50059,11 +50059,11 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -50073,15 +50073,15 @@
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G974" t="n">
-        <v>13.25</v>
+        <v>0.049037</v>
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
@@ -50096,7 +50096,7 @@
       </c>
       <c r="K974" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50110,11 +50110,11 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -50124,15 +50124,15 @@
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G975" t="n">
-        <v>13.75</v>
+        <v>0.05056</v>
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50161,11 +50161,11 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -50175,15 +50175,15 @@
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G976" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
@@ -50198,7 +50198,7 @@
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50212,11 +50212,11 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -50226,15 +50226,15 @@
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G977" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
@@ -50249,7 +50249,7 @@
       </c>
       <c r="K977" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50263,11 +50263,11 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -50277,15 +50277,15 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G978" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -50300,7 +50300,7 @@
       </c>
       <c r="K978" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50314,11 +50314,11 @@
         </is>
       </c>
       <c r="C979" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -50328,15 +50328,15 @@
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G979" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
@@ -50351,7 +50351,7 @@
       </c>
       <c r="K979" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50365,11 +50365,11 @@
         </is>
       </c>
       <c r="C980" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
@@ -50379,15 +50379,15 @@
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G980" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
@@ -50402,7 +50402,7 @@
       </c>
       <c r="K980" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50416,11 +50416,11 @@
         </is>
       </c>
       <c r="C981" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
@@ -50430,15 +50430,15 @@
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G981" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
@@ -50453,7 +50453,7 @@
       </c>
       <c r="K981" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50467,11 +50467,11 @@
         </is>
       </c>
       <c r="C982" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
@@ -50481,15 +50481,15 @@
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G982" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
@@ -50504,7 +50504,7 @@
       </c>
       <c r="K982" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50518,11 +50518,11 @@
         </is>
       </c>
       <c r="C983" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
@@ -50532,15 +50532,15 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G983" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
@@ -50555,7 +50555,7 @@
       </c>
       <c r="K983" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50569,11 +50569,11 @@
         </is>
       </c>
       <c r="C984" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
@@ -50583,15 +50583,15 @@
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G984" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -50606,7 +50606,7 @@
       </c>
       <c r="K984" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50620,11 +50620,11 @@
         </is>
       </c>
       <c r="C985" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -50634,15 +50634,15 @@
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G985" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -50657,7 +50657,7 @@
       </c>
       <c r="K985" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50671,11 +50671,11 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -50685,15 +50685,15 @@
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G986" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -50708,7 +50708,7 @@
       </c>
       <c r="K986" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50722,11 +50722,11 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
@@ -50736,15 +50736,15 @@
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G987" t="n">
-        <v>13.25</v>
+        <v>0.049189</v>
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
@@ -50759,7 +50759,7 @@
       </c>
       <c r="K987" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50773,11 +50773,11 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
@@ -50787,15 +50787,15 @@
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G988" t="n">
-        <v>12.75</v>
+        <v>0.048422</v>
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
@@ -50810,7 +50810,7 @@
       </c>
       <c r="K988" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50824,11 +50824,11 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -50838,15 +50838,15 @@
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G989" t="n">
-        <v>12.75</v>
+        <v>0.047279</v>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
@@ -50861,7 +50861,7 @@
       </c>
       <c r="K989" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50875,11 +50875,11 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
@@ -50889,15 +50889,15 @@
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G990" t="n">
-        <v>12.25</v>
+        <v>0.045601</v>
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
@@ -50912,7 +50912,7 @@
       </c>
       <c r="K990" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50926,11 +50926,11 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
@@ -50940,15 +50940,15 @@
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G991" t="n">
-        <v>11.75</v>
+        <v>0.044537</v>
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
@@ -50963,7 +50963,7 @@
       </c>
       <c r="K991" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -50977,11 +50977,11 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
@@ -50991,15 +50991,15 @@
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G992" t="n">
-        <v>11.75</v>
+        <v>0.043739</v>
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -51014,7 +51014,7 @@
       </c>
       <c r="K992" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51028,11 +51028,11 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -51042,15 +51042,15 @@
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G993" t="n">
-        <v>11.25</v>
+        <v>0.041957</v>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
@@ -51065,7 +51065,7 @@
       </c>
       <c r="K993" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51079,11 +51079,11 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
@@ -51093,15 +51093,15 @@
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G994" t="n">
-        <v>10.75</v>
+        <v>0.04142</v>
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I994" t="inlineStr">
@@ -51116,7 +51116,7 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51130,11 +51130,11 @@
         </is>
       </c>
       <c r="C995" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
@@ -51144,15 +51144,15 @@
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G995" t="n">
-        <v>10.75</v>
+        <v>0.040168</v>
       </c>
       <c r="H995" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I995" t="inlineStr">
@@ -51167,7 +51167,7 @@
       </c>
       <c r="K995" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51181,11 +51181,11 @@
         </is>
       </c>
       <c r="C996" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
@@ -51195,15 +51195,15 @@
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G996" t="n">
-        <v>10.5</v>
+        <v>0.039484</v>
       </c>
       <c r="H996" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I996" t="inlineStr">
@@ -51218,7 +51218,7 @@
       </c>
       <c r="K996" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51232,11 +51232,11 @@
         </is>
       </c>
       <c r="C997" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
@@ -51246,15 +51246,15 @@
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G997" t="n">
-        <v>10.5</v>
+        <v>0.03927</v>
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="K997" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51283,11 +51283,11 @@
         </is>
       </c>
       <c r="C998" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -51297,15 +51297,15 @@
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G998" t="n">
-        <v>10.5</v>
+        <v>0.03927</v>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -51320,7 +51320,7 @@
       </c>
       <c r="K998" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51334,11 +51334,11 @@
         </is>
       </c>
       <c r="C999" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -51348,15 +51348,15 @@
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G999" t="n">
-        <v>10.5</v>
+        <v>0.03927</v>
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -51371,7 +51371,7 @@
       </c>
       <c r="K999" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51385,11 +51385,11 @@
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -51399,15 +51399,15 @@
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>10.75</v>
+        <v>0.039612</v>
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -51422,7 +51422,7 @@
       </c>
       <c r="K1000" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51436,11 +51436,11 @@
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -51450,15 +51450,15 @@
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>10.75</v>
+        <v>0.040168</v>
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
@@ -51473,7 +51473,7 @@
       </c>
       <c r="K1001" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51487,11 +51487,11 @@
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -51501,15 +51501,15 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>11.25</v>
+        <v>0.04158</v>
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -51524,7 +51524,7 @@
       </c>
       <c r="K1002" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51538,11 +51538,11 @@
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -51552,15 +51552,15 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>12.25</v>
+        <v>0.044158</v>
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -51575,7 +51575,7 @@
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51589,11 +51589,11 @@
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -51603,15 +51603,15 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>13.25</v>
+        <v>0.045833</v>
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -51626,7 +51626,7 @@
       </c>
       <c r="K1004" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51640,11 +51640,11 @@
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -51654,15 +51654,15 @@
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>13.25</v>
+        <v>0.049037</v>
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -51677,7 +51677,7 @@
       </c>
       <c r="K1005" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51691,11 +51691,11 @@
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -51705,15 +51705,15 @@
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>14.25</v>
+        <v>0.050508</v>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -51728,7 +51728,7 @@
       </c>
       <c r="K1006" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51742,11 +51742,11 @@
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -51756,15 +51756,15 @@
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>14.25</v>
+        <v>0.052531</v>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -51779,7 +51779,7 @@
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51793,11 +51793,11 @@
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -51807,15 +51807,15 @@
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>14.75</v>
+        <v>0.053936</v>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
@@ -51830,7 +51830,7 @@
       </c>
       <c r="K1008" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51844,11 +51844,11 @@
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -51858,15 +51858,15 @@
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>15</v>
+        <v>0.054569</v>
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
@@ -51881,7 +51881,7 @@
       </c>
       <c r="K1009" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51895,11 +51895,11 @@
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
@@ -51909,15 +51909,15 @@
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
@@ -51932,7 +51932,7 @@
       </c>
       <c r="K1010" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51946,11 +51946,11 @@
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
@@ -51960,15 +51960,15 @@
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
@@ -51983,7 +51983,7 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -51997,11 +51997,11 @@
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -52011,15 +52011,15 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -52034,7 +52034,7 @@
       </c>
       <c r="K1012" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52048,11 +52048,11 @@
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
@@ -52062,15 +52062,15 @@
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
@@ -52085,7 +52085,7 @@
       </c>
       <c r="K1013" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52099,11 +52099,11 @@
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
@@ -52113,15 +52113,15 @@
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="K1014" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52150,11 +52150,11 @@
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
@@ -52164,15 +52164,15 @@
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="K1015" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52201,11 +52201,11 @@
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -52215,15 +52215,15 @@
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -52238,7 +52238,7 @@
       </c>
       <c r="K1016" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52252,11 +52252,11 @@
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
@@ -52266,15 +52266,15 @@
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
@@ -52289,7 +52289,7 @@
       </c>
       <c r="K1017" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52303,11 +52303,11 @@
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
@@ -52317,15 +52317,15 @@
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>14.75</v>
+        <v>0.054777</v>
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
@@ -52340,7 +52340,7 @@
       </c>
       <c r="K1018" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52354,11 +52354,11 @@
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -52368,15 +52368,15 @@
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>14.5</v>
+        <v>0.054223</v>
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
@@ -52391,7 +52391,7 @@
       </c>
       <c r="K1019" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52405,11 +52405,11 @@
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
@@ -52419,15 +52419,15 @@
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>14.5</v>
+        <v>0.0534</v>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -52442,7 +52442,7 @@
       </c>
       <c r="K1020" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52456,11 +52456,11 @@
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
@@ -52470,15 +52470,15 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>14.25</v>
+        <v>0.053028</v>
       </c>
       <c r="H1021" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1021" t="inlineStr">
@@ -52493,7 +52493,7 @@
       </c>
       <c r="K1021" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52507,11 +52507,11 @@
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -52521,15 +52521,15 @@
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>14.25</v>
+        <v>0.052531</v>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
@@ -52544,7 +52544,7 @@
       </c>
       <c r="K1022" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52558,11 +52558,11 @@
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -52572,15 +52572,15 @@
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>14</v>
+        <v>0.051784</v>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
@@ -52595,7 +52595,7 @@
       </c>
       <c r="K1023" t="inlineStr">
         <is>
-          <t>ultimo</t>
+          <t>media</t>
         </is>
       </c>
     </row>
@@ -52609,11 +52609,11 @@
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>selic_meta</t>
+          <t>selic_over</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -52623,15 +52623,15 @@
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t>% a.a.</t>
+          <t>% a.d.</t>
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>13.75</v>
+        <v>0.051293</v>
       </c>
       <c r="H1024" t="inlineStr">
         <is>
-          <t>Taxa Selic meta definida pelo Copom.</t>
+          <t>Taxa Selic over.</t>
         </is>
       </c>
       <c r="I1024" t="inlineStr">
@@ -52645,3117 +52645,6 @@
         </is>
       </c>
       <c r="K1024" t="inlineStr">
-        <is>
-          <t>ultimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="B1025" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1025" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1025" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1025" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1025" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1025" t="n">
-        <v>0.023687</v>
-      </c>
-      <c r="H1025" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1025" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1025" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1025" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="B1026" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1026" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1026" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1026" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1026" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1026" t="n">
-        <v>0.024244</v>
-      </c>
-      <c r="H1026" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1026" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1026" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1026" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" s="1" t="n">
-        <v>44530</v>
-      </c>
-      <c r="B1027" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1027" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1027" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1027" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1027" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1027" t="n">
-        <v>0.029256</v>
-      </c>
-      <c r="H1027" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1027" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1027" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1027" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B1028" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1028" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1028" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1028" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1028" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1028" t="n">
-        <v>0.033316</v>
-      </c>
-      <c r="H1028" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1028" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1028" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1028" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="B1029" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1029" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1029" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1029" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1029" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1029" t="n">
-        <v>0.034749</v>
-      </c>
-      <c r="H1029" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1029" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1029" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1029" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" s="1" t="n">
-        <v>44620</v>
-      </c>
-      <c r="B1030" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1030" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1030" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1030" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1030" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1030" t="n">
-        <v>0.039598</v>
-      </c>
-      <c r="H1030" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1030" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1030" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1030" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="B1031" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1031" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1031" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1031" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1031" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1031" t="n">
-        <v>0.041954</v>
-      </c>
-      <c r="H1031" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1031" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1031" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1031" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" s="1" t="n">
-        <v>44681</v>
-      </c>
-      <c r="B1032" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1032" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1032" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1032" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1032" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1032" t="n">
-        <v>0.043739</v>
-      </c>
-      <c r="H1032" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1032" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1032" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1032" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" s="1" t="n">
-        <v>44712</v>
-      </c>
-      <c r="B1033" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1033" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1033" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1033" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1033" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1033" t="n">
-        <v>0.046796</v>
-      </c>
-      <c r="H1033" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1033" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1033" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1033" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" s="1" t="n">
-        <v>44742</v>
-      </c>
-      <c r="B1034" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1034" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1034" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1034" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1034" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1034" t="n">
-        <v>0.048116</v>
-      </c>
-      <c r="H1034" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1034" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1034" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1034" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" s="1" t="n">
-        <v>44773</v>
-      </c>
-      <c r="B1035" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1035" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1035" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1035" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1035" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1035" t="n">
-        <v>0.049037</v>
-      </c>
-      <c r="H1035" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1035" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1035" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1035" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" s="1" t="n">
-        <v>44804</v>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1036" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1036" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1036" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1036" t="n">
-        <v>0.05056</v>
-      </c>
-      <c r="H1036" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1036" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1036" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1036" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" s="1" t="n">
-        <v>44834</v>
-      </c>
-      <c r="B1037" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1037" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1037" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1037" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1037" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1037" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1037" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1037" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1037" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1037" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" s="1" t="n">
-        <v>44865</v>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1038" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1038" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1038" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1038" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1038" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1038" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1038" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1038" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1038" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1039" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1039" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1039" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1039" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1039" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1039" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1039" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1040" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1040" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1040" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1040" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1040" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1040" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1040" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" s="1" t="n">
-        <v>44957</v>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1041" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1041" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1041" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1041" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1041" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1041" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1041" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1041" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" s="1" t="n">
-        <v>44985</v>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1042" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1042" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1042" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1042" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1042" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1042" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1042" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" s="1" t="n">
-        <v>45016</v>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1043" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1043" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1043" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1043" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1043" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1043" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1043" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" s="1" t="n">
-        <v>45046</v>
-      </c>
-      <c r="B1044" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1044" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1044" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1044" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1044" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1044" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1044" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1044" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1044" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1044" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" s="1" t="n">
-        <v>45077</v>
-      </c>
-      <c r="B1045" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1045" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1045" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1045" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1045" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1045" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1045" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1045" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1045" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1045" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" s="1" t="n">
-        <v>45107</v>
-      </c>
-      <c r="B1046" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1046" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1046" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1046" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1046" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1046" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1046" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1046" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1046" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1046" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" s="1" t="n">
-        <v>45138</v>
-      </c>
-      <c r="B1047" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1047" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1047" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1047" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1047" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1047" t="n">
-        <v>0.050788</v>
-      </c>
-      <c r="H1047" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1047" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1047" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1047" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" s="1" t="n">
-        <v>45169</v>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1048" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1048" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1048" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1048" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1048" t="n">
-        <v>0.049189</v>
-      </c>
-      <c r="H1048" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1048" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1048" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1048" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" s="1" t="n">
-        <v>45199</v>
-      </c>
-      <c r="B1049" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1049" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1049" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1049" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1049" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1049" t="n">
-        <v>0.048422</v>
-      </c>
-      <c r="H1049" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1049" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1049" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1049" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="B1050" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1050" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1050" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1050" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1050" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1050" t="n">
-        <v>0.047279</v>
-      </c>
-      <c r="H1050" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1050" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1050" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1050" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1051" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1051" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1051" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1051" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1051" t="n">
-        <v>0.045601</v>
-      </c>
-      <c r="H1051" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1051" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1051" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1051" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B1052" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1052" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1052" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1052" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1052" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1052" t="n">
-        <v>0.044537</v>
-      </c>
-      <c r="H1052" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1052" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1052" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1052" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" s="1" t="n">
-        <v>45322</v>
-      </c>
-      <c r="B1053" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1053" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1053" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1053" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1053" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1053" t="n">
-        <v>0.043739</v>
-      </c>
-      <c r="H1053" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1053" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1053" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1053" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1054" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1054" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1054" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1054" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1054" t="n">
-        <v>0.041957</v>
-      </c>
-      <c r="H1054" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1054" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1054" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1054" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" s="1" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B1055" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1055" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1055" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1055" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1055" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1055" t="n">
-        <v>0.04142</v>
-      </c>
-      <c r="H1055" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1055" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1055" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1055" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" s="1" t="n">
-        <v>45412</v>
-      </c>
-      <c r="B1056" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1056" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1056" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1056" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1056" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1056" t="n">
-        <v>0.040168</v>
-      </c>
-      <c r="H1056" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1056" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1056" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1056" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" s="1" t="n">
-        <v>45443</v>
-      </c>
-      <c r="B1057" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1057" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1057" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1057" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1057" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1057" t="n">
-        <v>0.039484</v>
-      </c>
-      <c r="H1057" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1057" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1057" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1057" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" s="1" t="n">
-        <v>45473</v>
-      </c>
-      <c r="B1058" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1058" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1058" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1058" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1058" t="n">
-        <v>0.03927</v>
-      </c>
-      <c r="H1058" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1058" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1058" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1058" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" s="1" t="n">
-        <v>45504</v>
-      </c>
-      <c r="B1059" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1059" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1059" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1059" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1059" t="n">
-        <v>0.03927</v>
-      </c>
-      <c r="H1059" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1059" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1059" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1059" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" s="1" t="n">
-        <v>45535</v>
-      </c>
-      <c r="B1060" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1060" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1060" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1060" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1060" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1060" t="n">
-        <v>0.03927</v>
-      </c>
-      <c r="H1060" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1060" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1060" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1060" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B1061" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1061" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1061" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1061" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1061" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1061" t="n">
-        <v>0.039612</v>
-      </c>
-      <c r="H1061" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1061" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1061" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1061" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" s="1" t="n">
-        <v>45596</v>
-      </c>
-      <c r="B1062" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1062" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1062" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1062" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1062" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1062" t="n">
-        <v>0.040168</v>
-      </c>
-      <c r="H1062" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1062" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1062" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1062" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" s="1" t="n">
-        <v>45626</v>
-      </c>
-      <c r="B1063" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1063" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1063" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1063" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1063" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1063" t="n">
-        <v>0.04158</v>
-      </c>
-      <c r="H1063" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1063" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1063" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1063" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B1064" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1064" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1064" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1064" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1064" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1064" t="n">
-        <v>0.044158</v>
-      </c>
-      <c r="H1064" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1064" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1064" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1064" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B1065" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1065" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1065" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1065" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1065" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1065" t="n">
-        <v>0.045833</v>
-      </c>
-      <c r="H1065" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1065" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1065" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1065" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" s="1" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B1066" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1066" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1066" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1066" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1066" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1066" t="n">
-        <v>0.049037</v>
-      </c>
-      <c r="H1066" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1066" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1066" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1066" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="B1067" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1067" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1067" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1067" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1067" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1067" t="n">
-        <v>0.050508</v>
-      </c>
-      <c r="H1067" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1067" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1067" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1067" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" s="1" t="n">
-        <v>45777</v>
-      </c>
-      <c r="B1068" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1068" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1068" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1068" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1068" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1068" t="n">
-        <v>0.052531</v>
-      </c>
-      <c r="H1068" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1068" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1068" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1068" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" s="1" t="n">
-        <v>45808</v>
-      </c>
-      <c r="B1069" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1069" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1069" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1069" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1069" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1069" t="n">
-        <v>0.053936</v>
-      </c>
-      <c r="H1069" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1069" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1069" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1069" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="B1070" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1070" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1070" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1070" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1070" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1070" t="n">
-        <v>0.054569</v>
-      </c>
-      <c r="H1070" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1070" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1070" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1070" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" s="1" t="n">
-        <v>45869</v>
-      </c>
-      <c r="B1071" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1071" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1071" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1071" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1071" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1071" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1071" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1071" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1071" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1071" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" s="1" t="n">
-        <v>45900</v>
-      </c>
-      <c r="B1072" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1072" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1072" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1072" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1072" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1072" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1072" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1072" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1072" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1072" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" s="1" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B1073" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1073" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1073" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1073" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1073" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1073" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1073" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1073" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1073" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1073" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" s="1" t="n">
-        <v>45961</v>
-      </c>
-      <c r="B1074" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1074" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1074" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1074" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1074" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1074" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1074" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1074" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1074" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1074" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B1075" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1075" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1075" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1075" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1075" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1075" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1075" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1075" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1075" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1075" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B1076" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1076" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1076" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1076" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1076" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1076" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1076" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1076" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1076" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1076" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B1077" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1077" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1077" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1077" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1077" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1077" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1077" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1077" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1077" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1077" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B1078" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1078" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1078" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1078" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1078" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1078" t="n">
-        <v>0.055131</v>
-      </c>
-      <c r="H1078" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1078" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1078" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1078" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1079">
-      <c r="A1079" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B1079" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1079" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1079" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1079" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1079" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1079" t="n">
-        <v>0.054777</v>
-      </c>
-      <c r="H1079" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1079" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1079" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1079" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1080">
-      <c r="A1080" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B1080" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1080" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1080" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1080" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1080" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1080" t="n">
-        <v>0.054223</v>
-      </c>
-      <c r="H1080" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1080" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1080" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1080" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1081">
-      <c r="A1081" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B1081" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1081" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1081" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1081" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1081" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1081" t="n">
-        <v>0.0534</v>
-      </c>
-      <c r="H1081" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1081" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1081" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1081" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1082">
-      <c r="A1082" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B1082" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1082" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1082" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1082" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1082" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1082" t="n">
-        <v>0.053028</v>
-      </c>
-      <c r="H1082" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1082" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1082" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1082" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1083">
-      <c r="A1083" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B1083" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1083" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1083" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1083" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1083" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1083" t="n">
-        <v>0.052531</v>
-      </c>
-      <c r="H1083" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1083" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1083" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1083" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1084">
-      <c r="A1084" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B1084" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1084" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1084" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1084" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1084" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1084" t="n">
-        <v>0.051784</v>
-      </c>
-      <c r="H1084" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1084" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1084" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1084" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B1085" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1085" t="n">
-        <v>11</v>
-      </c>
-      <c r="D1085" t="inlineStr">
-        <is>
-          <t>selic_over</t>
-        </is>
-      </c>
-      <c r="E1085" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="F1085" t="inlineStr">
-        <is>
-          <t>% a.d.</t>
-        </is>
-      </c>
-      <c r="G1085" t="n">
-        <v>0.051293</v>
-      </c>
-      <c r="H1085" t="inlineStr">
-        <is>
-          <t>Taxa Selic over.</t>
-        </is>
-      </c>
-      <c r="I1085" t="inlineStr">
-        <is>
-          <t>diaria</t>
-        </is>
-      </c>
-      <c r="J1085" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1085" t="inlineStr">
         <is>
           <t>media</t>
         </is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1024"/>
+  <dimension ref="A1:K1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.2126</v>
+        <v>5.2198</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.051293</v>
+        <v>0.051268</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -49549,11 +49549,11 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -49563,15 +49563,15 @@
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G964" t="n">
-        <v>0.023687</v>
+        <v>6.25</v>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -49586,7 +49586,7 @@
       </c>
       <c r="K964" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49600,11 +49600,11 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -49614,15 +49614,15 @@
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G965" t="n">
-        <v>0.024244</v>
+        <v>7.75</v>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -49637,7 +49637,7 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49651,11 +49651,11 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -49665,15 +49665,15 @@
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G966" t="n">
-        <v>0.029256</v>
+        <v>7.75</v>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
@@ -49688,7 +49688,7 @@
       </c>
       <c r="K966" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49702,11 +49702,11 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -49716,15 +49716,15 @@
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G967" t="n">
-        <v>0.033316</v>
+        <v>9.25</v>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -49739,7 +49739,7 @@
       </c>
       <c r="K967" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49753,11 +49753,11 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
@@ -49767,15 +49767,15 @@
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G968" t="n">
-        <v>0.034749</v>
+        <v>9.25</v>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I968" t="inlineStr">
@@ -49790,7 +49790,7 @@
       </c>
       <c r="K968" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49804,11 +49804,11 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -49818,15 +49818,15 @@
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G969" t="n">
-        <v>0.039598</v>
+        <v>10.75</v>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
@@ -49841,7 +49841,7 @@
       </c>
       <c r="K969" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49855,11 +49855,11 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -49869,15 +49869,15 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.041954</v>
+        <v>11.75</v>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
@@ -49892,7 +49892,7 @@
       </c>
       <c r="K970" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49906,11 +49906,11 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -49920,15 +49920,15 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.043739</v>
+        <v>11.75</v>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
@@ -49943,7 +49943,7 @@
       </c>
       <c r="K971" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -49957,11 +49957,11 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
@@ -49971,15 +49971,15 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.046796</v>
+        <v>12.75</v>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -49994,7 +49994,7 @@
       </c>
       <c r="K972" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50008,11 +50008,11 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
@@ -50022,15 +50022,15 @@
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.048116</v>
+        <v>13.25</v>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
@@ -50045,7 +50045,7 @@
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50059,11 +50059,11 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -50073,15 +50073,15 @@
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.049037</v>
+        <v>13.25</v>
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
@@ -50096,7 +50096,7 @@
       </c>
       <c r="K974" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50110,11 +50110,11 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -50124,15 +50124,15 @@
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.05056</v>
+        <v>13.75</v>
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50161,11 +50161,11 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -50175,15 +50175,15 @@
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G976" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
@@ -50198,7 +50198,7 @@
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50212,11 +50212,11 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -50226,15 +50226,15 @@
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
@@ -50249,7 +50249,7 @@
       </c>
       <c r="K977" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50263,11 +50263,11 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -50277,15 +50277,15 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -50300,7 +50300,7 @@
       </c>
       <c r="K978" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50314,11 +50314,11 @@
         </is>
       </c>
       <c r="C979" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -50328,15 +50328,15 @@
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G979" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
@@ -50351,7 +50351,7 @@
       </c>
       <c r="K979" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50365,11 +50365,11 @@
         </is>
       </c>
       <c r="C980" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
@@ -50379,15 +50379,15 @@
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
@@ -50402,7 +50402,7 @@
       </c>
       <c r="K980" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50416,11 +50416,11 @@
         </is>
       </c>
       <c r="C981" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
@@ -50430,15 +50430,15 @@
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G981" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
@@ -50453,7 +50453,7 @@
       </c>
       <c r="K981" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50467,11 +50467,11 @@
         </is>
       </c>
       <c r="C982" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
@@ -50481,15 +50481,15 @@
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G982" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
@@ -50504,7 +50504,7 @@
       </c>
       <c r="K982" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50518,11 +50518,11 @@
         </is>
       </c>
       <c r="C983" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
@@ -50532,15 +50532,15 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G983" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
@@ -50555,7 +50555,7 @@
       </c>
       <c r="K983" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50569,11 +50569,11 @@
         </is>
       </c>
       <c r="C984" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
@@ -50583,15 +50583,15 @@
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G984" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -50606,7 +50606,7 @@
       </c>
       <c r="K984" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50620,11 +50620,11 @@
         </is>
       </c>
       <c r="C985" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -50634,15 +50634,15 @@
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -50657,7 +50657,7 @@
       </c>
       <c r="K985" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50671,11 +50671,11 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -50685,15 +50685,15 @@
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -50708,7 +50708,7 @@
       </c>
       <c r="K986" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50722,11 +50722,11 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
@@ -50736,15 +50736,15 @@
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G987" t="n">
-        <v>0.049189</v>
+        <v>13.25</v>
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
@@ -50759,7 +50759,7 @@
       </c>
       <c r="K987" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50773,11 +50773,11 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
@@ -50787,15 +50787,15 @@
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G988" t="n">
-        <v>0.048422</v>
+        <v>12.75</v>
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
@@ -50810,7 +50810,7 @@
       </c>
       <c r="K988" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50824,11 +50824,11 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -50838,15 +50838,15 @@
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G989" t="n">
-        <v>0.047279</v>
+        <v>12.75</v>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
@@ -50861,7 +50861,7 @@
       </c>
       <c r="K989" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50875,11 +50875,11 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
@@ -50889,15 +50889,15 @@
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G990" t="n">
-        <v>0.045601</v>
+        <v>12.25</v>
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
@@ -50912,7 +50912,7 @@
       </c>
       <c r="K990" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50926,11 +50926,11 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
@@ -50940,15 +50940,15 @@
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G991" t="n">
-        <v>0.044537</v>
+        <v>11.75</v>
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
@@ -50963,7 +50963,7 @@
       </c>
       <c r="K991" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -50977,11 +50977,11 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
@@ -50991,15 +50991,15 @@
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G992" t="n">
-        <v>0.043739</v>
+        <v>11.75</v>
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -51014,7 +51014,7 @@
       </c>
       <c r="K992" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51028,11 +51028,11 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -51042,15 +51042,15 @@
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G993" t="n">
-        <v>0.041957</v>
+        <v>11.25</v>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
@@ -51065,7 +51065,7 @@
       </c>
       <c r="K993" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51079,11 +51079,11 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
@@ -51093,15 +51093,15 @@
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G994" t="n">
-        <v>0.04142</v>
+        <v>10.75</v>
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I994" t="inlineStr">
@@ -51116,7 +51116,7 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51130,11 +51130,11 @@
         </is>
       </c>
       <c r="C995" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
@@ -51144,15 +51144,15 @@
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G995" t="n">
-        <v>0.040168</v>
+        <v>10.75</v>
       </c>
       <c r="H995" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I995" t="inlineStr">
@@ -51167,7 +51167,7 @@
       </c>
       <c r="K995" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51181,11 +51181,11 @@
         </is>
       </c>
       <c r="C996" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
@@ -51195,15 +51195,15 @@
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.039484</v>
+        <v>10.5</v>
       </c>
       <c r="H996" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I996" t="inlineStr">
@@ -51218,7 +51218,7 @@
       </c>
       <c r="K996" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51232,11 +51232,11 @@
         </is>
       </c>
       <c r="C997" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
@@ -51246,15 +51246,15 @@
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.03927</v>
+        <v>10.5</v>
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="K997" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51283,11 +51283,11 @@
         </is>
       </c>
       <c r="C998" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -51297,15 +51297,15 @@
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.03927</v>
+        <v>10.5</v>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -51320,7 +51320,7 @@
       </c>
       <c r="K998" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51334,11 +51334,11 @@
         </is>
       </c>
       <c r="C999" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -51348,15 +51348,15 @@
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.03927</v>
+        <v>10.5</v>
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -51371,7 +51371,7 @@
       </c>
       <c r="K999" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51385,11 +51385,11 @@
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -51399,15 +51399,15 @@
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>0.039612</v>
+        <v>10.75</v>
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -51422,7 +51422,7 @@
       </c>
       <c r="K1000" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51436,11 +51436,11 @@
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -51450,15 +51450,15 @@
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>0.040168</v>
+        <v>10.75</v>
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
@@ -51473,7 +51473,7 @@
       </c>
       <c r="K1001" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51487,11 +51487,11 @@
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -51501,15 +51501,15 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>0.04158</v>
+        <v>11.25</v>
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -51524,7 +51524,7 @@
       </c>
       <c r="K1002" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51538,11 +51538,11 @@
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -51552,15 +51552,15 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>0.044158</v>
+        <v>12.25</v>
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -51575,7 +51575,7 @@
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51589,11 +51589,11 @@
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -51603,15 +51603,15 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>0.045833</v>
+        <v>13.25</v>
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -51626,7 +51626,7 @@
       </c>
       <c r="K1004" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51640,11 +51640,11 @@
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -51654,15 +51654,15 @@
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>0.049037</v>
+        <v>13.25</v>
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -51677,7 +51677,7 @@
       </c>
       <c r="K1005" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51691,11 +51691,11 @@
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -51705,15 +51705,15 @@
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>0.050508</v>
+        <v>14.25</v>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -51728,7 +51728,7 @@
       </c>
       <c r="K1006" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51742,11 +51742,11 @@
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -51756,15 +51756,15 @@
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>0.052531</v>
+        <v>14.25</v>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -51779,7 +51779,7 @@
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51793,11 +51793,11 @@
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -51807,15 +51807,15 @@
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>0.053936</v>
+        <v>14.75</v>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
@@ -51830,7 +51830,7 @@
       </c>
       <c r="K1008" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51844,11 +51844,11 @@
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -51858,15 +51858,15 @@
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>0.054569</v>
+        <v>15</v>
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
@@ -51881,7 +51881,7 @@
       </c>
       <c r="K1009" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51895,11 +51895,11 @@
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
@@ -51909,15 +51909,15 @@
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
@@ -51932,7 +51932,7 @@
       </c>
       <c r="K1010" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51946,11 +51946,11 @@
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
@@ -51960,15 +51960,15 @@
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
@@ -51983,7 +51983,7 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -51997,11 +51997,11 @@
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -52011,15 +52011,15 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -52034,7 +52034,7 @@
       </c>
       <c r="K1012" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52048,11 +52048,11 @@
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
@@ -52062,15 +52062,15 @@
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
@@ -52085,7 +52085,7 @@
       </c>
       <c r="K1013" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52099,11 +52099,11 @@
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
@@ -52113,15 +52113,15 @@
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -52136,7 +52136,7 @@
       </c>
       <c r="K1014" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52150,11 +52150,11 @@
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
@@ -52164,15 +52164,15 @@
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="K1015" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52201,11 +52201,11 @@
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -52215,15 +52215,15 @@
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -52238,7 +52238,7 @@
       </c>
       <c r="K1016" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52252,11 +52252,11 @@
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
@@ -52266,15 +52266,15 @@
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
@@ -52289,7 +52289,7 @@
       </c>
       <c r="K1017" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52303,11 +52303,11 @@
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
@@ -52317,15 +52317,15 @@
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>0.054777</v>
+        <v>14.75</v>
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
@@ -52340,7 +52340,7 @@
       </c>
       <c r="K1018" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52354,11 +52354,11 @@
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -52368,15 +52368,15 @@
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>0.054223</v>
+        <v>14.5</v>
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
@@ -52391,7 +52391,7 @@
       </c>
       <c r="K1019" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52405,11 +52405,11 @@
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
@@ -52419,15 +52419,15 @@
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.0534</v>
+        <v>14.5</v>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -52442,7 +52442,7 @@
       </c>
       <c r="K1020" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52456,11 +52456,11 @@
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
@@ -52470,15 +52470,15 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>0.053028</v>
+        <v>14.25</v>
       </c>
       <c r="H1021" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1021" t="inlineStr">
@@ -52493,7 +52493,7 @@
       </c>
       <c r="K1021" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52507,11 +52507,11 @@
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -52521,15 +52521,15 @@
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>0.052531</v>
+        <v>14.25</v>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
@@ -52544,7 +52544,7 @@
       </c>
       <c r="K1022" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52558,11 +52558,11 @@
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -52572,15 +52572,15 @@
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>0.051784</v>
+        <v>14</v>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
@@ -52595,7 +52595,7 @@
       </c>
       <c r="K1023" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
@@ -52609,42 +52609,3153 @@
         </is>
       </c>
       <c r="C1024" t="n">
+        <v>432</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>selic_meta</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>% a.a.</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>Taxa Selic meta definida pelo Copom.</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
         <v>11</v>
       </c>
-      <c r="D1024" t="inlineStr">
+      <c r="D1025" t="inlineStr">
         <is>
           <t>selic_over</t>
         </is>
       </c>
-      <c r="E1024" t="inlineStr">
+      <c r="E1025" t="inlineStr">
         <is>
           <t>politica_monetaria</t>
         </is>
       </c>
-      <c r="F1024" t="inlineStr">
+      <c r="F1025" t="inlineStr">
         <is>
           <t>% a.d.</t>
         </is>
       </c>
-      <c r="G1024" t="n">
-        <v>0.051293</v>
-      </c>
-      <c r="H1024" t="inlineStr">
+      <c r="G1025" t="n">
+        <v>0.023687</v>
+      </c>
+      <c r="H1025" t="inlineStr">
         <is>
           <t>Taxa Selic over.</t>
         </is>
       </c>
-      <c r="I1024" t="inlineStr">
+      <c r="I1025" t="inlineStr">
         <is>
           <t>diaria</t>
         </is>
       </c>
-      <c r="J1024" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1024" t="inlineStr">
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1026" t="n">
+        <v>0.024244</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1029" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="1" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1030" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1031" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="1" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1032" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1033" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1034" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1036" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1037" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1038" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1039" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1040" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="1" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1041" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="1" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1042" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1043" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1044" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1045" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1046" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1047" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="1" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1048" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1049" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1050" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1051" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1052" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1053" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1054" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1055" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1056" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1057" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1058" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1059" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1060" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1061" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1062" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1063" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1066" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1067" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1070" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1071" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1074" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1075" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1076" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1076" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1077" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1078" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1079" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1080" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1081" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1082" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1083" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1084" t="n">
+        <v>0.051784</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1085" t="n">
+        <v>0.051268</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1085" t="inlineStr">
         <is>
           <t>media</t>
         </is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1011"/>
+  <dimension ref="A1:K1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>4.9929</v>
+        <v>5.0113</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>4.9935</v>
+        <v>5.0119</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.024383</v>
+        <v>0.02443</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
     </row>
     <row r="774">
       <c r="A774" s="1" t="n">
-        <v>44500</v>
+        <v>46295</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -39859,34 +39859,34 @@
         </is>
       </c>
       <c r="C774" t="n">
-        <v>20541</v>
+        <v>3546</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>saldo_credito_pf</t>
+          <t>reservas_internacionais</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>R$ milhões</t>
+          <t>US$ milhões</t>
         </is>
       </c>
       <c r="G774" t="n">
-        <v>2601017</v>
+        <v>362821</v>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas físicas.</t>
+          <t>Reservas internacionais.</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -39896,13 +39896,13 @@
       </c>
       <c r="K774" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         </is>
       </c>
       <c r="G775" t="n">
-        <v>2664395</v>
+        <v>2601017</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
     </row>
     <row r="776">
       <c r="A776" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="G776" t="n">
-        <v>2708461</v>
+        <v>2664395</v>
       </c>
       <c r="H776" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
     </row>
     <row r="777">
       <c r="A777" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         </is>
       </c>
       <c r="G777" t="n">
-        <v>2735096</v>
+        <v>2708461</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
     </row>
     <row r="778">
       <c r="A778" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         </is>
       </c>
       <c r="G778" t="n">
-        <v>2756295</v>
+        <v>2735096</v>
       </c>
       <c r="H778" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
     </row>
     <row r="779">
       <c r="A779" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         </is>
       </c>
       <c r="G779" t="n">
-        <v>2800464</v>
+        <v>2756295</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
     </row>
     <row r="780">
       <c r="A780" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         </is>
       </c>
       <c r="G780" t="n">
-        <v>2830420</v>
+        <v>2800464</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
     </row>
     <row r="781">
       <c r="A781" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         </is>
       </c>
       <c r="G781" t="n">
-        <v>2875671</v>
+        <v>2830420</v>
       </c>
       <c r="H781" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
     </row>
     <row r="782">
       <c r="A782" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         </is>
       </c>
       <c r="G782" t="n">
-        <v>2913035</v>
+        <v>2875671</v>
       </c>
       <c r="H782" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         </is>
       </c>
       <c r="G783" t="n">
-        <v>2952207</v>
+        <v>2913035</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         </is>
       </c>
       <c r="G784" t="n">
-        <v>3008528</v>
+        <v>2952207</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         </is>
       </c>
       <c r="G785" t="n">
-        <v>3054969</v>
+        <v>3008528</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         </is>
       </c>
       <c r="G786" t="n">
-        <v>3110134</v>
+        <v>3054969</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         </is>
       </c>
       <c r="G787" t="n">
-        <v>3155345</v>
+        <v>3110134</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         </is>
       </c>
       <c r="G788" t="n">
-        <v>3187833</v>
+        <v>3155345</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>3221831</v>
+        <v>3187833</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         </is>
       </c>
       <c r="G790" t="n">
-        <v>3234845</v>
+        <v>3221831</v>
       </c>
       <c r="H790" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         </is>
       </c>
       <c r="G791" t="n">
-        <v>3269910</v>
+        <v>3234845</v>
       </c>
       <c r="H791" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         </is>
       </c>
       <c r="G792" t="n">
-        <v>3281308</v>
+        <v>3269910</v>
       </c>
       <c r="H792" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         </is>
       </c>
       <c r="G793" t="n">
-        <v>3308178</v>
+        <v>3281308</v>
       </c>
       <c r="H793" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         </is>
       </c>
       <c r="G794" t="n">
-        <v>3309846</v>
+        <v>3308178</v>
       </c>
       <c r="H794" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
     </row>
     <row r="795">
       <c r="A795" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         </is>
       </c>
       <c r="G795" t="n">
-        <v>3331330</v>
+        <v>3309846</v>
       </c>
       <c r="H795" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
     </row>
     <row r="796">
       <c r="A796" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         </is>
       </c>
       <c r="G796" t="n">
-        <v>3386405</v>
+        <v>3331330</v>
       </c>
       <c r="H796" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
     </row>
     <row r="797">
       <c r="A797" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         </is>
       </c>
       <c r="G797" t="n">
-        <v>3410769</v>
+        <v>3386405</v>
       </c>
       <c r="H797" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
     </row>
     <row r="798">
       <c r="A798" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         </is>
       </c>
       <c r="G798" t="n">
-        <v>3449000</v>
+        <v>3410769</v>
       </c>
       <c r="H798" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
     </row>
     <row r="799">
       <c r="A799" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         </is>
       </c>
       <c r="G799" t="n">
-        <v>3490337</v>
+        <v>3449000</v>
       </c>
       <c r="H799" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
     </row>
     <row r="800">
       <c r="A800" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="G800" t="n">
-        <v>3521672</v>
+        <v>3490337</v>
       </c>
       <c r="H800" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>3560345</v>
+        <v>3521672</v>
       </c>
       <c r="H801" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3580652</v>
+        <v>3560345</v>
       </c>
       <c r="H802" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3613967</v>
+        <v>3580652</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3646659</v>
+        <v>3613967</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         </is>
       </c>
       <c r="G805" t="n">
-        <v>3675652</v>
+        <v>3646659</v>
       </c>
       <c r="H805" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         </is>
       </c>
       <c r="G806" t="n">
-        <v>3705041</v>
+        <v>3675652</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         </is>
       </c>
       <c r="G807" t="n">
-        <v>3745844</v>
+        <v>3705041</v>
       </c>
       <c r="H807" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         </is>
       </c>
       <c r="G808" t="n">
-        <v>3790900</v>
+        <v>3745844</v>
       </c>
       <c r="H808" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         </is>
       </c>
       <c r="G809" t="n">
-        <v>3831700</v>
+        <v>3790900</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         </is>
       </c>
       <c r="G810" t="n">
-        <v>3877584</v>
+        <v>3831700</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="G811" t="n">
-        <v>3929668</v>
+        <v>3877584</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         </is>
       </c>
       <c r="G812" t="n">
-        <v>3965425</v>
+        <v>3929668</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="G813" t="n">
-        <v>4013059</v>
+        <v>3965425</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         </is>
       </c>
       <c r="G814" t="n">
-        <v>4034293</v>
+        <v>4013059</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         </is>
       </c>
       <c r="G815" t="n">
-        <v>4078202</v>
+        <v>4034293</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
     </row>
     <row r="816">
       <c r="A816" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         </is>
       </c>
       <c r="G816" t="n">
-        <v>4111522</v>
+        <v>4078202</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
     </row>
     <row r="817">
       <c r="A817" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         </is>
       </c>
       <c r="G817" t="n">
-        <v>4133579</v>
+        <v>4111522</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
     </row>
     <row r="818">
       <c r="A818" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         </is>
       </c>
       <c r="G818" t="n">
-        <v>4155970</v>
+        <v>4133579</v>
       </c>
       <c r="H818" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
     </row>
     <row r="819">
       <c r="A819" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         </is>
       </c>
       <c r="G819" t="n">
-        <v>4188808</v>
+        <v>4155970</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
     </row>
     <row r="820">
       <c r="A820" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         </is>
       </c>
       <c r="G820" t="n">
-        <v>4228171</v>
+        <v>4188808</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
     </row>
     <row r="821">
       <c r="A821" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         </is>
       </c>
       <c r="G821" t="n">
-        <v>4262888</v>
+        <v>4228171</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
     </row>
     <row r="822">
       <c r="A822" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         </is>
       </c>
       <c r="G822" t="n">
-        <v>4326256</v>
+        <v>4262888</v>
       </c>
       <c r="H822" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
     </row>
     <row r="823">
       <c r="A823" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         </is>
       </c>
       <c r="G823" t="n">
-        <v>4387321</v>
+        <v>4326256</v>
       </c>
       <c r="H823" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
     </row>
     <row r="824">
       <c r="A824" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         </is>
       </c>
       <c r="G824" t="n">
-        <v>4435517</v>
+        <v>4387321</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
     </row>
     <row r="825">
       <c r="A825" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         </is>
       </c>
       <c r="G825" t="n">
-        <v>4476542</v>
+        <v>4435517</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
     </row>
     <row r="826">
       <c r="A826" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="G826" t="n">
-        <v>4501299</v>
+        <v>4476542</v>
       </c>
       <c r="H826" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
     </row>
     <row r="827">
       <c r="A827" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         </is>
       </c>
       <c r="G827" t="n">
-        <v>4553022</v>
+        <v>4501299</v>
       </c>
       <c r="H827" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
     </row>
     <row r="828">
       <c r="A828" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         </is>
       </c>
       <c r="G828" t="n">
-        <v>4574368</v>
+        <v>4553022</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
     </row>
     <row r="829">
       <c r="A829" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>4597168</v>
+        <v>4574368</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
     </row>
     <row r="830">
       <c r="A830" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>4602668</v>
+        <v>4597168</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
     </row>
     <row r="831">
       <c r="A831" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>4633143</v>
+        <v>4602668</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
     </row>
     <row r="832">
       <c r="A832" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>4670170</v>
+        <v>4633143</v>
       </c>
       <c r="H832" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
     </row>
     <row r="833">
       <c r="A833" s="1" t="n">
-        <v>44500</v>
+        <v>46265</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -42868,11 +42868,11 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>20540</v>
+        <v>20541</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>saldo_credito_pj</t>
+          <t>saldo_credito_pf</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -42886,11 +42886,11 @@
         </is>
       </c>
       <c r="G833" t="n">
-        <v>1910940</v>
+        <v>4670170</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
+          <t>Saldo da carteira de crédito - pessoas físicas.</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -42911,7 +42911,7 @@
     </row>
     <row r="834">
       <c r="A834" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>1933111</v>
+        <v>1910940</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
     </row>
     <row r="835">
       <c r="A835" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1974391</v>
+        <v>1933111</v>
       </c>
       <c r="H835" t="inlineStr">
         <is>
@@ -43013,7 +43013,7 @@
     </row>
     <row r="836">
       <c r="A836" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>1947035</v>
+        <v>1974391</v>
       </c>
       <c r="H836" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
     </row>
     <row r="837">
       <c r="A837" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="G837" t="n">
-        <v>1971524</v>
+        <v>1947035</v>
       </c>
       <c r="H837" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
     </row>
     <row r="838">
       <c r="A838" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         </is>
       </c>
       <c r="G838" t="n">
-        <v>1994119</v>
+        <v>1971524</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>2003312</v>
+        <v>1994119</v>
       </c>
       <c r="H839" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         </is>
       </c>
       <c r="G840" t="n">
-        <v>2013726</v>
+        <v>2003312</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
     </row>
     <row r="841">
       <c r="A841" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>2052569</v>
+        <v>2013726</v>
       </c>
       <c r="H841" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
     </row>
     <row r="842">
       <c r="A842" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>2047038</v>
+        <v>2052569</v>
       </c>
       <c r="H842" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
     </row>
     <row r="843">
       <c r="A843" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>2064183</v>
+        <v>2047038</v>
       </c>
       <c r="H843" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
     </row>
     <row r="844">
       <c r="A844" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         </is>
       </c>
       <c r="G844" t="n">
-        <v>2109806</v>
+        <v>2064183</v>
       </c>
       <c r="H844" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
     </row>
     <row r="845">
       <c r="A845" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         </is>
       </c>
       <c r="G845" t="n">
-        <v>2105856</v>
+        <v>2109806</v>
       </c>
       <c r="H845" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
     </row>
     <row r="846">
       <c r="A846" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         </is>
       </c>
       <c r="G846" t="n">
-        <v>2130312</v>
+        <v>2105856</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
     </row>
     <row r="847">
       <c r="A847" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         </is>
       </c>
       <c r="G847" t="n">
-        <v>2178236</v>
+        <v>2130312</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
     </row>
     <row r="848">
       <c r="A848" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>2151399</v>
+        <v>2178236</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
     </row>
     <row r="849">
       <c r="A849" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>2136105</v>
+        <v>2151399</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
     </row>
     <row r="850">
       <c r="A850" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>2154900</v>
+        <v>2136105</v>
       </c>
       <c r="H850" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
     </row>
     <row r="851">
       <c r="A851" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>2145000</v>
+        <v>2154900</v>
       </c>
       <c r="H851" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
     </row>
     <row r="852">
       <c r="A852" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         </is>
       </c>
       <c r="G852" t="n">
-        <v>2145530</v>
+        <v>2145000</v>
       </c>
       <c r="H852" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         </is>
       </c>
       <c r="G853" t="n">
-        <v>2169613</v>
+        <v>2145530</v>
       </c>
       <c r="H853" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
     </row>
     <row r="854">
       <c r="A854" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>2153541</v>
+        <v>2169613</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>2172658</v>
+        <v>2153541</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>2215175</v>
+        <v>2172658</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
     </row>
     <row r="857">
       <c r="A857" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>2204808</v>
+        <v>2215175</v>
       </c>
       <c r="H857" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
     </row>
     <row r="858">
       <c r="A858" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>2220766</v>
+        <v>2204808</v>
       </c>
       <c r="H858" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
     </row>
     <row r="859">
       <c r="A859" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>2283485</v>
+        <v>2220766</v>
       </c>
       <c r="H859" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
     </row>
     <row r="860">
       <c r="A860" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>2234362</v>
+        <v>2283485</v>
       </c>
       <c r="H860" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
     </row>
     <row r="861">
       <c r="A861" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="G861" t="n">
-        <v>2235302</v>
+        <v>2234362</v>
       </c>
       <c r="H861" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
     </row>
     <row r="862">
       <c r="A862" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2285775</v>
+        <v>2235302</v>
       </c>
       <c r="H862" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
     </row>
     <row r="863">
       <c r="A863" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>2268879</v>
+        <v>2285775</v>
       </c>
       <c r="H863" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
     </row>
     <row r="864">
       <c r="A864" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         </is>
       </c>
       <c r="G864" t="n">
-        <v>2278309</v>
+        <v>2268879</v>
       </c>
       <c r="H864" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
     </row>
     <row r="865">
       <c r="A865" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>2336858</v>
+        <v>2278309</v>
       </c>
       <c r="H865" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
     </row>
     <row r="866">
       <c r="A866" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>2323362</v>
+        <v>2336858</v>
       </c>
       <c r="H866" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
     </row>
     <row r="867">
       <c r="A867" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>2344397</v>
+        <v>2323362</v>
       </c>
       <c r="H867" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
     </row>
     <row r="868">
       <c r="A868" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2384828</v>
+        <v>2344397</v>
       </c>
       <c r="H868" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
     </row>
     <row r="869">
       <c r="A869" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2397533</v>
+        <v>2384828</v>
       </c>
       <c r="H869" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
     </row>
     <row r="870">
       <c r="A870" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>2436022</v>
+        <v>2397533</v>
       </c>
       <c r="H870" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
     </row>
     <row r="871">
       <c r="A871" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>2499177</v>
+        <v>2436022</v>
       </c>
       <c r="H871" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
     </row>
     <row r="872">
       <c r="A872" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -44875,7 +44875,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>2451957</v>
+        <v>2499177</v>
       </c>
       <c r="H872" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
     </row>
     <row r="873">
       <c r="A873" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2477151</v>
+        <v>2451957</v>
       </c>
       <c r="H873" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
     </row>
     <row r="874">
       <c r="A874" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B874" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2498262</v>
+        <v>2477151</v>
       </c>
       <c r="H874" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
     </row>
     <row r="875">
       <c r="A875" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B875" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2512426</v>
+        <v>2498262</v>
       </c>
       <c r="H875" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
     </row>
     <row r="876">
       <c r="A876" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B876" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2532708</v>
+        <v>2512426</v>
       </c>
       <c r="H876" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
     </row>
     <row r="877">
       <c r="A877" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B877" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2547693</v>
+        <v>2532708</v>
       </c>
       <c r="H877" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
     </row>
     <row r="878">
       <c r="A878" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B878" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>2544400</v>
+        <v>2547693</v>
       </c>
       <c r="H878" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
     </row>
     <row r="879">
       <c r="A879" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B879" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>2546265</v>
+        <v>2544400</v>
       </c>
       <c r="H879" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
     </row>
     <row r="880">
       <c r="A880" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B880" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>2589817</v>
+        <v>2546265</v>
       </c>
       <c r="H880" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
     </row>
     <row r="881">
       <c r="A881" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B881" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>2597630</v>
+        <v>2589817</v>
       </c>
       <c r="H881" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
     </row>
     <row r="882">
       <c r="A882" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B882" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>2616902</v>
+        <v>2597630</v>
       </c>
       <c r="H882" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
     </row>
     <row r="883">
       <c r="A883" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B883" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>2701735</v>
+        <v>2616902</v>
       </c>
       <c r="H883" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
     </row>
     <row r="884">
       <c r="A884" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B884" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>2654220</v>
+        <v>2701735</v>
       </c>
       <c r="H884" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
     </row>
     <row r="885">
       <c r="A885" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B885" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>2656484</v>
+        <v>2654220</v>
       </c>
       <c r="H885" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
     </row>
     <row r="886">
       <c r="A886" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B886" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>2687535</v>
+        <v>2656484</v>
       </c>
       <c r="H886" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
     </row>
     <row r="887">
       <c r="A887" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B887" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>2685397</v>
+        <v>2687535</v>
       </c>
       <c r="H887" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
     </row>
     <row r="888">
       <c r="A888" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B888" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>2708154</v>
+        <v>2685397</v>
       </c>
       <c r="H888" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
     </row>
     <row r="889">
       <c r="A889" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B889" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>2750634</v>
+        <v>2708154</v>
       </c>
       <c r="H889" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
     </row>
     <row r="890">
       <c r="A890" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B890" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>2729162</v>
+        <v>2750634</v>
       </c>
       <c r="H890" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
     </row>
     <row r="891">
       <c r="A891" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B891" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         </is>
       </c>
       <c r="G891" t="n">
-        <v>2727499</v>
+        <v>2729162</v>
       </c>
       <c r="H891" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
     </row>
     <row r="892">
       <c r="A892" s="1" t="n">
-        <v>44500</v>
+        <v>46265</v>
       </c>
       <c r="B892" t="inlineStr">
         <is>
@@ -45877,11 +45877,11 @@
         </is>
       </c>
       <c r="C892" t="n">
-        <v>20539</v>
+        <v>20540</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>saldo_credito_total</t>
+          <t>saldo_credito_pj</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -45895,11 +45895,11 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>4511956</v>
+        <v>2727499</v>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>Saldo da carteira de crédito - total.</t>
+          <t>Saldo da carteira de crédito - pessoas jurídicas.</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -45920,7 +45920,7 @@
     </row>
     <row r="893">
       <c r="A893" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B893" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>4597507</v>
+        <v>4511956</v>
       </c>
       <c r="H893" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
     </row>
     <row r="894">
       <c r="A894" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B894" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>4682852</v>
+        <v>4597507</v>
       </c>
       <c r="H894" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
     </row>
     <row r="895">
       <c r="A895" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B895" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>4682131</v>
+        <v>4682852</v>
       </c>
       <c r="H895" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
     </row>
     <row r="896">
       <c r="A896" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B896" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>4727818</v>
+        <v>4682131</v>
       </c>
       <c r="H896" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
     </row>
     <row r="897">
       <c r="A897" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B897" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>4794583</v>
+        <v>4727818</v>
       </c>
       <c r="H897" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
     </row>
     <row r="898">
       <c r="A898" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B898" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>4833732</v>
+        <v>4794583</v>
       </c>
       <c r="H898" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
     </row>
     <row r="899">
       <c r="A899" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B899" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>4889397</v>
+        <v>4833732</v>
       </c>
       <c r="H899" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
     </row>
     <row r="900">
       <c r="A900" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B900" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>4965603</v>
+        <v>4889397</v>
       </c>
       <c r="H900" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
     </row>
     <row r="901">
       <c r="A901" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B901" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>4999244</v>
+        <v>4965603</v>
       </c>
       <c r="H901" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
     </row>
     <row r="902">
       <c r="A902" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B902" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>5072711</v>
+        <v>4999244</v>
       </c>
       <c r="H902" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
     </row>
     <row r="903">
       <c r="A903" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B903" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>5164775</v>
+        <v>5072711</v>
       </c>
       <c r="H903" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
     </row>
     <row r="904">
       <c r="A904" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B904" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>5215990</v>
+        <v>5164775</v>
       </c>
       <c r="H904" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
     </row>
     <row r="905">
       <c r="A905" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B905" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>5285657</v>
+        <v>5215990</v>
       </c>
       <c r="H905" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
     </row>
     <row r="906">
       <c r="A906" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B906" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>5366069</v>
+        <v>5285657</v>
       </c>
       <c r="H906" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
     </row>
     <row r="907">
       <c r="A907" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B907" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>5373231</v>
+        <v>5366069</v>
       </c>
       <c r="H907" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
     </row>
     <row r="908">
       <c r="A908" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B908" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         </is>
       </c>
       <c r="G908" t="n">
-        <v>5370950</v>
+        <v>5373231</v>
       </c>
       <c r="H908" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
     </row>
     <row r="909">
       <c r="A909" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B909" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         </is>
       </c>
       <c r="G909" t="n">
-        <v>5424811</v>
+        <v>5370950</v>
       </c>
       <c r="H909" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
     </row>
     <row r="910">
       <c r="A910" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B910" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>5426307</v>
+        <v>5424811</v>
       </c>
       <c r="H910" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
     </row>
     <row r="911">
       <c r="A911" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B911" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>5453708</v>
+        <v>5426307</v>
       </c>
       <c r="H911" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
     </row>
     <row r="912">
       <c r="A912" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B912" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>5479459</v>
+        <v>5453708</v>
       </c>
       <c r="H912" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
     </row>
     <row r="913">
       <c r="A913" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B913" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>5484871</v>
+        <v>5479459</v>
       </c>
       <c r="H913" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
     </row>
     <row r="914">
       <c r="A914" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B914" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>5559063</v>
+        <v>5484871</v>
       </c>
       <c r="H914" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
     </row>
     <row r="915">
       <c r="A915" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B915" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>5625945</v>
+        <v>5559063</v>
       </c>
       <c r="H915" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
     </row>
     <row r="916">
       <c r="A916" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B916" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>5653808</v>
+        <v>5625945</v>
       </c>
       <c r="H916" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
     </row>
     <row r="917">
       <c r="A917" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B917" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>5711103</v>
+        <v>5653808</v>
       </c>
       <c r="H917" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
     </row>
     <row r="918">
       <c r="A918" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B918" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>5805157</v>
+        <v>5711103</v>
       </c>
       <c r="H918" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
     </row>
     <row r="919">
       <c r="A919" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B919" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>5794707</v>
+        <v>5805157</v>
       </c>
       <c r="H919" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
     </row>
     <row r="920">
       <c r="A920" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B920" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>5815954</v>
+        <v>5794707</v>
       </c>
       <c r="H920" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
     </row>
     <row r="921">
       <c r="A921" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B921" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>5899742</v>
+        <v>5815954</v>
       </c>
       <c r="H921" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
     </row>
     <row r="922">
       <c r="A922" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B922" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>5915538</v>
+        <v>5899742</v>
       </c>
       <c r="H922" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
     </row>
     <row r="923">
       <c r="A923" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B923" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>5953960</v>
+        <v>5915538</v>
       </c>
       <c r="H923" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
     </row>
     <row r="924">
       <c r="A924" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B924" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>6041898</v>
+        <v>5953960</v>
       </c>
       <c r="H924" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
     </row>
     <row r="925">
       <c r="A925" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B925" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>6069205</v>
+        <v>6041898</v>
       </c>
       <c r="H925" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
     </row>
     <row r="926">
       <c r="A926" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B926" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         </is>
       </c>
       <c r="G926" t="n">
-        <v>6135298</v>
+        <v>6069205</v>
       </c>
       <c r="H926" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
     </row>
     <row r="927">
       <c r="A927" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B927" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>6216528</v>
+        <v>6135298</v>
       </c>
       <c r="H927" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
     </row>
     <row r="928">
       <c r="A928" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B928" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>6275117</v>
+        <v>6216528</v>
       </c>
       <c r="H928" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
     </row>
     <row r="929">
       <c r="A929" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B929" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         </is>
       </c>
       <c r="G929" t="n">
-        <v>6365690</v>
+        <v>6275117</v>
       </c>
       <c r="H929" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
     </row>
     <row r="930">
       <c r="A930" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B930" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>6464602</v>
+        <v>6365690</v>
       </c>
       <c r="H930" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
     </row>
     <row r="931">
       <c r="A931" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B931" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>6465016</v>
+        <v>6464602</v>
       </c>
       <c r="H931" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
     </row>
     <row r="932">
       <c r="A932" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B932" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>6511444</v>
+        <v>6465016</v>
       </c>
       <c r="H932" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
     </row>
     <row r="933">
       <c r="A933" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B933" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>6576464</v>
+        <v>6511444</v>
       </c>
       <c r="H933" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
     </row>
     <row r="934">
       <c r="A934" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B934" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>6623948</v>
+        <v>6576464</v>
       </c>
       <c r="H934" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
     </row>
     <row r="935">
       <c r="A935" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B935" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         </is>
       </c>
       <c r="G935" t="n">
-        <v>6666287</v>
+        <v>6623948</v>
       </c>
       <c r="H935" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
     </row>
     <row r="936">
       <c r="A936" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B936" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         </is>
       </c>
       <c r="G936" t="n">
-        <v>6703663</v>
+        <v>6666287</v>
       </c>
       <c r="H936" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
     </row>
     <row r="937">
       <c r="A937" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B937" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         </is>
       </c>
       <c r="G937" t="n">
-        <v>6733209</v>
+        <v>6703663</v>
       </c>
       <c r="H937" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
     </row>
     <row r="938">
       <c r="A938" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B938" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         </is>
       </c>
       <c r="G938" t="n">
-        <v>6774436</v>
+        <v>6733209</v>
       </c>
       <c r="H938" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
     </row>
     <row r="939">
       <c r="A939" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B939" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         </is>
       </c>
       <c r="G939" t="n">
-        <v>6852705</v>
+        <v>6774436</v>
       </c>
       <c r="H939" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
     </row>
     <row r="940">
       <c r="A940" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B940" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         </is>
       </c>
       <c r="G940" t="n">
-        <v>6923886</v>
+        <v>6852705</v>
       </c>
       <c r="H940" t="inlineStr">
         <is>
@@ -48368,7 +48368,7 @@
     </row>
     <row r="941">
       <c r="A941" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B941" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="G941" t="n">
-        <v>7004223</v>
+        <v>6923886</v>
       </c>
       <c r="H941" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
     </row>
     <row r="942">
       <c r="A942" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B942" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>7137252</v>
+        <v>7004223</v>
       </c>
       <c r="H942" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
     </row>
     <row r="943">
       <c r="A943" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B943" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>7130762</v>
+        <v>7137252</v>
       </c>
       <c r="H943" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B944" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>7157783</v>
+        <v>7130762</v>
       </c>
       <c r="H944" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B945" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         </is>
       </c>
       <c r="G945" t="n">
-        <v>7240557</v>
+        <v>7157783</v>
       </c>
       <c r="H945" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
     </row>
     <row r="946">
       <c r="A946" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B946" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>7259766</v>
+        <v>7240557</v>
       </c>
       <c r="H946" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
     </row>
     <row r="947">
       <c r="A947" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B947" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>7305322</v>
+        <v>7259766</v>
       </c>
       <c r="H947" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
     </row>
     <row r="948">
       <c r="A948" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B948" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>7353302</v>
+        <v>7305322</v>
       </c>
       <c r="H948" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
     </row>
     <row r="949">
       <c r="A949" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B949" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>7362305</v>
+        <v>7353302</v>
       </c>
       <c r="H949" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
     </row>
     <row r="950">
       <c r="A950" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B950" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         </is>
       </c>
       <c r="G950" t="n">
-        <v>7397669</v>
+        <v>7362305</v>
       </c>
       <c r="H950" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
     </row>
     <row r="951">
       <c r="A951" s="1" t="n">
-        <v>44500</v>
+        <v>46265</v>
       </c>
       <c r="B951" t="inlineStr">
         <is>
@@ -48886,34 +48886,34 @@
         </is>
       </c>
       <c r="C951" t="n">
-        <v>11</v>
+        <v>20539</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>saldo_credito_total</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>R$ milhões</t>
         </is>
       </c>
       <c r="G951" t="n">
-        <v>0.024383</v>
+        <v>7397669</v>
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Saldo da carteira de crédito - total.</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="J951" t="inlineStr">
@@ -48923,13 +48923,13 @@
       </c>
       <c r="K951" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B952" t="inlineStr">
         <is>
@@ -48937,11 +48937,11 @@
         </is>
       </c>
       <c r="C952" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -48951,15 +48951,15 @@
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G952" t="n">
-        <v>0.029256</v>
+        <v>7.75</v>
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
@@ -48974,13 +48974,13 @@
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B953" t="inlineStr">
         <is>
@@ -48988,11 +48988,11 @@
         </is>
       </c>
       <c r="C953" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -49002,15 +49002,15 @@
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G953" t="n">
-        <v>0.033316</v>
+        <v>7.75</v>
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
@@ -49025,13 +49025,13 @@
       </c>
       <c r="K953" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B954" t="inlineStr">
         <is>
@@ -49039,11 +49039,11 @@
         </is>
       </c>
       <c r="C954" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -49053,15 +49053,15 @@
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G954" t="n">
-        <v>0.034749</v>
+        <v>9.25</v>
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
@@ -49076,13 +49076,13 @@
       </c>
       <c r="K954" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B955" t="inlineStr">
         <is>
@@ -49090,11 +49090,11 @@
         </is>
       </c>
       <c r="C955" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -49104,15 +49104,15 @@
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G955" t="n">
-        <v>0.039598</v>
+        <v>9.25</v>
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
@@ -49127,13 +49127,13 @@
       </c>
       <c r="K955" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B956" t="inlineStr">
         <is>
@@ -49141,11 +49141,11 @@
         </is>
       </c>
       <c r="C956" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -49155,15 +49155,15 @@
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G956" t="n">
-        <v>0.041954</v>
+        <v>10.75</v>
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
@@ -49178,13 +49178,13 @@
       </c>
       <c r="K956" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B957" t="inlineStr">
         <is>
@@ -49192,11 +49192,11 @@
         </is>
       </c>
       <c r="C957" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
@@ -49206,15 +49206,15 @@
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G957" t="n">
-        <v>0.043739</v>
+        <v>11.75</v>
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
@@ -49229,13 +49229,13 @@
       </c>
       <c r="K957" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B958" t="inlineStr">
         <is>
@@ -49243,11 +49243,11 @@
         </is>
       </c>
       <c r="C958" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
@@ -49257,15 +49257,15 @@
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G958" t="n">
-        <v>0.046796</v>
+        <v>11.75</v>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
@@ -49280,13 +49280,13 @@
       </c>
       <c r="K958" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B959" t="inlineStr">
         <is>
@@ -49294,11 +49294,11 @@
         </is>
       </c>
       <c r="C959" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -49308,15 +49308,15 @@
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G959" t="n">
-        <v>0.048116</v>
+        <v>12.75</v>
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -49331,13 +49331,13 @@
       </c>
       <c r="K959" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B960" t="inlineStr">
         <is>
@@ -49345,11 +49345,11 @@
         </is>
       </c>
       <c r="C960" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -49359,15 +49359,15 @@
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G960" t="n">
-        <v>0.049037</v>
+        <v>13.25</v>
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
@@ -49382,13 +49382,13 @@
       </c>
       <c r="K960" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B961" t="inlineStr">
         <is>
@@ -49396,11 +49396,11 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
@@ -49410,15 +49410,15 @@
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G961" t="n">
-        <v>0.05056</v>
+        <v>13.25</v>
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
@@ -49433,13 +49433,13 @@
       </c>
       <c r="K961" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B962" t="inlineStr">
         <is>
@@ -49447,11 +49447,11 @@
         </is>
       </c>
       <c r="C962" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
@@ -49461,15 +49461,15 @@
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G962" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
@@ -49484,13 +49484,13 @@
       </c>
       <c r="K962" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B963" t="inlineStr">
         <is>
@@ -49498,11 +49498,11 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
@@ -49512,15 +49512,15 @@
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G963" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
@@ -49535,13 +49535,13 @@
       </c>
       <c r="K963" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B964" t="inlineStr">
         <is>
@@ -49549,11 +49549,11 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -49563,15 +49563,15 @@
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G964" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -49586,13 +49586,13 @@
       </c>
       <c r="K964" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B965" t="inlineStr">
         <is>
@@ -49600,11 +49600,11 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -49614,15 +49614,15 @@
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G965" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -49637,13 +49637,13 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B966" t="inlineStr">
         <is>
@@ -49651,11 +49651,11 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
@@ -49665,15 +49665,15 @@
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G966" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
@@ -49688,13 +49688,13 @@
       </c>
       <c r="K966" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B967" t="inlineStr">
         <is>
@@ -49702,11 +49702,11 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -49716,15 +49716,15 @@
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G967" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -49739,13 +49739,13 @@
       </c>
       <c r="K967" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B968" t="inlineStr">
         <is>
@@ -49753,11 +49753,11 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
@@ -49767,15 +49767,15 @@
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G968" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I968" t="inlineStr">
@@ -49790,13 +49790,13 @@
       </c>
       <c r="K968" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B969" t="inlineStr">
         <is>
@@ -49804,11 +49804,11 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -49818,15 +49818,15 @@
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G969" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
@@ -49841,13 +49841,13 @@
       </c>
       <c r="K969" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B970" t="inlineStr">
         <is>
@@ -49855,11 +49855,11 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -49869,15 +49869,15 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
@@ -49892,13 +49892,13 @@
       </c>
       <c r="K970" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B971" t="inlineStr">
         <is>
@@ -49906,11 +49906,11 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -49920,15 +49920,15 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
@@ -49943,13 +49943,13 @@
       </c>
       <c r="K971" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B972" t="inlineStr">
         <is>
@@ -49957,11 +49957,11 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
@@ -49971,15 +49971,15 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.050788</v>
+        <v>13.75</v>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -49994,13 +49994,13 @@
       </c>
       <c r="K972" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B973" t="inlineStr">
         <is>
@@ -50008,11 +50008,11 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
@@ -50022,15 +50022,15 @@
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.049189</v>
+        <v>13.75</v>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
@@ -50045,13 +50045,13 @@
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B974" t="inlineStr">
         <is>
@@ -50059,11 +50059,11 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -50073,15 +50073,15 @@
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.048422</v>
+        <v>13.25</v>
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
@@ -50096,13 +50096,13 @@
       </c>
       <c r="K974" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B975" t="inlineStr">
         <is>
@@ -50110,11 +50110,11 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -50124,15 +50124,15 @@
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.047279</v>
+        <v>12.75</v>
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -50147,13 +50147,13 @@
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B976" t="inlineStr">
         <is>
@@ -50161,11 +50161,11 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -50175,15 +50175,15 @@
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G976" t="n">
-        <v>0.045601</v>
+        <v>12.75</v>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
@@ -50198,13 +50198,13 @@
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B977" t="inlineStr">
         <is>
@@ -50212,11 +50212,11 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -50226,15 +50226,15 @@
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.044537</v>
+        <v>12.25</v>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
@@ -50249,13 +50249,13 @@
       </c>
       <c r="K977" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B978" t="inlineStr">
         <is>
@@ -50263,11 +50263,11 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -50277,15 +50277,15 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.043739</v>
+        <v>11.75</v>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -50300,13 +50300,13 @@
       </c>
       <c r="K978" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B979" t="inlineStr">
         <is>
@@ -50314,11 +50314,11 @@
         </is>
       </c>
       <c r="C979" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -50328,15 +50328,15 @@
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G979" t="n">
-        <v>0.041957</v>
+        <v>11.75</v>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
@@ -50351,13 +50351,13 @@
       </c>
       <c r="K979" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B980" t="inlineStr">
         <is>
@@ -50365,11 +50365,11 @@
         </is>
       </c>
       <c r="C980" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
@@ -50379,15 +50379,15 @@
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.04142</v>
+        <v>11.25</v>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
@@ -50402,13 +50402,13 @@
       </c>
       <c r="K980" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B981" t="inlineStr">
         <is>
@@ -50416,11 +50416,11 @@
         </is>
       </c>
       <c r="C981" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
@@ -50430,15 +50430,15 @@
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G981" t="n">
-        <v>0.040168</v>
+        <v>10.75</v>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
@@ -50453,13 +50453,13 @@
       </c>
       <c r="K981" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B982" t="inlineStr">
         <is>
@@ -50467,11 +50467,11 @@
         </is>
       </c>
       <c r="C982" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
@@ -50481,15 +50481,15 @@
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G982" t="n">
-        <v>0.039484</v>
+        <v>10.75</v>
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
@@ -50504,13 +50504,13 @@
       </c>
       <c r="K982" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B983" t="inlineStr">
         <is>
@@ -50518,11 +50518,11 @@
         </is>
       </c>
       <c r="C983" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
@@ -50532,15 +50532,15 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G983" t="n">
-        <v>0.03927</v>
+        <v>10.5</v>
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
@@ -50555,13 +50555,13 @@
       </c>
       <c r="K983" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B984" t="inlineStr">
         <is>
@@ -50569,11 +50569,11 @@
         </is>
       </c>
       <c r="C984" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
@@ -50583,15 +50583,15 @@
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G984" t="n">
-        <v>0.03927</v>
+        <v>10.5</v>
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -50606,13 +50606,13 @@
       </c>
       <c r="K984" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B985" t="inlineStr">
         <is>
@@ -50620,11 +50620,11 @@
         </is>
       </c>
       <c r="C985" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -50634,15 +50634,15 @@
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.03927</v>
+        <v>10.5</v>
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -50657,13 +50657,13 @@
       </c>
       <c r="K985" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B986" t="inlineStr">
         <is>
@@ -50671,11 +50671,11 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -50685,15 +50685,15 @@
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.039612</v>
+        <v>10.5</v>
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -50708,13 +50708,13 @@
       </c>
       <c r="K986" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B987" t="inlineStr">
         <is>
@@ -50722,11 +50722,11 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
@@ -50736,15 +50736,15 @@
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G987" t="n">
-        <v>0.040168</v>
+        <v>10.75</v>
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
@@ -50759,13 +50759,13 @@
       </c>
       <c r="K987" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B988" t="inlineStr">
         <is>
@@ -50773,11 +50773,11 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
@@ -50787,15 +50787,15 @@
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G988" t="n">
-        <v>0.04158</v>
+        <v>10.75</v>
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
@@ -50810,13 +50810,13 @@
       </c>
       <c r="K988" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B989" t="inlineStr">
         <is>
@@ -50824,11 +50824,11 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -50838,15 +50838,15 @@
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G989" t="n">
-        <v>0.044158</v>
+        <v>11.25</v>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
@@ -50861,13 +50861,13 @@
       </c>
       <c r="K989" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B990" t="inlineStr">
         <is>
@@ -50875,11 +50875,11 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
@@ -50889,15 +50889,15 @@
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G990" t="n">
-        <v>0.045833</v>
+        <v>12.25</v>
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
@@ -50912,13 +50912,13 @@
       </c>
       <c r="K990" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B991" t="inlineStr">
         <is>
@@ -50926,11 +50926,11 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
@@ -50940,15 +50940,15 @@
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G991" t="n">
-        <v>0.049037</v>
+        <v>13.25</v>
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I991" t="inlineStr">
@@ -50963,13 +50963,13 @@
       </c>
       <c r="K991" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B992" t="inlineStr">
         <is>
@@ -50977,11 +50977,11 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
@@ -50991,15 +50991,15 @@
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G992" t="n">
-        <v>0.050508</v>
+        <v>13.25</v>
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -51014,13 +51014,13 @@
       </c>
       <c r="K992" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B993" t="inlineStr">
         <is>
@@ -51028,11 +51028,11 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -51042,15 +51042,15 @@
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G993" t="n">
-        <v>0.052531</v>
+        <v>14.25</v>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
@@ -51065,13 +51065,13 @@
       </c>
       <c r="K993" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B994" t="inlineStr">
         <is>
@@ -51079,11 +51079,11 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
@@ -51093,15 +51093,15 @@
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G994" t="n">
-        <v>0.053936</v>
+        <v>14.25</v>
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I994" t="inlineStr">
@@ -51116,13 +51116,13 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B995" t="inlineStr">
         <is>
@@ -51130,11 +51130,11 @@
         </is>
       </c>
       <c r="C995" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
@@ -51144,15 +51144,15 @@
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G995" t="n">
-        <v>0.054569</v>
+        <v>14.75</v>
       </c>
       <c r="H995" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I995" t="inlineStr">
@@ -51167,13 +51167,13 @@
       </c>
       <c r="K995" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B996" t="inlineStr">
         <is>
@@ -51181,11 +51181,11 @@
         </is>
       </c>
       <c r="C996" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
@@ -51195,15 +51195,15 @@
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H996" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I996" t="inlineStr">
@@ -51218,13 +51218,13 @@
       </c>
       <c r="K996" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B997" t="inlineStr">
         <is>
@@ -51232,11 +51232,11 @@
         </is>
       </c>
       <c r="C997" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
@@ -51246,15 +51246,15 @@
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G997" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
@@ -51269,13 +51269,13 @@
       </c>
       <c r="K997" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B998" t="inlineStr">
         <is>
@@ -51283,11 +51283,11 @@
         </is>
       </c>
       <c r="C998" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -51297,15 +51297,15 @@
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -51320,13 +51320,13 @@
       </c>
       <c r="K998" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B999" t="inlineStr">
         <is>
@@ -51334,11 +51334,11 @@
         </is>
       </c>
       <c r="C999" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -51348,15 +51348,15 @@
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G999" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -51371,13 +51371,13 @@
       </c>
       <c r="K999" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
@@ -51385,11 +51385,11 @@
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -51399,15 +51399,15 @@
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -51422,13 +51422,13 @@
       </c>
       <c r="K1000" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
@@ -51436,11 +51436,11 @@
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -51450,15 +51450,15 @@
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
@@ -51473,13 +51473,13 @@
       </c>
       <c r="K1001" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
@@ -51487,11 +51487,11 @@
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -51501,15 +51501,15 @@
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -51524,13 +51524,13 @@
       </c>
       <c r="K1002" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
@@ -51538,11 +51538,11 @@
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -51552,15 +51552,15 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>0.055131</v>
+        <v>15</v>
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -51575,13 +51575,13 @@
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
@@ -51589,11 +51589,11 @@
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -51603,15 +51603,15 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1004" t="n">
-        <v>0.054777</v>
+        <v>15</v>
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -51626,13 +51626,13 @@
       </c>
       <c r="K1004" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
@@ -51640,11 +51640,11 @@
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -51654,15 +51654,15 @@
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1005" t="n">
-        <v>0.054223</v>
+        <v>14.75</v>
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -51677,13 +51677,13 @@
       </c>
       <c r="K1005" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
@@ -51691,11 +51691,11 @@
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -51705,15 +51705,15 @@
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>0.0534</v>
+        <v>14.5</v>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -51728,13 +51728,13 @@
       </c>
       <c r="K1006" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
@@ -51742,11 +51742,11 @@
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -51756,15 +51756,15 @@
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>0.053028</v>
+        <v>14.5</v>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -51779,13 +51779,13 @@
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
@@ -51793,11 +51793,11 @@
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -51807,15 +51807,15 @@
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>0.052531</v>
+        <v>14.25</v>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
@@ -51830,13 +51830,13 @@
       </c>
       <c r="K1008" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
@@ -51844,11 +51844,11 @@
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -51858,15 +51858,15 @@
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>0.051784</v>
+        <v>14.25</v>
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
@@ -51881,13 +51881,13 @@
       </c>
       <c r="K1009" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
@@ -51895,11 +51895,11 @@
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>selic_over</t>
+          <t>selic_meta</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
@@ -51909,15 +51909,15 @@
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t>% a.d.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G1010" t="n">
-        <v>0.051245</v>
+        <v>14</v>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>Taxa Selic over.</t>
+          <t>Taxa Selic meta definida pelo Copom.</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
@@ -51932,56 +51932,3218 @@
       </c>
       <c r="K1010" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>ultimo</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>432</v>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>selic_meta</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>% a.a.</t>
+        </is>
+      </c>
+      <c r="G1011" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>Taxa Selic meta definida pelo Copom.</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="1" t="n">
         <v>46326</v>
       </c>
-      <c r="B1011" t="inlineStr">
-        <is>
-          <t>Banco Central do Brasil - SGS/BCData</t>
-        </is>
-      </c>
-      <c r="C1011" t="n">
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>432</v>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>selic_meta</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>% a.a.</t>
+        </is>
+      </c>
+      <c r="G1012" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>Taxa Selic meta definida pelo Copom.</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>ultimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
         <v>11</v>
       </c>
-      <c r="D1011" t="inlineStr">
+      <c r="D1013" t="inlineStr">
         <is>
           <t>selic_over</t>
         </is>
       </c>
-      <c r="E1011" t="inlineStr">
+      <c r="E1013" t="inlineStr">
         <is>
           <t>politica_monetaria</t>
         </is>
       </c>
-      <c r="F1011" t="inlineStr">
+      <c r="F1013" t="inlineStr">
         <is>
           <t>% a.d.</t>
         </is>
       </c>
-      <c r="G1011" t="n">
+      <c r="G1013" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1014" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1016" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="1" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1017" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="1" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
         <v>0.050788</v>
       </c>
-      <c r="H1011" t="inlineStr">
+      <c r="H1024" t="inlineStr">
         <is>
           <t>Taxa Selic over.</t>
         </is>
       </c>
-      <c r="I1011" t="inlineStr">
+      <c r="I1024" t="inlineStr">
         <is>
           <t>diaria</t>
         </is>
       </c>
-      <c r="J1011" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="K1011" t="inlineStr">
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1026" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="1" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="1" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1029" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1030" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1031" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1032" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1033" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="1" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1034" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="1" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1036" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1037" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1038" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1039" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1040" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1041" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1042" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1043" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1044" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1045" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1046" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1047" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1048" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1049" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="1" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1050" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1051" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1052" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1053" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1054" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1055" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1056" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1057" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1058" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1059" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1060" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1061" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1062" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1063" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1066" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1067" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1070" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1071" t="n">
+        <v>0.051784</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>0.051245</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Banco Central do Brasil - SGS/BCData</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>selic_over</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>% a.d.</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Taxa Selic over.</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>diaria</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr">
         <is>
           <t>media</t>
         </is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="H1015" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.024925</v>
+        <v>0.025079</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -24916,16 +24916,16 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -24934,11 +24934,11 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>2.33</v>
+        <v>1.16</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -24967,16 +24967,16 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>2.36</v>
+        <v>0.84</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -25018,16 +25018,16 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -25036,11 +25036,11 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>2.35</v>
+        <v>0.73</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -25069,16 +25069,16 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -25087,11 +25087,11 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>2.51</v>
+        <v>0.67</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -25120,16 +25120,16 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -25138,11 +25138,11 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -25171,16 +25171,16 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -25189,11 +25189,11 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -25222,16 +25222,16 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -25240,11 +25240,11 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -25273,16 +25273,16 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -25291,11 +25291,11 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>2.79</v>
+        <v>0.45</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -25324,16 +25324,16 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -25342,11 +25342,11 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>2.73</v>
+        <v>0.62</v>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -25375,16 +25375,16 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -25393,11 +25393,11 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>2.84</v>
+        <v>-0.6</v>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -25426,16 +25426,16 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -25444,11 +25444,11 @@
         </is>
       </c>
       <c r="G491" t="n">
-        <v>2.9</v>
+        <v>-0.31</v>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -25477,16 +25477,16 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -25495,11 +25495,11 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>2.92</v>
+        <v>-0.32</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -25528,16 +25528,16 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -25546,11 +25546,11 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>3.04</v>
+        <v>0.47</v>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -25579,16 +25579,16 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -25597,11 +25597,11 @@
         </is>
       </c>
       <c r="G494" t="n">
-        <v>3.07</v>
+        <v>0.38</v>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -25630,16 +25630,16 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -25648,11 +25648,11 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>3.07</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -25681,16 +25681,16 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -25699,11 +25699,11 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>3.24</v>
+        <v>0.46</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -25732,16 +25732,16 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -25750,11 +25750,11 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>3.36</v>
+        <v>0.77</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -25783,16 +25783,16 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -25801,11 +25801,11 @@
         </is>
       </c>
       <c r="G498" t="n">
-        <v>3.35</v>
+        <v>0.64</v>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -25834,16 +25834,16 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -25852,11 +25852,11 @@
         </is>
       </c>
       <c r="G499" t="n">
-        <v>3.54</v>
+        <v>0.53</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -25885,16 +25885,16 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -25903,11 +25903,11 @@
         </is>
       </c>
       <c r="G500" t="n">
-        <v>3.65</v>
+        <v>0.36</v>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -25936,16 +25936,16 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -25954,11 +25954,11 @@
         </is>
       </c>
       <c r="G501" t="n">
-        <v>3.61</v>
+        <v>-0.1</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -25987,16 +25987,16 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>3.63</v>
+        <v>-0.09</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -26038,16 +26038,16 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -26056,11 +26056,11 @@
         </is>
       </c>
       <c r="G503" t="n">
-        <v>3.61</v>
+        <v>0.2</v>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -26089,16 +26089,16 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -26107,11 +26107,11 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>3.54</v>
+        <v>0.11</v>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -26140,16 +26140,16 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -26158,11 +26158,11 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>3.56</v>
+        <v>0.12</v>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -26191,16 +26191,16 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -26209,11 +26209,11 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>3.53</v>
+        <v>0.1</v>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -26242,16 +26242,16 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -26260,11 +26260,11 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>3.29</v>
+        <v>0.55</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -26293,16 +26293,16 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -26311,11 +26311,11 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>3.38</v>
+        <v>0.57</v>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -26344,16 +26344,16 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -26362,11 +26362,11 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>3.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -26395,16 +26395,16 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -26413,11 +26413,11 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>3.33</v>
+        <v>0.19</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -26446,16 +26446,16 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -26464,11 +26464,11 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>3.37</v>
+        <v>0.37</v>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -26497,16 +26497,16 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -26515,11 +26515,11 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>3.43</v>
+        <v>0.46</v>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -26548,16 +26548,16 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -26566,11 +26566,11 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>3.29</v>
+        <v>0.25</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -26599,16 +26599,16 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -26617,11 +26617,11 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>3.3</v>
+        <v>0.26</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -26650,16 +26650,16 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -26668,11 +26668,11 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>3.33</v>
+        <v>-0.14</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -26701,16 +26701,16 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -26719,11 +26719,11 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>3.34</v>
+        <v>0.48</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -26752,16 +26752,16 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -26770,11 +26770,11 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>3.3</v>
+        <v>0.61</v>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -26803,16 +26803,16 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -26821,11 +26821,11 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>3.27</v>
+        <v>0.33</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -26854,16 +26854,16 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -26872,11 +26872,11 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>3.08</v>
+        <v>0.48</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -26905,16 +26905,16 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -26923,11 +26923,11 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -26956,16 +26956,16 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -26974,11 +26974,11 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>3.41</v>
+        <v>1.48</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -27007,16 +27007,16 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -27025,11 +27025,11 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>3.44</v>
+        <v>0.51</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -27058,16 +27058,16 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -27076,11 +27076,11 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>3.67</v>
+        <v>0.48</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -27109,16 +27109,16 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -27127,11 +27127,11 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>3.72</v>
+        <v>0.35</v>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -27160,16 +27160,16 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -27178,11 +27178,11 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>3.75</v>
+        <v>0.23</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -27211,16 +27211,16 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -27229,11 +27229,11 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>3.96</v>
+        <v>0.21</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -27262,16 +27262,16 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
@@ -27280,11 +27280,11 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>4.14</v>
+        <v>-0.21</v>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -27313,16 +27313,16 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -27331,11 +27331,11 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>4.09</v>
+        <v>0.52</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -27364,16 +27364,16 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -27382,11 +27382,11 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>4.18</v>
+        <v>0.03</v>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -27415,16 +27415,16 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -27433,11 +27433,11 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>4.24</v>
+        <v>0.03</v>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -27466,16 +27466,16 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -27484,11 +27484,11 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>4.2</v>
+        <v>0.21</v>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -27517,16 +27517,16 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -27535,11 +27535,11 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>4.44</v>
+        <v>0.39</v>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -27568,16 +27568,16 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -27586,11 +27586,11 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>4.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -27619,16 +27619,16 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -27637,11 +27637,11 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>4.52</v>
+        <v>0.91</v>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -27670,16 +27670,16 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -27688,11 +27688,11 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>4.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -27721,16 +27721,16 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -27739,11 +27739,11 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>4.75</v>
+        <v>0.65</v>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -27772,16 +27772,16 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -27790,11 +27790,11 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>4.58</v>
+        <v>0.14</v>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -27823,16 +27823,16 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -27841,11 +27841,11 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>4.88</v>
+        <v>-0.01</v>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -27874,16 +27874,16 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>21082</v>
+        <v>188</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>inadimplencia_total</t>
+          <t>inpc</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -27892,11 +27892,11 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>5.04</v>
+        <v>-0.32</v>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Taxa de inadimplência da carteira de crédito - total.</t>
+          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -27917,7 +27917,7 @@
     </row>
     <row r="540">
       <c r="A540" s="1" t="n">
-        <v>44500</v>
+        <v>46295</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>1.16</v>
+        <v>0.82</v>
       </c>
       <c r="H540" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
     </row>
     <row r="541">
       <c r="A541" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -27976,11 +27976,11 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -27994,11 +27994,11 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>0.84</v>
+        <v>1.25</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -28019,7 +28019,7 @@
     </row>
     <row r="542">
       <c r="A542" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -28027,11 +28027,11 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -28045,11 +28045,11 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -28070,7 +28070,7 @@
     </row>
     <row r="543">
       <c r="A543" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -28078,11 +28078,11 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -28096,11 +28096,11 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -28121,7 +28121,7 @@
     </row>
     <row r="544">
       <c r="A544" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -28129,11 +28129,11 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -28147,11 +28147,11 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -28172,7 +28172,7 @@
     </row>
     <row r="545">
       <c r="A545" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -28180,11 +28180,11 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -28198,11 +28198,11 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -28223,7 +28223,7 @@
     </row>
     <row r="546">
       <c r="A546" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -28231,11 +28231,11 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -28249,11 +28249,11 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -28274,7 +28274,7 @@
     </row>
     <row r="547">
       <c r="A547" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -28282,11 +28282,11 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -28300,11 +28300,11 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -28325,7 +28325,7 @@
     </row>
     <row r="548">
       <c r="A548" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -28333,11 +28333,11 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -28351,11 +28351,11 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -28376,7 +28376,7 @@
     </row>
     <row r="549">
       <c r="A549" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -28384,11 +28384,11 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -28402,11 +28402,11 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>-0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -28427,7 +28427,7 @@
     </row>
     <row r="550">
       <c r="A550" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -28435,11 +28435,11 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -28453,11 +28453,11 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>-0.31</v>
+        <v>-0.68</v>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -28478,7 +28478,7 @@
     </row>
     <row r="551">
       <c r="A551" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -28486,11 +28486,11 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -28504,11 +28504,11 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -28529,7 +28529,7 @@
     </row>
     <row r="552">
       <c r="A552" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -28537,11 +28537,11 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -28555,11 +28555,11 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>0.47</v>
+        <v>-0.29</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -28580,7 +28580,7 @@
     </row>
     <row r="553">
       <c r="A553" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -28588,11 +28588,11 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -28606,11 +28606,11 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -28631,7 +28631,7 @@
     </row>
     <row r="554">
       <c r="A554" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -28639,11 +28639,11 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -28657,11 +28657,11 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -28682,7 +28682,7 @@
     </row>
     <row r="555">
       <c r="A555" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -28690,11 +28690,11 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -28708,11 +28708,11 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -28733,7 +28733,7 @@
     </row>
     <row r="556">
       <c r="A556" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -28741,11 +28741,11 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -28759,11 +28759,11 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>0.77</v>
+        <v>0.53</v>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -28784,7 +28784,7 @@
     </row>
     <row r="557">
       <c r="A557" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -28792,11 +28792,11 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -28810,11 +28810,11 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -28835,7 +28835,7 @@
     </row>
     <row r="558">
       <c r="A558" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -28843,11 +28843,11 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -28861,11 +28861,11 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -28886,7 +28886,7 @@
     </row>
     <row r="559">
       <c r="A559" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -28894,11 +28894,11 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -28912,11 +28912,11 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -28937,7 +28937,7 @@
     </row>
     <row r="560">
       <c r="A560" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -28945,11 +28945,11 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -28963,11 +28963,11 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>-0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -28988,7 +28988,7 @@
     </row>
     <row r="561">
       <c r="A561" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -28996,11 +28996,11 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -29014,11 +29014,11 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -29039,7 +29039,7 @@
     </row>
     <row r="562">
       <c r="A562" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -29047,11 +29047,11 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -29065,11 +29065,11 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -29090,7 +29090,7 @@
     </row>
     <row r="563">
       <c r="A563" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -29098,11 +29098,11 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -29116,11 +29116,11 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -29141,7 +29141,7 @@
     </row>
     <row r="564">
       <c r="A564" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -29149,11 +29149,11 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -29167,11 +29167,11 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -29192,7 +29192,7 @@
     </row>
     <row r="565">
       <c r="A565" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -29200,11 +29200,11 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -29218,11 +29218,11 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -29243,7 +29243,7 @@
     </row>
     <row r="566">
       <c r="A566" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -29251,11 +29251,11 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -29269,11 +29269,11 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -29294,7 +29294,7 @@
     </row>
     <row r="567">
       <c r="A567" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -29302,11 +29302,11 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -29320,11 +29320,11 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -29345,7 +29345,7 @@
     </row>
     <row r="568">
       <c r="A568" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -29353,11 +29353,11 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -29371,11 +29371,11 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -29396,7 +29396,7 @@
     </row>
     <row r="569">
       <c r="A569" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -29404,11 +29404,11 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -29422,11 +29422,11 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>0.19</v>
+        <v>0.83</v>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -29447,7 +29447,7 @@
     </row>
     <row r="570">
       <c r="A570" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -29455,11 +29455,11 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -29473,11 +29473,11 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -29498,7 +29498,7 @@
     </row>
     <row r="571">
       <c r="A571" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -29506,11 +29506,11 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -29524,11 +29524,11 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -29549,7 +29549,7 @@
     </row>
     <row r="572">
       <c r="A572" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -29557,11 +29557,11 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -29575,11 +29575,11 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -29600,7 +29600,7 @@
     </row>
     <row r="573">
       <c r="A573" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -29608,11 +29608,11 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -29626,11 +29626,11 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -29651,7 +29651,7 @@
     </row>
     <row r="574">
       <c r="A574" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -29659,11 +29659,11 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -29677,11 +29677,11 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>-0.14</v>
+        <v>0.38</v>
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -29702,7 +29702,7 @@
     </row>
     <row r="575">
       <c r="A575" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -29710,11 +29710,11 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -29728,11 +29728,11 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>0.48</v>
+        <v>-0.02</v>
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -29753,7 +29753,7 @@
     </row>
     <row r="576">
       <c r="A576" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -29761,11 +29761,11 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -29779,11 +29779,11 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>0.61</v>
+        <v>0.44</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -29804,7 +29804,7 @@
     </row>
     <row r="577">
       <c r="A577" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -29812,11 +29812,11 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -29830,11 +29830,11 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -29855,7 +29855,7 @@
     </row>
     <row r="578">
       <c r="A578" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -29863,11 +29863,11 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -29881,11 +29881,11 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -29906,7 +29906,7 @@
     </row>
     <row r="579">
       <c r="A579" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -29914,11 +29914,11 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -29932,11 +29932,11 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -29957,7 +29957,7 @@
     </row>
     <row r="580">
       <c r="A580" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -29965,11 +29965,11 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -29983,11 +29983,11 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>1.48</v>
+        <v>0.16</v>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -30008,7 +30008,7 @@
     </row>
     <row r="581">
       <c r="A581" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -30016,11 +30016,11 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -30034,11 +30034,11 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>0.51</v>
+        <v>1.31</v>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -30059,7 +30059,7 @@
     </row>
     <row r="582">
       <c r="A582" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -30067,11 +30067,11 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -30085,11 +30085,11 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -30110,7 +30110,7 @@
     </row>
     <row r="583">
       <c r="A583" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -30118,11 +30118,11 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -30136,11 +30136,11 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -30161,7 +30161,7 @@
     </row>
     <row r="584">
       <c r="A584" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -30169,11 +30169,11 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -30187,11 +30187,11 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -30212,7 +30212,7 @@
     </row>
     <row r="585">
       <c r="A585" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -30220,11 +30220,11 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -30238,11 +30238,11 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -30263,7 +30263,7 @@
     </row>
     <row r="586">
       <c r="A586" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -30271,11 +30271,11 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -30289,11 +30289,11 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>-0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -30314,7 +30314,7 @@
     </row>
     <row r="587">
       <c r="A587" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -30322,11 +30322,11 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -30340,11 +30340,11 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>0.52</v>
+        <v>-0.11</v>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -30365,7 +30365,7 @@
     </row>
     <row r="588">
       <c r="A588" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -30373,11 +30373,11 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -30391,11 +30391,11 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -30416,7 +30416,7 @@
     </row>
     <row r="589">
       <c r="A589" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -30424,11 +30424,11 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -30442,11 +30442,11 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -30467,7 +30467,7 @@
     </row>
     <row r="590">
       <c r="A590" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -30475,11 +30475,11 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -30493,11 +30493,11 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -30518,7 +30518,7 @@
     </row>
     <row r="591">
       <c r="A591" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -30526,11 +30526,11 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -30544,11 +30544,11 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -30569,7 +30569,7 @@
     </row>
     <row r="592">
       <c r="A592" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -30577,11 +30577,11 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -30595,11 +30595,11 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -30620,7 +30620,7 @@
     </row>
     <row r="593">
       <c r="A593" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -30628,11 +30628,11 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -30646,11 +30646,11 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -30671,7 +30671,7 @@
     </row>
     <row r="594">
       <c r="A594" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -30679,11 +30679,11 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -30697,11 +30697,11 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -30722,7 +30722,7 @@
     </row>
     <row r="595">
       <c r="A595" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -30730,11 +30730,11 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -30748,11 +30748,11 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -30773,7 +30773,7 @@
     </row>
     <row r="596">
       <c r="A596" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -30781,11 +30781,11 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -30799,11 +30799,11 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>0.14</v>
+        <v>0.58</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -30824,7 +30824,7 @@
     </row>
     <row r="597">
       <c r="A597" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -30832,11 +30832,11 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -30850,11 +30850,11 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>-0.01</v>
+        <v>0.16</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -30875,7 +30875,7 @@
     </row>
     <row r="598">
       <c r="A598" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -30883,11 +30883,11 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -30901,11 +30901,11 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>-0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -30926,7 +30926,7 @@
     </row>
     <row r="599">
       <c r="A599" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -30934,11 +30934,11 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>inpc</t>
+          <t>ipca</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -30952,11 +30952,11 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>0.82</v>
+        <v>-0.32</v>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor - INPC.</t>
+          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -30977,7 +30977,7 @@
     </row>
     <row r="600">
       <c r="A600" s="1" t="n">
-        <v>44500</v>
+        <v>46295</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>1.25</v>
+        <v>0.82</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
     </row>
     <row r="601">
       <c r="A601" s="1" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -31036,29 +31036,29 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G601" t="n">
-        <v>0.95</v>
+        <v>22.89</v>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -31079,7 +31079,7 @@
     </row>
     <row r="602">
       <c r="A602" s="1" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -31087,29 +31087,29 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>0.73</v>
+        <v>23.91</v>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -31130,7 +31130,7 @@
     </row>
     <row r="603">
       <c r="A603" s="1" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -31138,29 +31138,29 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>0.54</v>
+        <v>24.21</v>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -31181,7 +31181,7 @@
     </row>
     <row r="604">
       <c r="A604" s="1" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -31189,29 +31189,29 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G604" t="n">
-        <v>1.01</v>
+        <v>25.23</v>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -31232,7 +31232,7 @@
     </row>
     <row r="605">
       <c r="A605" s="1" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -31240,29 +31240,29 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>1.62</v>
+        <v>25.63</v>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -31283,7 +31283,7 @@
     </row>
     <row r="606">
       <c r="A606" s="1" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -31291,29 +31291,29 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G606" t="n">
-        <v>1.06</v>
+        <v>26.54</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -31334,7 +31334,7 @@
     </row>
     <row r="607">
       <c r="A607" s="1" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -31342,29 +31342,29 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G607" t="n">
-        <v>0.47</v>
+        <v>27.46</v>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -31385,7 +31385,7 @@
     </row>
     <row r="608">
       <c r="A608" s="1" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -31393,29 +31393,29 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G608" t="n">
-        <v>0.67</v>
+        <v>27.42</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -31436,7 +31436,7 @@
     </row>
     <row r="609">
       <c r="A609" s="1" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -31444,29 +31444,29 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G609" t="n">
-        <v>-0.68</v>
+        <v>27.88</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -31487,7 +31487,7 @@
     </row>
     <row r="610">
       <c r="A610" s="1" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -31495,29 +31495,29 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G610" t="n">
-        <v>-0.36</v>
+        <v>29.24</v>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -31538,7 +31538,7 @@
     </row>
     <row r="611">
       <c r="A611" s="1" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -31546,29 +31546,29 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G611" t="n">
-        <v>-0.29</v>
+        <v>28.6</v>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -31589,7 +31589,7 @@
     </row>
     <row r="612">
       <c r="A612" s="1" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -31597,29 +31597,29 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G612" t="n">
-        <v>0.59</v>
+        <v>28.57</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -31640,7 +31640,7 @@
     </row>
     <row r="613">
       <c r="A613" s="1" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -31648,29 +31648,29 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G613" t="n">
-        <v>0.41</v>
+        <v>29.68</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -31691,7 +31691,7 @@
     </row>
     <row r="614">
       <c r="A614" s="1" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -31699,29 +31699,29 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G614" t="n">
-        <v>0.62</v>
+        <v>30.52</v>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -31742,7 +31742,7 @@
     </row>
     <row r="615">
       <c r="A615" s="1" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -31750,29 +31750,29 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G615" t="n">
-        <v>0.53</v>
+        <v>29.64</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -31793,7 +31793,7 @@
     </row>
     <row r="616">
       <c r="A616" s="1" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -31801,29 +31801,29 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G616" t="n">
-        <v>0.84</v>
+        <v>30.54</v>
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -31844,7 +31844,7 @@
     </row>
     <row r="617">
       <c r="A617" s="1" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -31852,29 +31852,29 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G617" t="n">
-        <v>0.71</v>
+        <v>30.48</v>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -31895,7 +31895,7 @@
     </row>
     <row r="618">
       <c r="A618" s="1" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -31903,29 +31903,29 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G618" t="n">
-        <v>0.61</v>
+        <v>30.99</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -31946,7 +31946,7 @@
     </row>
     <row r="619">
       <c r="A619" s="1" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -31954,29 +31954,29 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G619" t="n">
-        <v>0.23</v>
+        <v>31.62</v>
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -31997,7 +31997,7 @@
     </row>
     <row r="620">
       <c r="A620" s="1" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -32005,29 +32005,29 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G620" t="n">
-        <v>-0.08</v>
+        <v>31.63</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -32048,7 +32048,7 @@
     </row>
     <row r="621">
       <c r="A621" s="1" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -32056,29 +32056,29 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G621" t="n">
-        <v>0.12</v>
+        <v>30.85</v>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -32099,7 +32099,7 @@
     </row>
     <row r="622">
       <c r="A622" s="1" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -32107,29 +32107,29 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G622" t="n">
-        <v>0.23</v>
+        <v>30.43</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -32150,7 +32150,7 @@
     </row>
     <row r="623">
       <c r="A623" s="1" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -32158,29 +32158,29 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G623" t="n">
-        <v>0.26</v>
+        <v>29.92</v>
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -32201,7 +32201,7 @@
     </row>
     <row r="624">
       <c r="A624" s="1" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -32209,29 +32209,29 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G624" t="n">
-        <v>0.24</v>
+        <v>29.66</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -32252,7 +32252,7 @@
     </row>
     <row r="625">
       <c r="A625" s="1" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -32260,29 +32260,29 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G625" t="n">
-        <v>0.28</v>
+        <v>29.24</v>
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -32303,7 +32303,7 @@
     </row>
     <row r="626">
       <c r="A626" s="1" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -32311,29 +32311,29 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G626" t="n">
-        <v>0.5600000000000001</v>
+        <v>29.01</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -32354,7 +32354,7 @@
     </row>
     <row r="627">
       <c r="A627" s="1" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -32362,29 +32362,29 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G627" t="n">
-        <v>0.42</v>
+        <v>28.14</v>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -32405,7 +32405,7 @@
     </row>
     <row r="628">
       <c r="A628" s="1" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -32413,29 +32413,29 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G628" t="n">
-        <v>0.83</v>
+        <v>28</v>
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -32456,7 +32456,7 @@
     </row>
     <row r="629">
       <c r="A629" s="1" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -32464,29 +32464,29 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G629" t="n">
-        <v>0.16</v>
+        <v>27.85</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -32507,7 +32507,7 @@
     </row>
     <row r="630">
       <c r="A630" s="1" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -32515,29 +32515,29 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G630" t="n">
-        <v>0.38</v>
+        <v>28.14</v>
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -32558,7 +32558,7 @@
     </row>
     <row r="631">
       <c r="A631" s="1" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -32566,29 +32566,29 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G631" t="n">
-        <v>0.46</v>
+        <v>27.86</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -32609,7 +32609,7 @@
     </row>
     <row r="632">
       <c r="A632" s="1" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -32617,29 +32617,29 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G632" t="n">
-        <v>0.21</v>
+        <v>27.75</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -32660,7 +32660,7 @@
     </row>
     <row r="633">
       <c r="A633" s="1" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -32668,29 +32668,29 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G633" t="n">
-        <v>0.38</v>
+        <v>27.81</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -32711,7 +32711,7 @@
     </row>
     <row r="634">
       <c r="A634" s="1" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -32719,29 +32719,29 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G634" t="n">
-        <v>-0.02</v>
+        <v>27.74</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -32762,7 +32762,7 @@
     </row>
     <row r="635">
       <c r="A635" s="1" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -32770,29 +32770,29 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G635" t="n">
-        <v>0.44</v>
+        <v>27.59</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -32813,7 +32813,7 @@
     </row>
     <row r="636">
       <c r="A636" s="1" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -32821,29 +32821,29 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G636" t="n">
-        <v>0.5600000000000001</v>
+        <v>27.49</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -32864,7 +32864,7 @@
     </row>
     <row r="637">
       <c r="A637" s="1" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -32872,29 +32872,29 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G637" t="n">
-        <v>0.39</v>
+        <v>27.94</v>
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -32915,7 +32915,7 @@
     </row>
     <row r="638">
       <c r="A638" s="1" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -32923,29 +32923,29 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G638" t="n">
-        <v>0.52</v>
+        <v>28.45</v>
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -32966,7 +32966,7 @@
     </row>
     <row r="639">
       <c r="A639" s="1" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -32974,29 +32974,29 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G639" t="n">
-        <v>0.16</v>
+        <v>28.5</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -33017,7 +33017,7 @@
     </row>
     <row r="640">
       <c r="A640" s="1" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -33025,29 +33025,29 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G640" t="n">
-        <v>1.31</v>
+        <v>29.88</v>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -33068,7 +33068,7 @@
     </row>
     <row r="641">
       <c r="A641" s="1" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -33076,29 +33076,29 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G641" t="n">
-        <v>0.5600000000000001</v>
+        <v>30.53</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -33119,7 +33119,7 @@
     </row>
     <row r="642">
       <c r="A642" s="1" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -33127,29 +33127,29 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G642" t="n">
-        <v>0.43</v>
+        <v>31.34</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -33170,7 +33170,7 @@
     </row>
     <row r="643">
       <c r="A643" s="1" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -33178,29 +33178,29 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G643" t="n">
-        <v>0.26</v>
+        <v>31.63</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -33221,7 +33221,7 @@
     </row>
     <row r="644">
       <c r="A644" s="1" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -33229,29 +33229,29 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G644" t="n">
-        <v>0.24</v>
+        <v>31.7</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -33272,7 +33272,7 @@
     </row>
     <row r="645">
       <c r="A645" s="1" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -33280,29 +33280,29 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G645" t="n">
-        <v>0.26</v>
+        <v>31.85</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -33323,7 +33323,7 @@
     </row>
     <row r="646">
       <c r="A646" s="1" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -33331,29 +33331,29 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G646" t="n">
-        <v>-0.11</v>
+        <v>31.75</v>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -33374,7 +33374,7 @@
     </row>
     <row r="647">
       <c r="A647" s="1" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -33382,29 +33382,29 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G647" t="n">
-        <v>0.48</v>
+        <v>31.87</v>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -33425,7 +33425,7 @@
     </row>
     <row r="648">
       <c r="A648" s="1" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -33433,29 +33433,29 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G648" t="n">
-        <v>0.09</v>
+        <v>31.47</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -33476,7 +33476,7 @@
     </row>
     <row r="649">
       <c r="A649" s="1" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -33484,29 +33484,29 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G649" t="n">
-        <v>0.18</v>
+        <v>32.04</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -33527,7 +33527,7 @@
     </row>
     <row r="650">
       <c r="A650" s="1" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -33535,29 +33535,29 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G650" t="n">
-        <v>0.33</v>
+        <v>32.2</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -33578,7 +33578,7 @@
     </row>
     <row r="651">
       <c r="A651" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -33586,29 +33586,29 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G651" t="n">
-        <v>0.33</v>
+        <v>31.87</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -33629,7 +33629,7 @@
     </row>
     <row r="652">
       <c r="A652" s="1" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -33637,29 +33637,29 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G652" t="n">
-        <v>0.7</v>
+        <v>32.45</v>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -33680,7 +33680,7 @@
     </row>
     <row r="653">
       <c r="A653" s="1" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -33688,29 +33688,29 @@
         </is>
       </c>
       <c r="C653" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G653" t="n">
-        <v>0.88</v>
+        <v>32.63</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -33731,7 +33731,7 @@
     </row>
     <row r="654">
       <c r="A654" s="1" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -33739,29 +33739,29 @@
         </is>
       </c>
       <c r="C654" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G654" t="n">
-        <v>0.67</v>
+        <v>32.84</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -33782,7 +33782,7 @@
     </row>
     <row r="655">
       <c r="A655" s="1" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -33790,29 +33790,29 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G655" t="n">
-        <v>0.58</v>
+        <v>33.36</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -33833,7 +33833,7 @@
     </row>
     <row r="656">
       <c r="A656" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -33841,29 +33841,29 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G656" t="n">
-        <v>0.16</v>
+        <v>32.97</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -33884,7 +33884,7 @@
     </row>
     <row r="657">
       <c r="A657" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -33892,29 +33892,29 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G657" t="n">
-        <v>0.07000000000000001</v>
+        <v>32.63</v>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -33935,7 +33935,7 @@
     </row>
     <row r="658">
       <c r="A658" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -33943,29 +33943,29 @@
         </is>
       </c>
       <c r="C658" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G658" t="n">
-        <v>-0.32</v>
+        <v>32.06</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -33986,7 +33986,7 @@
     </row>
     <row r="659">
       <c r="A659" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -33994,29 +33994,29 @@
         </is>
       </c>
       <c r="C659" t="n">
-        <v>433</v>
+        <v>20714</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>ipca</t>
+          <t>juros_credito_total</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>% a.m.</t>
+          <t>% a.a.</t>
         </is>
       </c>
       <c r="G659" t="n">
-        <v>0.82</v>
+        <v>32.26</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Índice Nacional de Preços ao Consumidor Amplo - IPCA.</t>
+          <t>Taxa média de juros das operações de crédito - total.</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -49261,7 +49261,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>0.024925</v>
+        <v>0.025079</v>
       </c>
       <c r="H958" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.0134</v>
+        <v>5.027</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.014</v>
+        <v>5.0277</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.025278</v>
+        <v>0.025543</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.025278</v>
+        <v>0.025543</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_longa.xlsx
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5.4998</v>
+        <v>5.3414</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5.5007</v>
+        <v>5.342</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.0274</v>
+        <v>0.029256</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.0274</v>
+        <v>0.029256</v>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
